--- a/research.xlsx
+++ b/research.xlsx
@@ -16,9 +16,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'頁面設定'!$A$1:$J$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'研究成果'!$A$1:$I$54</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'實驗室'!$A$1:$D$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'實驗室'!$A$1:$D$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'教師獲獎記錄'!$A$1:$D$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'國外學者來訪'!$A$1:$F$439</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'國外學者來訪'!$A$1:$F$438</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3148,7 +3148,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -3596,129 +3596,129 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>低溫物理實驗室</t>
+          <t>基礎理論研究室</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Low Temperature Physics Laboratory</t>
+          <t>Fundamental Theory Group</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>陳永富 Yung-Fu Chen</t>
+          <t>江祖永 Otto Kong、陳江梅 Chiang-Mei Chen、瞿怡仁 Yi-Zen Chu</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>http://hep.phy.ncu.edu.tw/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>基礎理論研究室</t>
+          <t>分子馬達生物物理實驗室</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fundamental Theory Group</t>
+          <t>Molecular-Motor Biophysics Laboratory</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>江祖永 Otto Kong、陳江梅 Chiang-Mei Chen、瞿怡仁 Yi-Zen Chu</t>
+          <t>羅健榮 Chien-Jung Lo</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>http://hep.phy.ncu.edu.tw/</t>
+          <t>https://sites.google.com/phy.ncu.edu.tw/motorslab</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>分子馬達生物物理實驗室</t>
+          <t>探測器研發中心</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Molecular-Motor Biophysics Laboratory</t>
+          <t>Detector Center</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>羅健榮 Chien-Jung Lo</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/phy.ncu.edu.tw/motorslab</t>
+          <t>陳鎰鋒 Ei-Fong Chen</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>探測器研發中心</t>
+          <t>生物物理/生物薄膜實驗室</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Detector Center</t>
+          <t>Biological Physics Laboratory</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>陳鎰鋒 Ei-Fong Chen</t>
+          <t>薛雅薇 Ya-Wei Hsueh</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>http://yhsueh.phy.ncu.edu.tw/new_page_0.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>生物物理/生物薄膜實驗室</t>
+          <t>探測器研發實驗室</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biological Physics Laboratory</t>
+          <t>Detector R&amp;D Laboratory</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>薛雅薇 Ya-Wei Hsueh</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>http://yhsueh.phy.ncu.edu.tw/new_page_0.htm</t>
+          <t>林宗泰 Tsung-Tai Lin、余欣珊 Shin-Shan Yu、郭家銘 Chia-Ming Kuo、張元翰 Yuan-Hann Chang</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>探測器研發實驗室</t>
+          <t>先進顯微實驗室</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Detector R&amp;D Laboratory</t>
+          <t>Advanced Microscopy Laboratory</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>林宗泰 Tsung-Tai Lin、余欣珊 Shin-Shan Yu、郭家銘 Chia-Ming Kuo、張元翰 Yuan-Hann Chang</t>
+          <t>羅健榮 Chien-Jung Lo</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>先進顯微實驗室</t>
+          <t>生物物理與軟物質核心設施實驗室</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Advanced Microscopy Laboratory</t>
+          <t>BioPhysics and Soft-matter Core Facility Laboratory</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3730,197 +3730,163 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>生物物理與軟物質核心設施實驗室</t>
+          <t>生物軟物質及非線性物理實驗室</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BioPhysics and Soft-matter Core Facility Laboratory</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>羅健榮 Chien-Jung Lo</t>
+          <t>Bio-Soft Matters &amp; Nonlinear Physics Laboratory</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://pikyinlai.wixsite.com/lai_research_group</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>生物軟物質及非線性物理實驗室</t>
+          <t>理論量子與統計物理研究室</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bio-Soft Matters &amp; Nonlinear Physics Laboratory</t>
+          <t>&lt;a href="https://sites.google.com/view/jhcphysics" target="_blank" rel="noreferrer noopener" class="ek-link"&gt;Theoretical Quantum and Statistical Physics Group&lt;/a&gt;&lt;br&gt;</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>陳炯豪 Jyong-Hao Chen</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pikyinlai.wixsite.com/lai_research_group</t>
+          <t>https://sites.google.com/view/jhcphysics</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>理論量子與統計物理研究室</t>
+          <t>複雜液體研究室</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>&lt;a href="https://sites.google.com/view/jhcphysics" target="_blank" rel="noreferrer noopener" class="ek-link"&gt;Theoretical Quantum and Statistical Physics Group&lt;/a&gt;&lt;br&gt;</t>
+          <t>Complex Liquids Laboratory</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>陳炯豪 Jyong-Hao Chen</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/view/jhcphysics</t>
+          <t>賴山強 San-Kiong Lai</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>複雜液體研究室</t>
+          <t>電漿理論與模擬實驗室</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Complex Liquids Laboratory</t>
+          <t>Plasma Theory and Simulation Group</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>賴山強 San-Kiong Lai</t>
+          <t>林留玉仁  Y.R.Lin-Liu</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>電漿理論與模擬實驗室</t>
+          <t>理論量子光學研究室</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Plasma Theory and Simulation Group</t>
+          <t>Theoretical Quantum Optics Group</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>林留玉仁  Y.R.Lin-Liu</t>
+          <t>廖文德 Wen-Te Liao</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>理論量子光學研究室</t>
+          <t>軟物質與生物物理研究室</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Theoretical Quantum Optics Group</t>
+          <t>Soft Matters and BioPhysics Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>廖文德 Wen-Te Liao</t>
+          <t>陳宣毅 Hsuan-Yi Chen</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>軟物質與生物物理研究室</t>
+          <t>廣義相對論研究室</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Soft Matters and BioPhysics Group</t>
+          <t>General Relativity Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>陳宣毅 Hsuan-Yi Chen</t>
+          <t>陳江梅 Chiang-Mei Chen</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>廣義相對論研究室</t>
+          <t>計算材料研究室</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>General Relativity Group</t>
+          <t>Computational Materials Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>陳江梅 Chiang-Mei Chen</t>
+          <t>徐翰 Han Hsu</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>計算材料研究室</t>
+          <t>理論與計算自旋電子學研究室</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Computational Materials Group</t>
+          <t>Theoretical and Computational Spintronics Group</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>徐翰 Han Hsu</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>軟物質與生物物理研究室</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Soft Matters and BioPhysics Group</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>陳宣毅 Hsuan-Yi Chen</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>理論與計算自旋電子學研究室</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Theoretical and Computational Spintronics Group</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
           <t>唐毓慧 Yu-Hui Tang</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D41"/>
+  <autoFilter ref="A1:D39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5030,7 +4996,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F439"/>
+  <dimension ref="A1:F438"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7947,125 +7913,125 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ralf Kaiser</t>
+          <t>Thong Leng Lim</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>Senior Lecturer</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Department of Chemistry, University of Hawaii</t>
+          <t>馬來西亞Multimedia University</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>陳俞融</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>105.06.24-105.06.25</t>
+          <t>105.08.10-105.08.18</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Thong Leng Lim</t>
+          <t>Eung Jin Chun</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Senior Lecturer</t>
+          <t>教授</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>馬來西亞Multimedia University</t>
+          <t>KIAS</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>105.08.10-105.08.18</t>
+          <t>105.05.22-105.05.25</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Eung Jin Chun</t>
+          <t>Mudit Rai</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>大學部學生</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>KIAS</t>
+          <t>印度理工學院</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>105.05.22-105.05.25</t>
+          <t>105.05.06-105.07.15</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Mudit Rai</t>
+          <t>Michael Ramsey-Musolf</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>大學部學生</t>
+          <t>教授</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>印度理工學院</t>
+          <t>University of Massachusetts-Amherst, USA</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>105.05.06-105.07.15</t>
+          <t>105.05.15-105.05.21</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Michael Ramsey-Musolf</t>
+          <t>Koji Tsumura</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>助理教授</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>University of Massachusetts-Amherst, USA</t>
+          <t>Kyoto University, Japan</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8075,73 +8041,73 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>105.05.15-105.05.21</t>
+          <t>105.03.28-105.03.30</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Koji Tsumura</t>
+          <t>Hanna Salman</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>副教授</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Kyoto University, Japan</t>
+          <t>University of Pittsburgh</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>105.03.28-105.03.30</t>
+          <t>104.09.21-104.09.24</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Hanna Salman</t>
+          <t>Cesare Cecchi-Pestellini</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>副教授</t>
+          <t>教授</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>University of Pittsburgh</t>
+          <t>INAF – Osservatorio Astronomico di Palermo, Italy</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳俞融</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>104.09.21-104.09.24</t>
+          <t>104.11.14-104.12.13</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cesare Cecchi-Pestellini</t>
+          <t>Angela Ciaravella</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>教授</t>
+          <t>研究員</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8163,152 +8129,152 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Angela Ciaravella</t>
+          <t>Koji Tsumura</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>研究員</t>
+          <t>助理教授</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>INAF – Osservatorio Astronomico di Palermo, Italy</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>陳俞融</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>104.11.14-104.12.13</t>
+          <t>104.11.15-104.11.20</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Koji Tsumura</t>
+          <t>Guillermo Manuel Munoz Caro</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>研究員</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
+          <t>Centro de Astrobiologi?a, DepartamentodeAstrofi?sica, Instituto Nacional de Te?cnica Aeroespacial, S</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳俞融</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>104.11.15-104.11.20</t>
+          <t>104.11.20-104.11.29</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Guillermo Manuel Munoz Caro</t>
+          <t>Donald A MacLaren</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>研究員</t>
+          <t>講師</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Centro de Astrobiologi?a, DepartamentodeAstrofi?sica, Instituto Nacional de Te?cnica Aeroespacial, S</t>
+          <t>University of Glasgow, UK</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>陳俞融</t>
+          <t>羅夢凡</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>104.11.20-104.11.29</t>
+          <t>104.11.22-104.11.28</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Donald A MacLaren</t>
+          <t>DZHU Shiwei</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>講師</t>
+          <t>博士後研究</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>University of Glasgow, UK</t>
+          <t>Nagoya University</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>羅夢凡</t>
+          <t>羅健榮</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>104.11.22-104.11.28</t>
+          <t>104.12.07-104.12.15</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>DZHU Shiwei</t>
+          <t>Masahiro Ibe</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>博士後研究</t>
+          <t>副教授</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nagoya University</t>
+          <t>University of Tokyo</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>羅健榮</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>104.12.07-104.12.15</t>
+          <t>104.12.20-104.12.31</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Masahiro Ibe</t>
+          <t>Toshinori Matsui</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>副教授</t>
+          <t>博士生</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>University of Tokyo</t>
+          <t>U. Toyama, Japan</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8318,14 +8284,14 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>104.12.20-104.12.31</t>
+          <t>105.01.03-105.01.05</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Toshinori Matsui</t>
+          <t>Mariko Kikuchi</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8352,34 +8318,34 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Mariko Kikuchi</t>
+          <t>Dong-Won Jung</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>博士生</t>
+          <t>研究員</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>U. Toyama, Japan</t>
+          <t>韓國KIAS</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>105.01.03-105.01.05</t>
+          <t>105.01.03-105.01.09</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Dong-Won Jung</t>
+          <t>Yonggun Jun</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8389,51 +8355,51 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>韓國KIAS</t>
+          <t>University of California at San Diego</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>105.01.03-105.01.09</t>
+          <t>105.01.05-105.01.31</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Yonggun Jun</t>
+          <t>Leonardo Mancini</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>研究員</t>
+          <t>博士生</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>University of California at San Diego</t>
+          <t>愛丁堡大學合成生物學與系統生物學中心</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>羅健榮</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>105.01.05-105.01.31</t>
+          <t>105.01.24-105.01.30</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Leonardo Mancini</t>
+          <t>Ekaterina Krasnopeeva</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8460,12 +8426,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ekaterina Krasnopeeva</t>
+          <t>Teuta Pilizota</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>博士生</t>
+          <t>助理教授</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -8487,17 +8453,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Teuta Pilizota</t>
+          <t>李穎星</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>博士生</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>愛丁堡大學合成生物學與系統生物學中心</t>
+          <t>北京大學生物動態光學成像中心</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -8514,7 +8480,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>李穎星</t>
+          <t>趙梓伊</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8541,12 +8507,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>趙梓伊</t>
+          <t>普穎穎</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>博士生</t>
+          <t>博士後研究</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -8568,12 +8534,12 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>普穎穎</t>
+          <t>白凡</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>博士後研究</t>
+          <t>副研究員</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -8595,71 +8561,71 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>白凡</t>
+          <t>Michel Nuevo</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>副研究員</t>
+          <t>研究員</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>北京大學生物動態光學成像中心</t>
+          <t>NASA Ames Research Center</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>羅健榮</t>
+          <t>陳俞融</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>105.01.24-105.01.30</t>
+          <t>105.02.24-105.02.26</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Michel Nuevo</t>
+          <t>Kaori Fuyuto</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>研究員</t>
+          <t>博士生</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NASA Ames Research Center</t>
+          <t>Nagoya University, Japan</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>陳俞融</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>105.02.24-105.02.26</t>
+          <t>105.02.25-105.03.13</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Kaori Fuyuto</t>
+          <t>Shinya Kanemura</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>博士生</t>
+          <t>副教授</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Nagoya University, Japan</t>
+          <t>U. Toyama, Japan</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -8669,19 +8635,19 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>105.02.25-105.03.13</t>
+          <t>105.03.24-105.03.31</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Shinya Kanemura</t>
+          <t>Mariko Kikuchi</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>副教授</t>
+          <t>博士生</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -8703,137 +8669,132 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Mariko Kikuchi</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>博士生</t>
+          <t>Nariya Uchida</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>助理教授</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>U. Toyama, Japan</t>
+          <t>東北大學物理系</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>溫偉源</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>105.03.24-105.03.31</t>
+          <t>105.02.29-105.03.02</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Nariya Uchida</t>
+          <t>Hirofumi Wada</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>助理教授</t>
+          <t>副教授</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>東北大學物理系</t>
+          <t>立命館大學物理系</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>溫偉源</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>105.02.29-105.03.02</t>
+          <t>105.03.17-105.03.19</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Hirofumi Wada</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>副教授</t>
+          <t>Hoang Thi Kieu Trang</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>立命館大學物理系</t>
+          <t>University of Science， National Vietnam University at Ho Chi Minh</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>105.03.17-105.03.19</t>
+          <t>104.09.02</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Hoang Thi Kieu Trang</t>
+          <t>葉芳</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>University of Science， National Vietnam University at Ho Chi Minh</t>
+          <t>University of Wisconsin at Madison</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>104.09.02</t>
+          <t>104.08.14-104.08.21</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>葉芳</t>
+          <t>Youichi Sakawa</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>University of Wisconsin at Madison</t>
+          <t>Osaka University</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>藏滿康浩</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>104.08.14-104.08.21</t>
+          <t>104.03.25-104.03.30</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Youichi Sakawa</t>
+          <t>Michel KOENIG</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Osaka University</t>
+          <t>法國CNRS</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -8843,85 +8804,85 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>104.03.25-104.03.30</t>
+          <t>104.09.13-104.09.20</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Michel KOENIG</t>
+          <t>馬曉光</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>法國CNRS</t>
+          <t>香港科技大學</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>藏滿康浩</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>104.09.13-104.09.20</t>
+          <t>104.06.22-104.06.27</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>馬曉光</t>
+          <t>Kaori Fuyuto</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>香港科技大學</t>
+          <t>Nagoya University, Japan</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>104.06.22-104.06.27</t>
+          <t>104.09.13-104.09.20</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Kaori Fuyuto</t>
+          <t>Ma. Carlota B. Decena 等14人</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nagoya University, Japan</t>
+          <t>菲律賓UST大學Department of Mathematics and Physics</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>羅夢凡</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>104.09.13-104.09.20</t>
+          <t>104.07.13</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Ma. Carlota B. Decena 等14人</t>
+          <t>鄭波等8人</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>菲律賓UST大學Department of Mathematics and Physics</t>
+          <t>浙江大學物理系</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -8931,41 +8892,41 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>104.07.13</t>
+          <t>104.06.20-104.06.26</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>鄭波等8人</t>
+          <t>華劍飛</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>浙江大學物理系</t>
+          <t>北京清華大學</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>羅夢凡</t>
+          <t>汪治平</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>104.06.20-104.06.26</t>
+          <t>104.07.20-104.08.30</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>華劍飛</t>
+          <t>張超杰 吳益鵬 郭博 程智 李飛 萬揚</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>北京清華大學</t>
+          <t>合作研究</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -8975,63 +8936,63 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>104.07.20-104.08.30</t>
+          <t>104.04.01-104.09.30</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>張超杰 吳益鵬 郭博 程智 李飛 萬揚</t>
+          <t>葉慶好</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>合作研究</t>
+          <t>上海交通大學</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>汪治平</t>
+          <t>易台生</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>104.04.01-104.09.30</t>
+          <t>102.10.01-102.10.04</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>葉慶好</t>
+          <t>Eung Jin Chun</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>上海交通大學</t>
+          <t>KIAS</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>易台生</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>102.10.01-102.10.04</t>
+          <t>103.12.28-104.01.03</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Eung Jin Chun</t>
+          <t>Koji Tsumura</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>KIAS</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9041,41 +9002,41 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>103.12.28-104.01.03</t>
+          <t>103.12.30-104.01.05</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Koji Tsumura</t>
+          <t>Prof. Lowen</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
+          <t>Institut f?r Theoretische Physik II - Soft Matter Heinrich-Heine-Universit?t D?sseldorf, Germany</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>103.12.30-104.01.05</t>
+          <t>103.11.24-103.11.28</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Prof. Lowen</t>
+          <t>Dr. Tatsuo Shibata</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Institut f?r Theoretische Physik II - Soft Matter Heinrich-Heine-Universit?t D?sseldorf, Germany</t>
+          <t>Laboratory head, Laboratory for Physical Biology, RIKEN Center for Developmental Biology, Japan</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -9092,29 +9053,29 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Dr. Tatsuo Shibata</t>
+          <t>Kentarou Tomita</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Laboratory head, Laboratory for Physical Biology, RIKEN Center for Developmental Biology, Japan</t>
+          <t>日本九州大學Kyushu University</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>藏滿康浩</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>103.11.24-103.11.28</t>
+          <t>103.10.15-103.10.18</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Kentarou Tomita</t>
+          <t>Shuichi Matsukiyo</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9136,29 +9097,29 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Shuichi Matsukiyo</t>
+          <t>Ong Yee Pin</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>日本九州大學Kyushu University</t>
+          <t>馬來西亞理科大學(Universiti Sains Malaysia）</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>藏滿康浩</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>103.10.15-103.10.18</t>
+          <t>103.10.02-103.10.30</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Ong Yee Pin</t>
+          <t>Soon Yee Yeen</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -9180,78 +9141,78 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Soon Yee Yeen</t>
+          <t>Koh Wee Shing</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>馬來西亞理科大學(Universiti Sains Malaysia）</t>
+          <t>Institute of High Performance Computing, Singapore</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>103.10.02-103.10.30</t>
+          <t>103.07.05-103.07.15</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Koh Wee Shing</t>
+          <t>MASAO IWAMATSU</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Institute of High Performance Computing, Singapore</t>
+          <t>Tokyo City University</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>103.07.05-103.07.15</t>
+          <t>103.01.11-103.01.14</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>MASAO IWAMATSU</t>
+          <t>Teuta Pilizota</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Tokyo City University</t>
+          <t>愛丁堡大學</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>羅健榮</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>103.01.11-103.01.14</t>
+          <t>103.02.09-103.03.01</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Teuta Pilizota</t>
+          <t>普穎穎</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>愛丁堡大學</t>
+          <t>北京大學</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -9261,63 +9222,63 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>103.02.09-103.03.01</t>
+          <t>103.02.25-103.03.22</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>普穎穎</t>
+          <t>徐寄遙</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>北京大學</t>
+          <t>中國科學院空間科學與應用研究中心</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>羅健榮</t>
+          <t>倪簡白</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>103.02.25-103.03.22</t>
+          <t>102.09.16-102.09.20</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>徐寄遙</t>
+          <t>Peter Kroll</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>中國科學院空間科學與應用研究中心</t>
+          <t>University of Wuppertal</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>倪簡白</t>
+          <t>陳鎰鋒</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>102.09.16-102.09.20</t>
+          <t>101.10.01-101.10.05</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Peter Kroll</t>
+          <t>Stanley J. Brodsky</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>University of Wuppertal</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -9334,188 +9295,188 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Stanley J. Brodsky</t>
+          <t>丁肇中</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Massachusetts Institute of Technology</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>陳鎰鋒</t>
+          <t>張元翰</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>101.10.01-101.10.05</t>
+          <t>100.08.07-100.08.12</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>丁肇中</t>
+          <t>Yongshang Han</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Massachusetts Institute of Technology</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>張元翰</t>
+          <t>林清誠</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>100.08.07-100.08.12</t>
+          <t>102.01.29</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Yongshang Han</t>
+          <t>Tung-Chang Liu</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Marland</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>林清誠</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>102.01.29</t>
+          <t>102.01.16</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Tung-Chang Liu</t>
+          <t>Yong Tang</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>University of Marland</t>
+          <t>國家理論科學研究中心</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>102.01.16</t>
+          <t>102.01.10</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Yong Tang</t>
+          <t>Plamen Ch Ivanov</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>國家理論科學研究中心</t>
+          <t>Boston University Physics</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>102.01.10</t>
+          <t>102.03.13-102.03.14</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Plamen Ch Ivanov</t>
+          <t>洪禮祺</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Boston University Physics</t>
+          <t>SUTT</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>102.03.13-102.03.14</t>
+          <t>102.03.05-102.03.07</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>洪禮祺</t>
+          <t>Alexander Mikhailov</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>SUTT</t>
+          <t>Fritz-Harber Institute</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>102.03.05-102.03.07</t>
+          <t>102.03.02-102.03.17</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Alexander Mikhailov</t>
+          <t>方向</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Fritz-Harber Institute</t>
+          <t>Kansas State University</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>102.03.02-102.03.17</t>
+          <t>100.10.26-101.02.29</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>Wei-Chi Yang</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Kansas State University</t>
+          <t>Radford University</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -9525,261 +9486,261 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>100.10.26-101.02.29</t>
+          <t>100.12.15-100.12.23</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Wei-Chi Yang</t>
+          <t>伍火熊</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Radford University</t>
+          <t>廈門大學</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>李明憶</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>100.12.15-100.12.23</t>
+          <t>100.12.24-101.01.13</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>伍火熊</t>
+          <t>Carsten Rott</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>廈門大學</t>
+          <t>The Ohio State University</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>李明憶</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>100.12.24-101.01.13</t>
+          <t>100.11.22-100.11.24</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Carsten Rott</t>
+          <t>Yoshitsugu Kabeya</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>The Ohio State University</t>
+          <t>Department of Mathematical Siences, Osaka Prefecture University, Japan</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳建隆</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>100.11.22-100.11.24</t>
+          <t>100.12.14-100.12.18</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Yoshitsugu Kabeya</t>
+          <t>Toshio Mikami</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Department of Mathematical Siences, Osaka Prefecture University, Japan</t>
+          <t>Osaka University</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>陳建隆</t>
+          <t>許順吉</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>100.12.14-100.12.18</t>
+          <t>100.11.21-100.11.26</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Toshio Mikami</t>
+          <t>Postdoc Neil Christensen</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Osaka University</t>
+          <t>Univ. of Pittsburgh</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>許順吉</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>100.11.21-100.11.26</t>
+          <t>101.02.15-101.02.28</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Postdoc Neil Christensen</t>
+          <t>Sagawa</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Univ. of Pittsburgh</t>
+          <t>Kyoto University</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>101.02.15-101.02.28</t>
+          <t>101.01.11-101.01.12</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sagawa</t>
+          <t>徐磊</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Kyoto University</t>
+          <t>香港中文大學</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>101.01.11-101.01.12</t>
+          <t>101.01.14-101.01.20</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>徐磊</t>
+          <t>Hidemitsu Wadade</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>香港中文大學</t>
+          <t>Waseda University</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳建隆</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>101.01.14-101.01.20</t>
+          <t>101.02.11-101.02.18</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Hidemitsu Wadade</t>
+          <t>韓永生</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Waseda University</t>
+          <t>University of Maryland USA</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>陳建隆</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>101.02.11-101.02.18</t>
+          <t>101.03.15-101.04.30</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>韓永生</t>
+          <t>Yuji Omura</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>University of Maryland USA</t>
+          <t>KIAS</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>101.03.15-101.04.30</t>
+          <t>101.01.08-101.01.20</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Yuji Omura</t>
+          <t>Mikhailov</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>KIAS</t>
+          <t>Fritz-Harber Institute</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>101.01.08-101.01.20</t>
+          <t>101.02.20-101.03.07</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Mikhailov</t>
+          <t>Wada Hirofumi</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Fritz-Harber Institute</t>
+          <t>University of Kyoto</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -9789,173 +9750,173 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>101.02.20-101.03.07</t>
+          <t>101.03.12-101.03.15</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Wada Hirofumi</t>
+          <t>Lim Thong Leng</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>University of Kyoto</t>
+          <t>Multimedia University</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>101.03.12-101.03.15</t>
+          <t>101.02.22-101.02.29</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Lim Thong Leng</t>
+          <t>Eiji Yanagidu</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Multimedia University</t>
+          <t>Tokyo Institute of Techology</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳建隆</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>101.02.22-101.02.29</t>
+          <t>101.02.17-101.02.24</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Eiji Yanagidu</t>
+          <t>T.Kawakatsu</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Tokyo Institute of Techology</t>
+          <t>Tohoku University</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>陳建隆</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>101.02.17-101.02.24</t>
+          <t>101.03.03-101.03.06</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>T.Kawakatsu</t>
+          <t>Naoyuki Ichihara</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Tohoku University</t>
+          <t>Hiroshima University</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>許順吉</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>101.03.03-101.03.06</t>
+          <t>101.03.15-101.03.25</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Naoyuki Ichihara</t>
+          <t>Akira Hasegawa</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Hiroshima University</t>
+          <t>Osaka University</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>許順吉</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>101.03.15-101.03.25</t>
+          <t>101.04.09-101.04.13</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Akira Hasegawa</t>
+          <t>K. Hoshino</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Osaka University</t>
+          <t>Hiroshima University</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>101.04.09-101.04.13</t>
+          <t>101.05.10-101.05.13</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>K. Hoshino</t>
+          <t>Niall O Morchadha</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Hiroshima University</t>
+          <t>University College Cork</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>101.05.10-101.05.13</t>
+          <t>101.06.06-101.06.09</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Niall O Morchadha</t>
+          <t>許祖斌</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>University College Cork</t>
+          <t>國立成功大學</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -9965,19 +9926,19 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>101.06.06-101.06.09</t>
+          <t>101.06.06</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>許祖斌</t>
+          <t>余海禮</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>國立成功大學</t>
+          <t>中研院</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -9994,56 +9955,56 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>余海禮</t>
+          <t>Arnaldo Rapallo</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>中研院</t>
+          <t>Istituto per lo Studio delle Macromelecole</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>101.06.06</t>
+          <t>101.11.01-101.11.30</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Arnaldo Rapallo</t>
+          <t>Wada</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Istituto per lo Studio delle Macromelecole</t>
+          <t>University of Kyoto</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>101.11.01-101.11.30</t>
+          <t>100.10.23-100.10.27</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Wada</t>
+          <t>Mikhailov</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>University of Kyoto</t>
+          <t>Fritz-Harber Institute</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -10053,29 +10014,29 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>100.10.23-100.10.27</t>
+          <t>100.11.19-100.12.05</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Mikhailov</t>
+          <t>Hiroaki Hata</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Fritz-Harber Institute</t>
+          <t>Shizuoka University</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>許順吉</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>100.11.19-100.12.05</t>
+          <t>100.08.20-100.09.04</t>
         </is>
       </c>
     </row>
@@ -10087,7 +10048,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Shizuoka University</t>
+          <t>Institute of High Performance Computing</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -10097,14 +10058,14 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>100.08.20-100.09.04</t>
+          <t>100.10.17-100.10.25</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Hiroaki Hata</t>
+          <t>許偉勳</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -10114,7 +10075,7 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>許順吉</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -10126,34 +10087,34 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>許偉勳</t>
+          <t>Hidemitsu Wadade</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Institute of High Performance Computing</t>
+          <t>Waseda University,</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>陳建隆</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>100.10.17-100.10.25</t>
+          <t>100.10.01-100.10.31</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Hidemitsu Wadade</t>
+          <t>Eiji Yanagidu</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Waseda University,</t>
+          <t>Tokyo Institute of Techology,</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -10163,80 +10124,80 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>100.10.01-100.10.31</t>
+          <t>100.09.01-100.09.04</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Eiji Yanagidu</t>
+          <t>烏蘭哈斯</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Tokyo Institute of Techology,</t>
+          <t>汕頭大學</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>陳建隆</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>100.09.01-100.09.04</t>
+          <t>100.09.01-100.10.05</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>烏蘭哈斯</t>
+          <t>Lee Hwee Kuan</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>汕頭大學</t>
+          <t>Bioinformatics Institute Singapore</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>100.09.01-100.10.05</t>
+          <t>100.09.18-100.09.20</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Lee Hwee Kuan</t>
+          <t>Sitabhra Sinha</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Bioinformatics Institute Singapore</t>
+          <t>The Institute of Mathematical Sciences</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>黎壁賢</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>100.09.18-100.09.20</t>
+          <t>100.07.25-100.07.29</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Sitabhra Sinha</t>
+          <t>W. K. Liu</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -10246,12 +10207,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>黎壁賢</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>100.07.25-100.07.29</t>
+          <t>100.07.14-100.07.20</t>
         </is>
       </c>
     </row>
@@ -10263,112 +10224,107 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>The Institute of Mathematical Sciences</t>
+          <t>University of Waterloo, Canada</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>100.07.14-100.07.20</t>
+          <t>100.08.05-100.08.06</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>W. K. Liu</t>
+          <t>Debajyoti Choudhury</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>University of Waterloo, Canada</t>
+          <t>University of Dehli</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>100.08.05-100.08.06</t>
+          <t>100.07.14-100.07.20</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Debajyoti Choudhury</t>
+          <t>Dinesh Thakur</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>University of Dehli</t>
+          <t>University of Arizona</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>數學系</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>100.07.14-100.07.20</t>
+          <t>100.07.04-100.07.08</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Dinesh Thakur</t>
+          <t>William T. Trotter</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>University of Arizona</t>
+          <t>Georgia Institute of Technology, School of Math</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>數學系</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>100.07.04-100.07.08</t>
+          <t>100.06.19-100.07.02</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>William T. Trotter</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>Georgia Institute of Technology, School of Math</t>
+          <t>Wai-Yee Keung</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>100.06.19-100.07.02</t>
+          <t>100.06.02-100.06.09</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Wai-Yee Keung</t>
+          <t>Danny Marfatia</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -10378,102 +10334,107 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>100.06.02-100.06.09</t>
+          <t>100.06.02-100.06.14</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Danny Marfatia</t>
+          <t>方向</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Kansas State University</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>數學系</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>100.06.02-100.06.14</t>
+          <t>100.06.01-100.07.31</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>方向</t>
+          <t>Naveen Gaur</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Kansas State University</t>
+          <t>Oehli, India</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>數學系</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>100.06.01-100.07.31</t>
+          <t>100.06.01-100.06.21</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Naveen Gaur</t>
+          <t>Yasushi Ishikawa</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Oehli, India</t>
+          <t>Ehime University</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>管理者</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>100.06.01-100.06.21</t>
+          <t>100.05.03-100.05.08</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Yasushi Ishikawa</t>
+          <t>李兵</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Ehime University</t>
+          <t>華南理工大學</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>管理者</t>
+          <t>許正雄</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>100.05.03-100.05.08</t>
+          <t>100.06.03-100.07.02</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>李兵</t>
+          <t>Xingfu Zou</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>華南理工大學</t>
+          <t>University of Western Ontario</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -10483,97 +10444,92 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>100.06.03-100.07.02</t>
+          <t>100.05.06-100.05.12</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Xingfu Zou</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>University of Western Ontario</t>
+          <t>韓永生</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>許正雄</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>100.05.06-100.05.12</t>
+          <t>100.03.15-100.05.01</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>韓永生</t>
+          <t>Sergey Ivanovich</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>Bastrukov</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>黎壁賢</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>100.03.15-100.05.01</t>
+          <t>100.04.10-100.06.01</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Sergey Ivanovich</t>
-        </is>
-      </c>
-      <c r="D216" t="inlineStr">
-        <is>
-          <t>Bastrukov</t>
+          <t>陳騮</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>黎壁賢</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>100.04.10-100.06.01</t>
+          <t>100.04.26-100.05.09</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>陳騮</t>
+          <t>Prof. Masao Doi</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>The University of Tokyo</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>黎壁賢</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>100.04.26-100.05.09</t>
+          <t>100.03.02-100.03.03</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Prof. Masao Doi</t>
-        </is>
-      </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>The University of Tokyo</t>
+          <t>陳俊仲(NCTS)</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
@@ -10583,273 +10539,278 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>100.03.02-100.03.03</t>
+          <t>100.02.24</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>陳俊仲(NCTS)</t>
+          <t>Jose-Lius Jaramillo</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>黎壁賢</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>100.02.24</t>
+          <t>100.02.15-100.02.20</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Jose-Lius Jaramillo</t>
+          <t>Mahesh M. Bandi</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>India(Harvard University)</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>100.02.15-100.02.20</t>
+          <t>100.02.23-100.03.02</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Mahesh M. Bandi</t>
+          <t>Alexander Mikhailov</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>India(Harvard University)</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>100.02.23-100.03.02</t>
+          <t>100.03.10-100.03.25</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Alexander Mikhailov</t>
+          <t>Jayanta K. Bhattacharjee</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳世宏</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>100.03.10-100.03.25</t>
+          <t>100.03.07-100.03.20</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Jayanta K. Bhattacharjee</t>
+          <t>Javier Duoandikoetxea</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>陳世宏</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>100.03.07-100.03.20</t>
+          <t>100.02.10-100.02.23</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Javier Duoandikoetxea</t>
+          <t>謝納慶</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>復旦大學</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>100.02.10-100.02.23</t>
+          <t>100.01.22-100.01.31</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>謝納慶</t>
+          <t>Hiroshi Endo</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>復旦大學</t>
+          <t>Tokyo University</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>100.01.22-100.01.31</t>
+          <t>100.09.26-100.09.27</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Hiroshi Endo</t>
+          <t>Krzysztof Stempak</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Tokyo University</t>
+          <t>Poland</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>100.09.26-100.09.27</t>
+          <t>100.01.09-100.01.28</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Krzysztof Stempak</t>
+          <t>謝納慶</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>復旦大學數學科學學院</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>James M. Nester</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>100.01.09-100.01.28</t>
+          <t>100.01.22-100.01.31</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>謝納慶</t>
+          <t>Krzysztof Stempak</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>復旦大學數學科學學院</t>
+          <t>Instytut Matematyki i Informatyki Politechnika Wroclawska,Poland</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>James M. Nester</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>100.01.22-100.01.31</t>
+          <t>099.01.09-099.01.29</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Krzysztof Stempak</t>
+          <t>江孟蓉</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Instytut Matematyki i Informatyki Politechnika Wroclawska,Poland</t>
+          <t>國立成功大學數學系</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>姚美琳</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>099.01.09-099.01.29</t>
+          <t>100.01.10-100.02.09</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>江孟蓉</t>
+          <t>Hailiang Liu</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>國立成功大學數學系</t>
+          <t>Iowa State University 數學系</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>姚美琳</t>
+          <t>洪盟凱</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>100.01.10-100.02.09</t>
+          <t>099.12.27-100.01.09</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Hailiang Liu</t>
+          <t>Jiahong Wu</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Iowa State University 數學系</t>
+          <t>Oklahoma State University 數學系</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -10859,195 +10820,195 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>099.12.27-100.01.09</t>
+          <t>099.12.15-100.12.28</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Jiahong Wu</t>
+          <t>楊瑋琦</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Oklahoma State University 數學系</t>
+          <t>Department of Mathematics and Statistics Radford University</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>洪盟凱</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>099.12.15-100.12.28</t>
+          <t>099.12.13-099.12.14</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>楊瑋琦</t>
+          <t>陳斌</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Department of Mathematics and Statistics Radford University</t>
+          <t>北京大學物理學院</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>099.12.13-099.12.14</t>
+          <t>099.12.12-099.12.21</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>陳斌</t>
+          <t>袁添亮</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>北京大學物理學院</t>
+          <t>檳城理科大學</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>099.12.12-099.12.21</t>
+          <t>099.11.20-099.11.25</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>袁添亮</t>
+          <t>Qingying Bu</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>檳城理科大學</t>
+          <t>University of Mississippi</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>王雅書</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>099.11.20-099.11.25</t>
+          <t>099.11.17-099.11.18</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Qingying Bu</t>
+          <t>Naoyuki Ichihara</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>University of Mississippi</t>
+          <t>Hiroshima University,Japan</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>王雅書</t>
+          <t>許順吉</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>099.11.17-099.11.18</t>
+          <t>099.09.21-099.12.21</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Naoyuki Ichihara</t>
+          <t>VO LUONG Hong Phuoc</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Hiroshima University,Japan</t>
+          <t>Physics Faculty in Ho Chi Minh University of Science</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>許順吉</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>099.09.21-099.12.21</t>
+          <t>099.09.25-099.09.26</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>VO LUONG Hong Phuoc</t>
+          <t>Gaber Younes Mohamed Faisel</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>Physics Faculty in Ho Chi Minh University of Science</t>
+          <t>Egyptian Center for Theoretical Physics,MTI Modern University,Egypt</t>
         </is>
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>099.09.25-099.09.26</t>
+          <t>099.09.13-099.10.12</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Gaber Younes Mohamed Faisel</t>
+          <t>Elliot Gilbert</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>Egyptian Center for Theoretical Physics,MTI Modern University,Egypt</t>
+          <t>澳洲ANSTO</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>李文献</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>099.09.13-099.10.12</t>
+          <t>096.11.07-096.11.11</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Elliot Gilbert</t>
+          <t>Jill Trewhella</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>澳洲ANSTO</t>
+          <t>澳洲USYD</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
@@ -11064,12 +11025,12 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Jill Trewhella</t>
+          <t>Chun Ken Loong</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>澳洲USYD</t>
+          <t>CSNS and CARR,China</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
@@ -11079,19 +11040,19 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>096.11.07-096.11.11</t>
+          <t>098.02.22-098.02.25</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>Chun Ken Loong</t>
+          <t>Kye Hong Lee</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>CSNS and CARR,China</t>
+          <t>韓國KAIST</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
@@ -11108,7 +11069,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Kye Hong Lee</t>
+          <t>Ki Bong Lee</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -11130,7 +11091,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Ki Bong Lee</t>
+          <t>Sung-Min Choi</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11152,7 +11113,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Sung-Min Choi</t>
+          <t>Mahn Won Kim</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -11174,12 +11135,12 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Mahn Won Kim</t>
+          <t>Brendan Kennedy</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>韓國KAIST</t>
+          <t>澳洲ANSTO</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
@@ -11196,7 +11157,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Brendan Kennedy</t>
+          <t>Rob Robinson</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11218,12 +11179,12 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Rob Robinson</t>
+          <t>John White</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>澳洲ANSTO</t>
+          <t>ANU, Australian</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
@@ -11240,12 +11201,12 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>John White</t>
+          <t>Yasuhiko Fujii</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>ANU, Australian</t>
+          <t>日本JAEA</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
@@ -11262,12 +11223,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Yasuhiko Fujii</t>
+          <t>Kazuyoshi Yamada</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>日本JAEA</t>
+          <t>Tohoku University, Japan</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
@@ -11284,12 +11245,12 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Kazuyoshi Yamada</t>
+          <t>Masatoshi Arai</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>Tohoku University, Japan</t>
+          <t>日本JAEA</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
@@ -11306,12 +11267,12 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Masatoshi Arai</t>
+          <t>Jiri Kulda</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>日本JAEA</t>
+          <t>歐洲ILL</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -11321,19 +11282,19 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>098.02.22-098.02.25</t>
+          <t>096.06.06-096.06.13</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Jiri Kulda</t>
+          <t>Kazu Kakurai</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>歐洲ILL</t>
+          <t>日本JAERI</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -11350,12 +11311,12 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Kazu Kakurai</t>
+          <t>Wiels Christensen</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>日本JAERI</t>
+          <t>PSI, Sweden</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
@@ -11372,12 +11333,12 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Wiels Christensen</t>
+          <t>Jeffrey Lynn</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>PSI, Sweden</t>
+          <t>美國NIST</t>
         </is>
       </c>
       <c r="E255" t="inlineStr">
@@ -11394,12 +11355,12 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Jeffrey Lynn</t>
+          <t>Elliot Gilbert</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>美國NIST</t>
+          <t>澳洲ANSTO</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -11416,7 +11377,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Elliot Gilbert</t>
+          <t>Michael James</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -11438,7 +11399,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Michael James</t>
+          <t>Don Kearley</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -11460,7 +11421,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Don Kearley</t>
+          <t>Mohana Yethiraj</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -11482,7 +11443,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Mohana Yethiraj</t>
+          <t>Shane Kennedy</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -11504,7 +11465,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Shane Kennedy</t>
+          <t>Robert Robinson</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -11526,34 +11487,34 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Robert Robinson</t>
+          <t>束立生</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>澳洲ANSTO</t>
+          <t>安徽師範大學</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>李文献</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>096.06.06-096.06.13</t>
+          <t>099.07.09-099.07.22</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>束立生</t>
+          <t>Kazo Yabuta</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>安徽師範大學</t>
+          <t>Kwansei Gakuin university</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
@@ -11563,19 +11524,19 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>099.07.09-099.07.22</t>
+          <t>099.07.11-099.07.16</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Kazo Yabuta</t>
+          <t>Marcin Bownik</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>Kwansei Gakuin university</t>
+          <t>University of Oregon</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
@@ -11592,12 +11553,12 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Marcin Bownik</t>
+          <t>韓永生</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>University of Oregon</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
@@ -11607,19 +11568,19 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>099.07.11-099.07.16</t>
+          <t>099.07.05-099.08.07</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>韓永生</t>
+          <t>Jong-Guk Bak</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>Pohang University of Science and Technology</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -11629,217 +11590,217 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>099.07.05-099.08.07</t>
+          <t>099.07.05-099.07.09</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Jong-Guk Bak</t>
+          <t>黃建平</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>Pohang University of Science and Technology</t>
+          <t>中國蘭州大學</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>倪簡白</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>099.07.05-099.07.09</t>
+          <t>099.06.21-099.06.26</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>黃建平</t>
+          <t>洪理祺</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>中國蘭州大學</t>
+          <t>新加坡南洋理工大學</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>倪簡白</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>099.06.21-099.06.26</t>
+          <t>099.06.10-099.06.17</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>洪理祺</t>
+          <t>Chau Van Tao</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>新加坡南洋理工大學</t>
+          <t>University of Science at Ho Chi Minh</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>099.06.10-099.06.17</t>
+          <t>099.06.20-099.06.24</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Chau Van Tao</t>
+          <t>Douglas D. Osheroff</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>University of Science at Ho Chi Minh</t>
+          <t>Stanford University</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>099.06.20-099.06.24</t>
+          <t>099.06.05-099.06.11</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Douglas D. Osheroff</t>
+          <t>Alexander S. Mikhailov</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>Stanford University</t>
+          <t>Fritz-Haber-Institut der Max-Planck-Gesellschaft</t>
         </is>
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>099.06.05-099.06.11</t>
+          <t>099.05.18-099.05.20</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Alexander S. Mikhailov</t>
+          <t>楊義清</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>Fritz-Haber-Institut der Max-Planck-Gesellschaft</t>
+          <t>台東大學</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>099.05.18-099.05.20</t>
+          <t>099.04.18-099.04.20</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>楊義清</t>
+          <t>李躍先</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>台東大學</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>099.04.18-099.04.20</t>
+          <t>099.04.11-099.04.17</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>李躍先</t>
+          <t>Padma-Kent-Shukla</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>德國魯爾大學</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>伊林</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>099.04.11-099.04.17</t>
+          <t>098.12.06-098.12.12</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Padma-Kent-Shukla</t>
+          <t>喀蔚波</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>德國魯爾大學</t>
+          <t>北京大學</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>伊林</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>098.12.06-098.12.12</t>
+          <t>099.03.19-099.03.30</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>喀蔚波</t>
+          <t>喀興林</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>北京大學</t>
+          <t>北京師範大學</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
@@ -11856,12 +11817,12 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>喀興林</t>
+          <t>趙凱華</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>北京師範大學</t>
+          <t>北京大學</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
@@ -11878,7 +11839,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>趙凱華</t>
+          <t>吳思誠</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -11900,7 +11861,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>吳思誠</t>
+          <t>秦克誠</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -11922,56 +11883,56 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>秦克誠</t>
+          <t>Maurice van Putten</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>北京大學</t>
+          <t>Le Studium IAS, Orleans, France</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>099.03.19-099.03.30</t>
+          <t>099.03.03-099.03.04</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Maurice van Putten</t>
+          <t>Jonathan Rosner</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>Le Studium IAS, Orleans, France</t>
+          <t>University of Chicago</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>099.03.03-099.03.04</t>
+          <t>099.04.06-099.04.16</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Jonathan Rosner</t>
+          <t>Chris Quigg</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>University of Chicago</t>
+          <t>Fermilab, USA</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
@@ -11981,151 +11942,151 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>099.04.06-099.04.16</t>
+          <t>099.03.28-099.03.29</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Chris Quigg</t>
+          <t>韓永生</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>Fermilab, USA</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>099.03.28-099.03.29</t>
+          <t>099.03.14-099.05.01</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>韓永生</t>
+          <t>Mario Liu</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Tubingen</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>099.03.14-099.05.01</t>
+          <t>099.02.22-099.03.22</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Mario Liu</t>
+          <t>伍火熊</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>University of Tubingen</t>
+          <t>廈門大學</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>李明憶</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>099.02.22-099.03.22</t>
+          <t>098.12.18-098.12.25</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>伍火熊</t>
+          <t>Myoung Chu Oh</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>廈門大學</t>
+          <t>University of Seoul</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>李明憶</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>098.12.18-098.12.25</t>
+          <t>098.12.24-099.01.13</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Myoung Chu Oh</t>
+          <t>許偉勳</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>University of Seoul</t>
+          <t>Institute of High Performance Computing</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>098.12.24-099.01.13</t>
+          <t>098.11.08-098.11.14</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>許偉勳</t>
+          <t>宋偉</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>Institute of High Performance Computing</t>
+          <t>哈佛大學</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>098.11.08-098.11.14</t>
+          <t>098.12.14-098.12.26</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>宋偉</t>
+          <t>Hong Lu</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>哈佛大學</t>
+          <t>China Institute of Advanced Study</t>
         </is>
       </c>
       <c r="E289" t="inlineStr">
@@ -12135,19 +12096,19 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>098.12.14-098.12.26</t>
+          <t>098.10.05-098.10.06</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Hong Lu</t>
+          <t>龐大偉</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>China Institute of Advanced Study</t>
+          <t>Sogan University</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -12157,63 +12118,63 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>098.10.05-098.10.06</t>
+          <t>098.10.18-098.11.01</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>龐大偉</t>
+          <t>Jiahong Wu</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>Sogan University</t>
+          <t>Oklahoma State University</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>洪盟凱</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>098.10.18-098.11.01</t>
+          <t>098.08.05-098.08.11</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Jiahong Wu</t>
+          <t>江惠坤</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>Oklahoma State University</t>
+          <t>南京大學數學系</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>洪盟凱</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>098.08.05-098.08.11</t>
+          <t>098.07.01-098.07.31</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>江惠坤</t>
+          <t>蕭杰</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>南京大學數學系</t>
+          <t>Memorial University of Newfoundland</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
@@ -12223,195 +12184,195 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>098.07.01-098.07.31</t>
+          <t>098.06.21-098.06.28</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>蕭杰</t>
+          <t>費少明</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>Memorial University of Newfoundland</t>
+          <t>首都師範大學數學系</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>098.06.21-098.06.28</t>
+          <t>097.10.28-097.10.29</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>費少明</t>
+          <t>王曉鋼</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>首都師範大學數學系</t>
+          <t>北京大學</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>陳培亮</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>097.10.28-097.10.29</t>
+          <t>098.08.10-098.08.22</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>王曉鋼</t>
+          <t>Martin Zuckermann</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>北京大學</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>陳培亮</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>098.08.10-098.08.22</t>
+          <t>098.07.10-098.07.31</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Martin Zuckermann</t>
+          <t>C. Y. R. Wu</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>University of Southern California</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>易台生</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>098.07.10-098.07.31</t>
+          <t>098.03.24</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>C. Y. R. Wu</t>
+          <t>Ziyou Li</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>University of Southern California</t>
+          <t>英國University of Birmingham</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>易台生</t>
+          <t>羅夢凡</t>
         </is>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>098.03.24</t>
+          <t>098.05.07-098.05.14</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>Ziyou Li</t>
+          <t>陳騮</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>英國University of Birmingham</t>
+          <t>Dept. of Physics &amp; Astronomy, University of California, Irvine</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>羅夢凡</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>098.05.07-098.05.14</t>
+          <t>098.04.27-098.05.07</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>陳騮</t>
+          <t>韓永生</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
         <is>
-          <t>Dept. of Physics &amp; Astronomy, University of California, Irvine</t>
+          <t>Auburn University</t>
         </is>
       </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>098.04.27-098.05.07</t>
+          <t>098.03.15-098.05.31</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>韓永生</t>
+          <t>Friedrich Hehl</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>Auburn University</t>
+          <t>University of Cologne</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>098.03.15-098.05.31</t>
+          <t>098.03.12-098.04.04</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Friedrich Hehl</t>
+          <t>白姍</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>University of Cologne</t>
+          <t>中國科學院</t>
         </is>
       </c>
       <c r="E302" t="inlineStr">
@@ -12421,283 +12382,283 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>098.03.12-098.04.04</t>
+          <t>098.03.17-098.03.22</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>白姍</t>
+          <t>Doochul Kim</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
         <is>
-          <t>中國科學院</t>
+          <t>National Seoul University</t>
         </is>
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>098.03.17-098.03.22</t>
+          <t>098.03.01-098.03.09</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Doochul Kim</t>
+          <t>江府峻</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>National Seoul University</t>
+          <t>Bern University</t>
         </is>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>098.03.01-098.03.09</t>
+          <t>098.02.23-098.02.24</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>江府峻</t>
+          <t>李躍先</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
         <is>
-          <t>Bern University</t>
+          <t>University of British Columbia</t>
         </is>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>098.02.23-098.02.24</t>
+          <t>098.01.15-098.01.18</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>李躍先</t>
+          <t>陳隆基</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
         <is>
-          <t>University of British Columbia</t>
+          <t>Oregon State University</t>
         </is>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>098.01.15-098.01.18</t>
+          <t>097.12.18-097.12.26</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>陳隆基</t>
+          <t>Christopher-B.-Gorman</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Oregon State University</t>
+          <t>North Carolina State University, Raleigh, NC USA</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>羅夢凡</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>097.12.18-097.12.26</t>
+          <t>097.10.19-097.10.24</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Christopher-B.-Gorman</t>
+          <t>Wax Jean-Francois</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
         <is>
-          <t>North Carolina State University, Raleigh, NC USA</t>
+          <t>University of Metz</t>
         </is>
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>羅夢凡</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>097.10.19-097.10.24</t>
+          <t>097.11.25-097.12.24</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Wax Jean-Francois</t>
+          <t>Seungwon Baek</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
         <is>
-          <t>University of Metz</t>
+          <t>Korea University</t>
         </is>
       </c>
       <c r="E309" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>097.11.25-097.12.24</t>
+          <t>097.08.17-097.08.31</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Seungwon Baek</t>
+          <t>于秋明</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>Korea University</t>
+          <t>美國華盛頓大學</t>
         </is>
       </c>
       <c r="E310" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>097.08.17-097.08.31</t>
+          <t>097.08.01-097.08.05</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>于秋明</t>
+          <t>I&amp;ntilde;aki Garay</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>美國華盛頓大學</t>
+          <t>Universidad Autonoma de Madrid</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>097.08.01-097.08.05</t>
+          <t>097.07.04-097.07.07</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>I&amp;ntilde;aki Garay</t>
+          <t>許祖斌</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Universidad Autonoma de Madrid</t>
+          <t>國立成功大學</t>
         </is>
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>聶斯特</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>097.07.04-097.07.07</t>
+          <t>097.06.24-097.06.27</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>許祖斌</t>
+          <t>Michael Ramsey-Musolf</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>國立成功大學</t>
+          <t>美國威斯康辛大學</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>聶斯特</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>097.06.24-097.06.27</t>
+          <t>097.06.23-097.06.25</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Michael Ramsey-Musolf</t>
+          <t>姜偉宜</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>美國威斯康辛大學</t>
+          <t>美國伊利諾大學</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>097.06.23-097.06.25</t>
+          <t>097.06.11-097.06.13</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>姜偉宜</t>
+          <t>曹周鍵</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
         <is>
-          <t>美國伊利諾大學</t>
+          <t>中國科學院</t>
         </is>
       </c>
       <c r="E315" t="inlineStr">
@@ -12707,41 +12668,41 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>097.06.11-097.06.13</t>
+          <t>097.05.26-097.05.27</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>曹周鍵</t>
+          <t>Yohannes Shiferaw</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
         <is>
-          <t>中國科學院</t>
+          <t>Dept. of Physics and Astronomy, California State University, Northridge</t>
         </is>
       </c>
       <c r="E316" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>陳仕宏</t>
         </is>
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>097.05.26-097.05.27</t>
+          <t>097.05.26-097.05.31</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Yohannes Shiferaw</t>
+          <t>Peter Messmer</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
         <is>
-          <t>Dept. of Physics and Astronomy, California State University, Northridge</t>
+          <t>Space Applications Group, Tech-X Corporation, Boulder, CO, USA</t>
         </is>
       </c>
       <c r="E317" t="inlineStr">
@@ -12751,19 +12712,19 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>097.05.26-097.05.31</t>
+          <t>097.05.18-097.05.23</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Peter Messmer</t>
+          <t>許偉勳</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Space Applications Group, Tech-X Corporation, Boulder, CO, USA</t>
+          <t>Institute of High Performance Computing</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -12773,41 +12734,41 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>097.05.18-097.05.23</t>
+          <t>097.05.17-097.05.31</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>許偉勳</t>
+          <t>許人丰</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>Institute of High Performance Computing</t>
+          <t>中研院物理所</t>
         </is>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>陳仕宏</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>097.05.17-097.05.31</t>
+          <t>097.05.12-097.05.16</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>許人丰</t>
+          <t>Dang Van Soa</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>中研院物理所</t>
+          <t>Hanoi University of Education</t>
         </is>
       </c>
       <c r="E320" t="inlineStr">
@@ -12817,151 +12778,151 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>097.05.12-097.05.16</t>
+          <t>097.04.10-097.06.10</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Dang Van Soa</t>
+          <t>Hyun-Seok Yang</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>Hanoi University of Education</t>
+          <t>KIAS</t>
         </is>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>097.04.10-097.06.10</t>
+          <t>097.04.21-097.05.03</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Hyun-Seok Yang</t>
+          <t>L&amp;aacute;szl&amp;oacute; Ben&amp;ouml; Szabados</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>KIAS</t>
+          <t>Research Institute for Particle and Nuclear Physics of Hungarian Academy of Sciences</t>
         </is>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>聶斯特</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>097.04.21-097.05.03</t>
+          <t>097.04.10-097.04.27</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>L&amp;aacute;szl&amp;oacute; Ben&amp;ouml; Szabados</t>
+          <t>陳騮</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Research Institute for Particle and Nuclear Physics of Hungarian Academy of Sciences</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>聶斯特</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>097.04.10-097.04.27</t>
+          <t>097.03.30-097.04.06</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>陳騮</t>
+          <t>christ Green</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>JILA</t>
         </is>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>倪簡白</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>097.03.30-097.04.06</t>
+          <t>097.05.14</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>christ Green</t>
+          <t>Chung Yung Wu</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
         <is>
-          <t>JILA</t>
+          <t>University of Southern California, USA</t>
         </is>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>倪簡白</t>
+          <t>易台生</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>097.05.14</t>
+          <t>097.03.24-097.04.26</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Chung Yung Wu</t>
+          <t>Hyoung-Jin Choi</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
         <is>
-          <t>University of Southern California, USA</t>
+          <t>Inha University</t>
         </is>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>易台生</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>097.03.24-097.04.26</t>
+          <t>097.03.18-097.03.19</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Hyoung-Jin Choi</t>
+          <t>禹東川</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Inha University</t>
+          <t>青島大學</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
@@ -12971,107 +12932,107 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>097.03.18-097.03.19</t>
+          <t>096.08.01-096.10.27</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>禹東川</t>
+          <t>C.-P.Yuan</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>青島大學</t>
+          <t>Department of Physics and Astronomy, Michigan State University, U.S.A.</t>
         </is>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>096.08.01-096.10.27</t>
+          <t>096.07.27-096.07.28</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>C.-P.Yuan</t>
+          <t>Gary Shiu</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Department of Physics and Astronomy, Michigan State University, U.S.A.</t>
+          <t>Department of Physics,Universiy of Wisconsin at Madison</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>096.07.27-096.07.28</t>
+          <t>096.04.04-096.04.05</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Gary Shiu</t>
+          <t>Toshiaki Tanaka</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>Department of Physics,Universiy of Wisconsin at Madison</t>
+          <t>NCTS; Department of Physics,National Cheng-Kung University</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>096.04.04-096.04.05</t>
+          <t>095.12.12-095.12.13</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Toshiaki Tanaka</t>
+          <t>陳智泓</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>NCTS; Department of Physics,National Cheng-Kung University</t>
+          <t>東京大學</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>陳培亮</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>095.12.12-095.12.13</t>
+          <t>097.03.06</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>陳智泓</t>
+          <t>Kingshuk Ghosh</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>東京大學</t>
+          <t>加州大學</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
@@ -13081,19 +13042,19 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>097.03.06</t>
+          <t>097.02.24-097.02.27</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Kingshuk Ghosh</t>
+          <t>羅健榮</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>加州大學</t>
+          <t>牛津大學</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
@@ -13103,19 +13064,19 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>097.02.24-097.02.27</t>
+          <t>097.02.21</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>羅健榮</t>
+          <t>吳國安</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>牛津大學</t>
+          <t>西北大學</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
@@ -13125,278 +13086,278 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>097.02.21</t>
+          <t>097.02.20</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>吳國安</t>
+          <t>Takao Ohta</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>西北大學</t>
+          <t>京都大學</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>陳培亮</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>097.02.20</t>
+          <t>097.02.18-097.02.20</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Takao Ohta</t>
+          <t>Shengpang Zhang, Gordon Shepherd</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>京都大學</t>
+          <t>York University, Canada</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>倪簡白</t>
         </is>
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>097.02.18-097.02.20</t>
+          <t>096.09-096.12</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Shengpang Zhang, Gordon Shepherd</t>
+          <t>Christopher C. Bernido</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>York University, Canada</t>
+          <t>Central Visayan Institute Foundation</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>倪簡白</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>096.09-096.12</t>
+          <t>097.01.27-097.02.03</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Christopher C. Bernido</t>
+          <t>Yeong Gyun Kim</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Central Visayan Institute Foundation</t>
+          <t>KAIST</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>李在植</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>097.01.27-097.02.03</t>
+          <t>097.01.21-097.01.27</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Yeong Gyun Kim</t>
+          <t>Giacomo Polesello</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>KAIST</t>
+          <t>ATLAS</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>李在植</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>097.01.21-097.01.27</t>
+          <t>097.01.13-097.01.19</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Giacomo Polesello</t>
+          <t>Marko Djordjevic</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>ATLAS</t>
+          <t>Mathematical Biosciences Institute, The Ohio State University</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>陳培亮</t>
         </is>
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>097.01.13-097.01.19</t>
+          <t>097.01.09-097.01.12</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Marko Djordjevic</t>
+          <t>周宇峰</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Mathematical Biosciences Institute, The Ohio State University</t>
+          <t>KIAS</t>
         </is>
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>陳培亮</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>097.01.09-097.01.12</t>
+          <t>096.12.24-097.01.12</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>周宇峰</t>
+          <t>Ho-Ung Yee</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>KIAS</t>
+          <t>Abdus Salam International Center for Theoretical Physics</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>096.12.24-097.01.12</t>
+          <t>096.12.24-096.12.29</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Ho-Ung Yee</t>
+          <t>Masao Iwamatsu</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Abdus Salam International Center for Theoretical Physics</t>
+          <t>Musashi Institute of Technology</t>
         </is>
       </c>
       <c r="E343" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>賴山強</t>
         </is>
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>096.12.24-096.12.29</t>
+          <t>096.12.21-096.12.26</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Masao Iwamatsu</t>
+          <t>成田誠</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Musashi Institute of Technology</t>
+          <t>台灣大學</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>賴山強</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>096.12.21-096.12.26</t>
+          <t>096.12.18-096.12.25</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>成田誠</t>
+          <t>杜蕙慈</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>台灣大學</t>
+          <t>University of California, Irvine, USA</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>096.12.18-096.12.25</t>
+          <t>096.12.17-096.12.18</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>杜蕙慈</t>
+          <t>Moira L. Steyn-Ross</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>University of California, Irvine, USA</t>
+          <t>University of Waikato</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>096.12.17-096.12.18</t>
+          <t>096.12.07-096.12.18</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Moira L. Steyn-Ross</t>
+          <t>D. Alistair Steyn-Ross</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -13418,342 +13379,342 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>D. Alistair Steyn-Ross</t>
+          <t>Toshifumi Yamashita</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>University of Waikato</t>
+          <t>Osaka University</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>096.12.07-096.12.18</t>
+          <t>096.12.02-096.12.09</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Toshifumi Yamashita</t>
+          <t>Jae-Sik Lee</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
         <is>
-          <t>Osaka University</t>
+          <t>KEK</t>
         </is>
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>096.12.02-096.12.09</t>
+          <t>096.12.01-096.12.09</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Jae-Sik Lee</t>
+          <t>Nobuhito Maru</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>KEK</t>
+          <t>Kobe University</t>
         </is>
       </c>
       <c r="E350" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>096.12.01-096.12.09</t>
+          <t>096.12.02-096.12.07</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Nobuhito Maru</t>
+          <t>Gordon G. Shepherd</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Kobe University</t>
+          <t>York University., Canada</t>
         </is>
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>倪簡白</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>096.12.02-096.12.07</t>
+          <t>096.11.18-096.11.25</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Gordon G. Shepherd</t>
+          <t>李元斌</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>York University., Canada</t>
+          <t>Department of Mathematics, University of Utah</t>
         </is>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>倪簡白</t>
+          <t>王金龍</t>
         </is>
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>096.11.18-096.11.25</t>
+          <t>096.11.19-096.12.09</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>李元斌</t>
+          <t>Stefano Scopel</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
         <is>
-          <t>Department of Mathematics, University of Utah</t>
+          <t>Korea Institute of Advanced Study (KIAS)</t>
         </is>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>王金龍</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>096.11.19-096.12.09</t>
+          <t>096.11.12-096.11.24</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Stefano Scopel</t>
+          <t>王昆湶</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Korea Institute of Advanced Study (KIAS)</t>
+          <t>花蓮教育大學</t>
         </is>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>096.11.12-096.11.24</t>
+          <t>096.08.21-096.09.20</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>王昆湶</t>
+          <t>陳騮</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>花蓮教育大學</t>
+          <t>University of California, Irvine</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>096.08.21-096.09.20</t>
+          <t>096.09.12-096.09.18</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>陳騮</t>
+          <t>Takashi Torii</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>University of California, Irvine</t>
+          <t>大阪工業大學</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>096.09.12-096.09.18</t>
+          <t>096.09.10-096.09.12</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Takashi Torii</t>
+          <t>南樹鉉</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>大阪工業大學</t>
+          <t>成功大學</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>096.09.10-096.09.12</t>
+          <t>096.08.13-096.08.14</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>南樹鉉</t>
+          <t>劉芳</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>成功大學</t>
+          <t>青島大學</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>096.08.13-096.08.14</t>
+          <t>096.08.01-096.10.27</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>劉芳</t>
+          <t>Tetsuo Shindou</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
         <is>
-          <t>青島大學</t>
+          <t>SISSA</t>
         </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>096.08.01-096.10.27</t>
+          <t>096.07.28-096.08.03</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Tetsuo Shindou</t>
+          <t>陳騮</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
         <is>
-          <t>SISSA</t>
+          <t>Dept. of Physics &amp; Astronomy, University of California, Irvine</t>
         </is>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>林留玉仁</t>
         </is>
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>096.07.28-096.08.03</t>
+          <t>096.07.02-096.07.03</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>陳騮</t>
+          <t>Hyoung-Jin Choi</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>Dept. of Physics &amp; Astronomy, University of California, Irvine</t>
+          <t>Department of Polymer Science and Engineering</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>林留玉仁</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>096.07.02-096.07.03</t>
+          <t>096.05.24-096.05.25</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Hyoung-Jin Choi</t>
+          <t>王志偉</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Department of Polymer Science and Engineering</t>
+          <t>University of South California</t>
         </is>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>096.05.24-096.05.25</t>
+          <t>096.11.01-096.12.31</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>王志偉</t>
+          <t>Akihiro Ishibashi</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>University of South California</t>
+          <t>KEK</t>
         </is>
       </c>
       <c r="E363" t="inlineStr">
@@ -13763,41 +13724,41 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>096.11.01-096.12.31</t>
+          <t>096.10.18-096.11.03</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Akihiro Ishibashi</t>
+          <t>Dong-Won Jung</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>KEK</t>
+          <t>Korea Institute for Advanced Study School of Physics</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>096.10.18-096.11.03</t>
+          <t>096.06.11-096.06.23</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Dong-Won Jung</t>
+          <t>C.N. Leung</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Korea Institute for Advanced Study School of Physics</t>
+          <t>Univ. of Delaware</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
@@ -13807,19 +13768,19 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>096.06.11-096.06.23</t>
+          <t>093</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>C.N. Leung</t>
+          <t>Bei-Lok Hu</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
         <is>
-          <t>Univ. of Delaware</t>
+          <t>Univ. of Maryland</t>
         </is>
       </c>
       <c r="E366" t="inlineStr">
@@ -13829,19 +13790,19 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>093</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Bei-Lok Hu</t>
+          <t>Pran Nath</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
         <is>
-          <t>Univ. of Maryland</t>
+          <t>Northeastern Univ.</t>
         </is>
       </c>
       <c r="E367" t="inlineStr">
@@ -13851,19 +13812,19 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>091</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Pran Nath</t>
+          <t>Kaoru Hagiwara</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
         <is>
-          <t>Northeastern Univ.</t>
+          <t>KEK Theory Group</t>
         </is>
       </c>
       <c r="E368" t="inlineStr">
@@ -13880,12 +13841,12 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Kaoru Hagiwara</t>
+          <t>Jonathan Feng</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>KEK Theory Group</t>
+          <t>Mass. Inst. of Tech.</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -13902,144 +13863,144 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Jonathan Feng</t>
+          <t>童若軒</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Mass. Inst. of Tech.</t>
+          <t>上海師範大學</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>聶斯特</t>
         </is>
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>091</t>
+          <t>096.05.07-096.05.27</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>童若軒</t>
+          <t>Jenifer Thewalt</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>上海師範大學</t>
+          <t>Depts. of Molecular Biology &amp; Biochemistry and Physics, Simon Fraser University</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
         <is>
-          <t>聶斯特</t>
+          <t>薛雅薇</t>
         </is>
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>096.05.07-096.05.27</t>
+          <t>096.05.04-096.05.11</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Jenifer Thewalt</t>
+          <t>Kenjiro Yanagi</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Depts. of Molecular Biology &amp; Biochemistry and Physics, Simon Fraser University</t>
+          <t>Yamaguchi University</t>
         </is>
       </c>
       <c r="E372" t="inlineStr">
         <is>
-          <t>薛雅薇</t>
+          <t>趙一峰</t>
         </is>
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>096.05.04-096.05.11</t>
+          <t>096.06.04-096.06.06</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Kenjiro Yanagi</t>
+          <t>李志光</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Yamaguchi University</t>
+          <t>Department of Mathematics, College of William &amp; Mary</t>
         </is>
       </c>
       <c r="E373" t="inlineStr">
         <is>
-          <t>趙一峰</t>
+          <t>高華隆</t>
         </is>
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>096.06.04-096.06.06</t>
+          <t>096.04.15-096.04.21</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>李志光</t>
+          <t>Baohua Fu</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>Department of Mathematics, College of William &amp; Mary</t>
+          <t>法國CNRS</t>
         </is>
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>高華隆</t>
+          <t>王金龍</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>096.04.15-096.04.21</t>
+          <t>096.04.02-096.04.08</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Baohua Fu</t>
+          <t>燕敦驗</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>法國CNRS</t>
+          <t>中國科學院</t>
         </is>
       </c>
       <c r="E375" t="inlineStr">
         <is>
-          <t>王金龍</t>
+          <t>林欽誠</t>
         </is>
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>096.04.02-096.04.08</t>
+          <t>096.05.18-096.06.16</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>燕敦驗</t>
+          <t>Ahmad Al-Salman</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>中國科學院</t>
+          <t>Yarmouk University, Jordan</t>
         </is>
       </c>
       <c r="E376" t="inlineStr">
@@ -14049,85 +14010,85 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>096.05.18-096.06.16</t>
+          <t>096.01.25-096.02.03</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Ahmad Al-Salman</t>
+          <t>Joseph H. Silverman</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Yarmouk University, Jordan</t>
+          <t>Brown University,U.S.A.</t>
         </is>
       </c>
       <c r="E377" t="inlineStr">
         <is>
-          <t>林欽誠</t>
+          <t>夏良忠</t>
         </is>
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>096.01.25-096.02.03</t>
+          <t>095.10.23-095.10.28</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Joseph H. Silverman</t>
+          <t>Yasuhiro Okada</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Brown University,U.S.A.</t>
+          <t>KEK</t>
         </is>
       </c>
       <c r="E378" t="inlineStr">
         <is>
-          <t>夏良忠</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>095.10.23-095.10.28</t>
+          <t>096.03.29-096.03.31</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Yasuhiro Okada</t>
+          <t>Mizumoto, Ohishi</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>KEK</t>
+          <t>日本國家天文台</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>高仲明</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>096.03.29-096.03.31</t>
+          <t>094.06</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>Mizumoto, Ohishi</t>
+          <t>Prof. Vladimir Dogiel</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>日本國家天文台</t>
+          <t>P.N. Lebedev Physical Institute, Russian Academy of Sciences</t>
         </is>
       </c>
       <c r="E380" t="inlineStr">
@@ -14137,7 +14098,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>094.06</t>
+          <t>095.01.04</t>
         </is>
       </c>
     </row>
@@ -14159,41 +14120,41 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>095.01.04</t>
+          <t>092.11.05-093.02.15</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Prof. Vladimir Dogiel</t>
+          <t>Ikaros Bigi</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>P.N. Lebedev Physical Institute, Russian Academy of Sciences</t>
+          <t>Notre Dame Univ.</t>
         </is>
       </c>
       <c r="E382" t="inlineStr">
         <is>
-          <t>高仲明</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>092.11.05-093.02.15</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Ikaros Bigi</t>
+          <t>K. Nishikawa</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Notre Dame Univ.</t>
+          <t>Kyoto Univ.</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
@@ -14210,12 +14171,12 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>K. Nishikawa</t>
+          <t>Samoil Bilenky</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Kyoto Univ.</t>
+          <t>SISSA / JINR</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">
@@ -14232,12 +14193,12 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Samoil Bilenky</t>
+          <t>Antonio Maserio</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>SISSA / JINR</t>
+          <t>Padova Univ.</t>
         </is>
       </c>
       <c r="E385" t="inlineStr">
@@ -14254,56 +14215,56 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Antonio Maserio</t>
+          <t>周海軍</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Padova Univ.</t>
+          <t>中國科學院</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>096.05.14-096.06.15</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>周海軍</t>
+          <t>Carlos Wagner</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>中國科學院</t>
+          <t>ANL/Univ. of Chiago</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>096.05.14-096.06.15</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>Carlos Wagner</t>
+          <t>Helen Quinn</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>ANL/Univ. of Chiago</t>
+          <t>SLAC</t>
         </is>
       </c>
       <c r="E388" t="inlineStr">
@@ -14320,56 +14281,56 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Helen Quinn</t>
+          <t>Andre de Gouvea</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>SLAC</t>
+          <t>Department of Physics, Northwestern University</t>
         </is>
       </c>
       <c r="E389" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>蔣正偉</t>
         </is>
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>096.03.29-096.03.31</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Andre de Gouvea</t>
+          <t>Xerxes Tata</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Department of Physics, Northwestern University</t>
+          <t>Department of Physics, Hawaii University</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>蔣正偉</t>
+          <t>蔣正偉、江祖永</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>096.03.29-096.03.31</t>
+          <t>096.03.27-096.03.31</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Xerxes Tata</t>
+          <t>Jae-Sik Lee</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Department of Physics, Hawaii University</t>
+          <t>Center of Theoretical Physics, Seoul National University, Korea</t>
         </is>
       </c>
       <c r="E391" t="inlineStr">
@@ -14379,107 +14340,107 @@
       </c>
       <c r="F391" t="inlineStr">
         <is>
-          <t>096.03.27-096.03.31</t>
+          <t>096.03.26-096.04.07</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Jae-Sik Lee</t>
+          <t>Dr. William Allison</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>Center of Theoretical Physics, Seoul National University, Korea</t>
+          <t>Cavendish Laborotory, University of Cambridge</t>
         </is>
       </c>
       <c r="E392" t="inlineStr">
         <is>
-          <t>蔣正偉、江祖永</t>
+          <t>羅夢凡</t>
         </is>
       </c>
       <c r="F392" t="inlineStr">
         <is>
-          <t>096.03.26-096.04.07</t>
+          <t>096.04.08-096.04.15</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Dr. William Allison</t>
+          <t>Michael-James</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
         <is>
-          <t>Cavendish Laborotory, University of Cambridge</t>
+          <t>澳洲ANSTO</t>
         </is>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>羅夢凡</t>
+          <t>李文献</t>
         </is>
       </c>
       <c r="F393" t="inlineStr">
         <is>
-          <t>096.04.08-096.04.15</t>
+          <t>095.07.22-095.07.26</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Michael-James</t>
+          <t>歐陽頎</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>澳洲ANSTO</t>
+          <t>北京大學物理系</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>李文献</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>095.07.22-095.07.26</t>
+          <t>096.01.20-096.01.26</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>歐陽頎</t>
+          <t>Kouji Nakamura</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>北京大學物理系</t>
+          <t>National Astronomical Observatory of Japan</t>
         </is>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F395" t="inlineStr">
         <is>
-          <t>096.01.20-096.01.26</t>
+          <t>096.01.16-096.01.23</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Kouji Nakamura</t>
+          <t>劉潤球</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>National Astronomical Observatory of Japan</t>
+          <t>中科院應數所</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
@@ -14489,19 +14450,19 @@
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>096.01.16-096.01.23</t>
+          <t>096.01.10-096.01.12</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>劉潤球</t>
+          <t>D. V. Gal'tsov</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>中科院應數所</t>
+          <t>Department of Theoretical Physics of the Lomonosov Moscow State University</t>
         </is>
       </c>
       <c r="E397" t="inlineStr">
@@ -14511,173 +14472,173 @@
       </c>
       <c r="F397" t="inlineStr">
         <is>
-          <t>096.01.10-096.01.12</t>
+          <t>096.01.05-096.02.02</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>D. V. Gal'tsov</t>
+          <t>歐陽頎</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Department of Theoretical Physics of the Lomonosov Moscow State University</t>
+          <t>北京大學物理系</t>
         </is>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F398" t="inlineStr">
         <is>
-          <t>096.01.05-096.02.02</t>
+          <t>095.12.25-095.12.29</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>歐陽頎</t>
+          <t>Toshifumi Yamashita</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>北京大學物理系</t>
+          <t>SISSA</t>
         </is>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F399" t="inlineStr">
         <is>
-          <t>095.12.25-095.12.29</t>
+          <t>095.12.21-095.12.25</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Toshifumi Yamashita</t>
+          <t>Vipin Kumar Tripathi</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>SISSA</t>
+          <t>Physics Department, IIT Delhi , India</t>
         </is>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>劉全生</t>
         </is>
       </c>
       <c r="F400" t="inlineStr">
         <is>
-          <t>095.12.21-095.12.25</t>
+          <t>095.12.18-095.12.31</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Vipin Kumar Tripathi</t>
+          <t>Joe Sato</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>Physics Department, IIT Delhi , India</t>
+          <t>Department of Physics, Saitama University</t>
         </is>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>劉全生</t>
+          <t>薄書梅</t>
         </is>
       </c>
       <c r="F401" t="inlineStr">
         <is>
-          <t>095.12.18-095.12.31</t>
+          <t>096.06.03-096.06.09</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Joe Sato</t>
+          <t>Kin-ya Oda</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Department of Physics, Saitama University</t>
+          <t>RIKEN , Japan</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>薄書梅</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>096.06.03-096.06.09</t>
+          <t>095.12.03-095.12.08</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Kin-ya Oda</t>
+          <t>楊彤</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>RIKEN , Japan</t>
+          <t>香港城市大學數學系</t>
         </is>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>許正雄/洪盟凱</t>
         </is>
       </c>
       <c r="F403" t="inlineStr">
         <is>
-          <t>095.12.03-095.12.08</t>
+          <t>095.11.22-095.11.25</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>楊彤</t>
+          <t>童若軒</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>香港城市大學數學系</t>
+          <t>上海師範大學</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>許正雄/洪盟凱</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>095.11.22-095.11.25</t>
+          <t>095.11.05-095.11.28</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>童若軒</t>
+          <t>Hideki Maeda</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>上海師範大學</t>
+          <t>Waseda University, Japan</t>
         </is>
       </c>
       <c r="E405" t="inlineStr">
@@ -14687,63 +14648,63 @@
       </c>
       <c r="F405" t="inlineStr">
         <is>
-          <t>095.11.05-095.11.28</t>
+          <t>095.10.31-095.11.12</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Hideki Maeda</t>
+          <t>Ａlex Levine</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Waseda University, Japan</t>
+          <t>University of California, Los Angeles</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>陳宣毅</t>
         </is>
       </c>
       <c r="F406" t="inlineStr">
         <is>
-          <t>095.10.31-095.11.12</t>
+          <t>095.09.20-095.09.24</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ａlex Levine</t>
+          <t>Francesca M. Borzumati</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>University of California, Los Angeles</t>
+          <t>International Centre for Theoretical Physics(ICTP), ,Italy</t>
         </is>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>陳宣毅</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F407" t="inlineStr">
         <is>
-          <t>095.09.20-095.09.24</t>
+          <t>095.09.30-095.10.04</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Francesca M. Borzumati</t>
+          <t>Norisuke Sakai</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>International Centre for Theoretical Physics(ICTP), ,Italy</t>
+          <t>Tokyo Institute of Technology</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -14753,85 +14714,85 @@
       </c>
       <c r="F408" t="inlineStr">
         <is>
-          <t>095.09.30-095.10.04</t>
+          <t>095.09.19-095.09.20</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Norisuke Sakai</t>
+          <t>EI-Hang</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>Tokyo Institute of Technology</t>
+          <t>韓國INHA大學</t>
         </is>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>彭保仁</t>
         </is>
       </c>
       <c r="F409" t="inlineStr">
         <is>
-          <t>095.09.19-095.09.20</t>
+          <t>095.04</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>EI-Hang</t>
+          <t>G.V.Osipov, O.I.Kanakov, and O.V.Drugova</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>韓國INHA大學</t>
+          <t>Nizhny Novogorod University, Russia</t>
         </is>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>彭保仁</t>
+          <t>黎璧賢/陳志強</t>
         </is>
       </c>
       <c r="F410" t="inlineStr">
         <is>
-          <t>095.04</t>
+          <t>095.01.11</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>G.V.Osipov, O.I.Kanakov, and O.V.Drugova</t>
+          <t>Hyoung-Jin Choi&amp;nbsp;</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>Nizhny Novogorod University, Russia</t>
+          <t>Inha University</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>黎璧賢/陳志強</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F411" t="inlineStr">
         <is>
-          <t>095.01.11</t>
+          <t>095.05.05-095.05.07</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Hyoung-Jin Choi&amp;nbsp;</t>
+          <t>Penger Tong</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>Inha University</t>
+          <t>Hong Kong U of Science &amp; Tech</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
@@ -14848,12 +14809,12 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Penger Tong</t>
+          <t>夏克青</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Hong Kong U of Science &amp; Tech</t>
+          <t>Chinese U of Hong Kong</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
@@ -14870,12 +14831,12 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>夏克青</t>
+          <t>Yoon-Hwae Hwang , Hyuk-Kyu Pak</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>Chinese U of Hong Kong</t>
+          <t>Pusan National U</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
@@ -14885,19 +14846,14 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>095.05.05-095.05.07</t>
+          <t>095</t>
         </is>
       </c>
     </row>
     <row r="415">
-      <c r="A415" t="inlineStr">
-        <is>
-          <t>Yoon-Hwae Hwang , Hyuk-Kyu Pak</t>
-        </is>
-      </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>Pusan National U</t>
+          <t>U Tokyo</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
@@ -14912,31 +14868,36 @@
       </c>
     </row>
     <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>A. J. M Medved</t>
+        </is>
+      </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>U Tokyo</t>
+          <t>U of Witwatersrand, South Africa</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>095</t>
+          <t>096.05.21-096.06.02</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>A. J. M Medved</t>
+          <t>D. V. Gal'tsov</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
         <is>
-          <t>U of Witwatersrand, South Africa</t>
+          <t>Moscow State University, Russia</t>
         </is>
       </c>
       <c r="E417" t="inlineStr">
@@ -14946,41 +14907,41 @@
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>096.05.21-096.06.02</t>
+          <t>094.11.18-094.12.14</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>D. V. Gal'tsov</t>
+          <t>Jose G. Pereira</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
         <is>
-          <t>Moscow State University, Russia</t>
+          <t>Instituto de F&amp;iacute;sica Te&amp;oacute;rica, Universidade Estadual Paulista, S&amp;atilde;o Paulo, Brazil</t>
         </is>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>聶斯特</t>
         </is>
       </c>
       <c r="F418" t="inlineStr">
         <is>
-          <t>094.11.18-094.12.14</t>
+          <t>095.11.18-095.12.06</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Jose G. Pereira</t>
+          <t>L&amp;aacute;szl&amp;oacute; B. Szabados</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
         <is>
-          <t>Instituto de F&amp;iacute;sica Te&amp;oacute;rica, Universidade Estadual Paulista, S&amp;atilde;o Paulo, Brazil</t>
+          <t>Research Institute for Particle and Nuclear Physics of the Hungarian Academy of Sciences ,Hungary</t>
         </is>
       </c>
       <c r="E419" t="inlineStr">
@@ -14990,85 +14951,85 @@
       </c>
       <c r="F419" t="inlineStr">
         <is>
-          <t>095.11.18-095.12.06</t>
+          <t>095.11.05-095.11.23</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>L&amp;aacute;szl&amp;oacute; B. Szabados</t>
+          <t>Nobuyoshi Ohta</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Research Institute for Particle and Nuclear Physics of the Hungarian Academy of Sciences ,Hungary</t>
+          <t>Kinki University, Japan</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>聶斯特</t>
+          <t>陳江梅</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>095.11.05-095.11.23</t>
+          <t>096.01.27-096.01.30</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Nobuyoshi Ohta</t>
+          <t>Ying Xu（徐鷹）</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
         <is>
-          <t>Kinki University, Japan</t>
+          <t>University of Georgia</t>
         </is>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>陳江梅</t>
+          <t>李弘謙</t>
         </is>
       </c>
       <c r="F421" t="inlineStr">
         <is>
-          <t>096.01.27-096.01.30</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Ying Xu（徐鷹）</t>
+          <t>Chung Kao</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
         <is>
-          <t>University of Georgia</t>
+          <t>Univ. of Olkahoma</t>
         </is>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>李弘謙</t>
+          <t>江祖永</t>
         </is>
       </c>
       <c r="F422" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>093</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Chung Kao</t>
+          <t>Ashok Das</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
         <is>
-          <t>Univ. of Olkahoma</t>
+          <t>Univ. of Rochester</t>
         </is>
       </c>
       <c r="E423" t="inlineStr">
@@ -15078,19 +15039,19 @@
       </c>
       <c r="F423" t="inlineStr">
         <is>
-          <t>093</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Ashok Das</t>
+          <t>Paul Frampton</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>Univ. of Rochester</t>
+          <t>Univ. of North Carolina at Chapel Hill</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
@@ -15107,34 +15068,34 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Paul Frampton</t>
+          <t>Y.K.Lau</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>Univ. of North Carolina at Chapel Hill</t>
+          <t>Chinese Academy of Sciences, B</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>江祖永</t>
+          <t>聶斯特</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
         <is>
-          <t>094</t>
+          <t>092、094</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Y.K.Lau</t>
+          <t>F.W.Hehl</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Chinese Academy of Sciences, B</t>
+          <t>University of Cologne</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
@@ -15144,41 +15105,41 @@
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>092、094</t>
+          <t>092</t>
         </is>
       </c>
     </row>
     <row r="427">
-      <c r="A427" t="inlineStr">
-        <is>
-          <t>F.W.Hehl</t>
-        </is>
-      </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>University of Cologne</t>
+          <t>Tokyo Metropolitan University</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>聶斯特</t>
+          <t>陳培亮</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>092</t>
+          <t>094</t>
         </is>
       </c>
     </row>
     <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>Martin Zuckermann</t>
+        </is>
+      </c>
       <c r="D428" t="inlineStr">
         <is>
-          <t>Tokyo Metropolitan University</t>
+          <t>Simon Fraser University</t>
         </is>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>陳培亮</t>
+          <t>薛雅薇</t>
         </is>
       </c>
       <c r="F428" t="inlineStr">
@@ -15190,17 +15151,17 @@
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Martin Zuckermann</t>
+          <t>Andrew Torda</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
         <is>
-          <t>Simon Fraser University</t>
+          <t>University of Hamburg</t>
         </is>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>薛雅薇</t>
+          <t>李弘謙</t>
         </is>
       </c>
       <c r="F429" t="inlineStr">
@@ -15212,12 +15173,12 @@
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Andrew Torda</t>
+          <t>Jack Tuszynsri</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>University of Hamburg</t>
+          <t>University of Alberta</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
@@ -15234,12 +15195,12 @@
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Jack Tuszynsri</t>
+          <t>Dominique Chu</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>University of Alberta</t>
+          <t>University of Birmingham</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
@@ -15254,14 +15215,9 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" t="inlineStr">
-        <is>
-          <t>Dominique Chu</t>
-        </is>
-      </c>
       <c r="D432" t="inlineStr">
         <is>
-          <t>University of Birmingham</t>
+          <t>Dartmouth College</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
@@ -15276,9 +15232,14 @@
       </c>
     </row>
     <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>Bo Zheng（鄭波）</t>
+        </is>
+      </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>Dartmouth College</t>
+          <t>Zhejiang University</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -15295,12 +15256,12 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Bo Zheng（鄭波）</t>
+          <t>S. C. Wang（王孫崇）</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
         <is>
-          <t>Zhejiang University</t>
+          <t>University of Toronto</t>
         </is>
       </c>
       <c r="E434" t="inlineStr">
@@ -15317,17 +15278,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>S. C. Wang（王孫崇）</t>
+          <t>厚美瑛（M-Hou）</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
         <is>
-          <t>University of Toronto</t>
+          <t>Chinese Academy of Sciences</t>
         </is>
       </c>
       <c r="E435" t="inlineStr">
         <is>
-          <t>李弘謙</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F435" t="inlineStr">
@@ -15339,12 +15300,12 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>厚美瑛（M-Hou）</t>
+          <t>Meerson</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
         <is>
-          <t>Chinese Academy of Sciences</t>
+          <t>Hebrew University</t>
         </is>
       </c>
       <c r="E436" t="inlineStr">
@@ -15361,17 +15322,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Meerson</t>
+          <t>K.Opisov&amp;O.Kanarov&amp;O</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
         <is>
-          <t>Hebrew University</t>
+          <t>Novogorod University, Russia</t>
         </is>
       </c>
       <c r="E437" t="inlineStr">
         <is>
-          <t>黎璧賢</t>
+          <t>黎璧賢/陳志強</t>
         </is>
       </c>
       <c r="F437" t="inlineStr">
@@ -15383,17 +15344,17 @@
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>K.Opisov&amp;O.Kanarov&amp;O</t>
+          <t>S.Bastuleov</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Novogorod University, Russia</t>
+          <t>Joint Institute for Nuclear Re</t>
         </is>
       </c>
       <c r="E438" t="inlineStr">
         <is>
-          <t>黎璧賢/陳志強</t>
+          <t>黎璧賢</t>
         </is>
       </c>
       <c r="F438" t="inlineStr">
@@ -15402,30 +15363,8 @@
         </is>
       </c>
     </row>
-    <row r="439">
-      <c r="A439" t="inlineStr">
-        <is>
-          <t>S.Bastuleov</t>
-        </is>
-      </c>
-      <c r="D439" t="inlineStr">
-        <is>
-          <t>Joint Institute for Nuclear Re</t>
-        </is>
-      </c>
-      <c r="E439" t="inlineStr">
-        <is>
-          <t>黎璧賢</t>
-        </is>
-      </c>
-      <c r="F439" t="inlineStr">
-        <is>
-          <t>094</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F439"/>
+  <autoFilter ref="A1:F438"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/research.xlsx
+++ b/research.xlsx
@@ -821,7 +821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -885,897 +885,939 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>符合熱力學第二定律之主動熱浴熱機描述</t>
+          <t>吸積冰晶中的CO譜線輪廓</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Phys. Rev. Research 8, 023136</t>
+          <t>The Astrophysical Journal 1003 (2026) 3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yi-Hung Liao, Jerard Vincent Ang, Pik-Yin Lai, and Yonggun Jun</t>
+          <t>Rashida Aslam, Chun-Yi Lee, Yi-Hsuan Chiu, Cesare Cecchi-Pestellini, Angela Ciaravella, Antonio Jiménez-Escobar, Alfonso Mangione, and Yu-Jung Chen</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Second law-abiding-account of heat engines in active bath</t>
+          <t>CO Line Profiles in Accreting Ices</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%ac%a6%e5%90%88%e7%86%b1%e5%8a%9b%e5%ad%b8%e7%ac%ac%e4%ba%8c%e5%ae%9a%e5%be%8b%e4%b9%8b%e4%b8%bb%e5%8b%95%e7%86%b1%e6%b5%b4%e7%86%b1%e6%a9%9f%e6%8f%8f%e8%bf%b0/</t>
+          <t>https://iopscience.iop.org/article/10.3847/1538-4357/ae6111</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>熱力學第二定律對能量轉換設下基本限制，例如卡諾效率上限。主動熱浴中若出現看似違反該限制的現象，通常與對熱庫能量學的考量不夠完整有關。若在布朗旋轉子模型中，將主動雜訊明確納入為獨立自由度，則可證明系統的熵產生仍維持非負，且卡諾極限依然成立。本研究顯示，只要將主動漲落正確納入熱力學描述，即可維持基本熱力學原理的適用性。</t>
+          <t>本研究以實驗室天文化學方法，系統探討CO冰在不同形成條件下，其紅外吸收光譜如何反映星際冰層的化學組成與結構演化。陳俞融教授指導的研究團隊與義大利合作研究團隊透過兩種沉積模式—固定低溫混合沉積，以及模擬星塵冷卻歷程的降溫分層沉積—建立含H2O、NH3、CH4、CO2與CH3OH的多組冰樣本，並結合高解析紅外光譜與Gaussian分解方法，建立43組CO微環境光譜資料庫。進一步應用於James Webb Space Telescope（JWST）觀測資料後發現，分子雲與原行星盤中的CO冰層，其光譜特徵主要由少數幾種關鍵微環境所主導。此成果提供了解析星際冰層形成歷史、化學分層與熱演化的重要光譜診斷工具，並為未來多成分星際冰研究奠定基礎。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>The second law of thermodynamics imposes limits on energy conversion, such as the Carnot bound. Apparent violations in active baths often arise from incomplete accounting of the reservoir's energetics. By treating active noise as an explicit degree of freedom in a Brownian gyrator model, we show that entropy production remains non-negative and the Carnot limit is preserved. This study demonstrates that properly accounting for active fluctuations as distinct thermodynamic components upholds fundamental principles.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>左）二維 AOUP 旋轉子示意圖。主動雜訊可視為熱浴的一部分。（右）四維白雜訊旋轉子示意圖。主動雜訊可視為一個粒子，浸沒於兩個彼此獨立、作用於膠體微粒的白雜訊熱浴之中。</t>
+          <t>Using a laboratory astrochemistry approach, this study systematically investigates how the infrared absorption spectra of CO ice formed under different conditions reflect the chemical composition and structural evolution of interstellar ice mantles. Under the guidance of Professor Yu-Jung Chen, the research team, in collaboration with Italian partners, employed two deposition protocols—fixed low-temperature mixed deposition and temperature-decreasing layered deposition simulating the cooling history of interstellar dust grains—to produce multiple ice samples containing H2O, NH3, CH4, CO2, and CH3OH. By combining high-resolution infrared spectroscopy with Gaussian decomposition analysis, the team established a spectral library of 43 distinct CO microenvironments. When further applied to observational data from the James Webb Space Telescope (JWST), the results revealed that the spectral characteristics of CO ice in molecular clouds and protoplanetary disks are primarily governed by only a few key microenvironments. These findings provide an important spectroscopic diagnostic framework for reconstructing the formation history, chemical stratification, and thermal evolution of interstellar ice mantles, while also laying the foundation for future studies of multicomponent interstellar ices.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>files/research/符合熱力學第二定律之主動熱浴熱機描述.webp</t>
+          <t>files/research/吸積冰晶中的CO譜線輪廓.webp</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>利用 Λ 型超導人造原子透過電磁誘發透明現象實現光的減速與儲存</t>
+          <t>符合熱力學第二定律之主動熱浴熱機描述</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Phys. Rev. Research 7, L012015</t>
+          <t>Phys. Rev. Research 8, 023136</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kai-I Chu, Xiao-Cheng Lu, Kuan-Hsun Chiang, Yen-Hsiang Lin, Chii-Dong Chen, Ite A. Yu, Wen-Te Liao, and Yung-Fu Chen</t>
+          <t>Yi-Hung Liao, Jerard Vincent Ang, Pik-Yin Lai, and Yonggun Jun</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Slow and stored light via electromagnetically induced transparency using a Λ-type superconducting artificial atom</t>
+          <t>Second law-abiding-account of heat engines in active bath</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/slow-and-stored-light-via-electromagnetically-induced-transparency-using-a-%ce%bb-type-superconducting-artificial-atom/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%ac%a6%e5%90%88%e7%86%b1%e5%8a%9b%e5%ad%b8%e7%ac%ac%e4%ba%8c%e5%ae%9a%e5%be%8b%e4%b9%8b%e4%b8%bb%e5%8b%95%e7%86%b1%e6%b5%b4%e7%86%b1%e6%a9%9f%e6%8f%8f%e8%bf%b0/</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>本研究成功利用單個超導量子位元與高品質共振腔耦合，構建出 Lambda 型人造原子並觀測到電磁誘發透明（EIT）現象。相較於傳統需大量原子團的系統，本研究僅憑單顆人造原子即可將微波脈衝減速至 3.6 km/s。透過絕熱切斷控制光，微波脈衝能被儲存於共振腔中，達成「按需儲存與取回」。此成果展現了在超導電路中實現微波量子記憶體的潛力，為量子資訊處理技術帶來重要進展。</t>
+          <t>熱力學第二定律對能量轉換設下基本限制，例如卡諾效率上限。主動熱浴中若出現看似違反該限制的現象，通常與對熱庫能量學的考量不夠完整有關。若在布朗旋轉子模型中，將主動雜訊明確納入為獨立自由度，則可證明系統的熵產生仍維持非負，且卡諾極限依然成立。本研究顯示，只要將主動漲落正確納入熱力學描述，即可維持基本熱力學原理的適用性。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>This study demonstrates the realization of Electromagnetically Induced Transparency (EIT) using a Lambda-type artificial atom formed by coupling a single superconducting qubit to a high-Q resonator. Unlike traditional systems that require atomic ensembles, this research achieves EIT with a single artificial atom, slowing microwave pulses down to 3.6 km/s. By adiabatically turning off the control light, microwave pulses can be stored in the resonator, enabling on-demand storage and retrieval. Our results highlight the potential of achieving microwave quantum memory, promising important advancements in quantum information processing within superconducting circuits.</t>
+          <t>The second law of thermodynamics imposes limits on energy conversion, such as the Carnot bound. Apparent violations in active baths often arise from incomplete accounting of the reservoir's energetics. By treating active noise as an explicit degree of freedom in a Brownian gyrator model, we show that entropy production remains non-negative and the Carnot limit is preserved. This study demonstrates that properly accounting for active fluctuations as distinct thermodynamic components upholds fundamental principles.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Upper plot: superconducting circuit and its energy level diagram.</t>
+          <t>左）二維 AOUP 旋轉子示意圖。主動雜訊可視為熱浴的一部分。（右）四維白雜訊旋轉子示意圖。主動雜訊可視為一個粒子，浸沒於兩個彼此獨立、作用於膠體微粒的白雜訊熱浴之中。</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>files/research/利用Lambda型超導人造原子透過電磁誘發透明現象實現光的減速與儲存.webp</t>
+          <t>files/research/符合熱力學第二定律之主動熱浴熱機描述.webp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>近極端帶電 Nariai 黑洞中泡利阻礙的飽和效應</t>
+          <t>利用 Λ 型超導人造原子透過電磁誘發透明現象實現光的減速與儲存</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Phys. Rev. D 113 (2026) 025011</t>
+          <t>Phys. Rev. Research 7, L012015</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chiang-Mei Chen, Chun-Chih Huang and Sang Pyo Kim</t>
+          <t>Kai-I Chu, Xiao-Cheng Lu, Kuan-Hsun Chiang, Yen-Hsiang Lin, Chii-Dong Chen, Ite A. Yu, Wen-Te Liao, and Yung-Fu Chen</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Saturation of Pauli Blocking in Near-extremal Charged Nariai Black Holes</t>
+          <t>Slow and stored light via electromagnetically induced transparency using a Λ-type superconducting artificial atom</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%bf%91%e6%a5%b5%e7%ab%af%e5%b8%b6%e9%9b%bb-nariai-%e9%bb%91%e6%b4%9e%e4%b8%ad%e6%b3%a1%e5%88%a9%e9%98%bb%e7%a4%99%e7%9a%84%e9%a3%bd%e5%92%8c%e6%95%88%e6%87%89/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/slow-and-stored-light-via-electromagnetically-induced-transparency-using-a-%ce%bb-type-superconducting-artificial-atom/</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>我們在近極端 Nariai 黑洞（近視界幾何為 de Sitter時空）中求解帶電費米子的狄拉克方程。與玻色子不同，費米子放射受到泡利阻礙限制，且不出現超輻射放大。利用對偶關係，我們亦分析 anti de Sitter 時空中的 Schwinger 產生，並比較費米子與玻色子的情形。</t>
+          <t>本研究成功利用單個超導量子位元與高品質共振腔耦合，構建出 Lambda 型人造原子並觀測到電磁誘發透明（EIT）現象。相較於傳統需大量原子團的系統，本研究僅憑單顆人造原子即可將微波脈衝減速至 3.6 km/s。透過絕熱切斷控制光，微波脈衝能被儲存於共振腔中，達成「按需儲存與取回」。此成果展現了在超導電路中實現微波量子記憶體的潛力，為量子資訊處理技術帶來重要進展。</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>We solve the Dirac equation for charged fermions in near-extremal Nariai black holes with de Sitter (dS) geometry. Unlike bosons, fermion emission is Pauli-blocked and shows no superradiant amplification. Using a reciprocal relation, we also analyze Schwinger emission in anti-de Sitter (AdS) and compare fermionic and bosonic cases.</t>
+          <t>This study demonstrates the realization of Electromagnetically Induced Transparency (EIT) using a Lambda-type artificial atom formed by coupling a single superconducting qubit to a high-Q resonator. Unlike traditional systems that require atomic ensembles, this research achieves EIT with a single artificial atom, slowing microwave pulses down to 3.6 km/s. By adiabatically turning off the control light, microwave pulses can be stored in the resonator, enabling on-demand storage and retrieval. Our results highlight the potential of achieving microwave quantum memory, promising important advancements in quantum information processing within superconducting circuits.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>近極端 Nariai 黑洞中費米子與純量粒子放射的比較。虛線表示純量粒子，實線表示費米子。</t>
+          <t>Upper plot: superconducting circuit and its energy level diagram.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>files/research/近極端帶電Nariai黑洞中泡利阻礙的飽和效應.webp</t>
+          <t>files/research/利用Lambda型超導人造原子透過電磁誘發透明現象實現光的減速與儲存.webp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>具熱力學一致性的旋轉黑洞陰影</t>
+          <t>近極端帶電 Nariai 黑洞中泡利阻礙的飽和效應</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Phys. Rev. D 113 (2026) 044044</t>
+          <t>Phys. Rev. D 113 (2026) 025011</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Che-Yu Chen, Chiang-Mei Chen and Nobuyoshi Ohta</t>
+          <t>Chiang-Mei Chen, Chun-Chih Huang and Sang Pyo Kim</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Shadow of Rotating Black Holes with Consistent Thermodynamics</t>
+          <t>Saturation of Pauli Blocking in Near-extremal Charged Nariai Black Holes</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%85%b7%e7%86%b1%e5%8a%9b%e5%ad%b8%e4%b8%80%e8%87%b4%e6%80%a7%e7%9a%84%e6%97%8b%e8%bd%89%e9%bb%91%e6%b4%9e%e9%99%b0%e5%bd%b1/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%bf%91%e6%a5%b5%e7%ab%af%e5%b8%b6%e9%9b%bb-nariai-%e9%bb%91%e6%b4%9e%e4%b8%ad%e6%b3%a1%e5%88%a9%e9%98%bb%e7%a4%99%e7%9a%84%e9%a3%bd%e5%92%8c%e6%95%88%e6%87%89/</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>我們研究具有尺度依賴牛頓常數的 Kerr 黑洞，並以熱力學一致性加以約束。結合 Sgr A* 的觀測資料，我們對模型參數空間給出限制，並指出黑洞陰影的特徵主要由事件視界性質所決定。值得注意的是，熱力學一致性預示陰影尺寸存在下限，且模型允許超越 Kerr 極限的自旋，並可能產生具有尖角結構的陰影。</t>
+          <t>我們在近極端 Nariai 黑洞（近視界幾何為 de Sitter時空）中求解帶電費米子的狄拉克方程。與玻色子不同，費米子放射受到泡利阻礙限制，且不出現超輻射放大。利用對偶關係，我們亦分析 anti de Sitter 時空中的 Schwinger 產生，並比較費米子與玻色子的情形。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>We study Kerr black holes with a running Newton coupling, constrained by thermodynamic consistency. Using Sgr A* observations, we place bounds on the model and show that shadow features are largely determined by horizon properties. Notably, consistency implies a lower bound on shadow size and allows for possible super-Kerr rotation with distinctive cuspy shadows.</t>
+          <t>We solve the Dirac equation for charged fermions in near-extremal Nariai black holes with de Sitter (dS) geometry. Unlike bosons, fermion emission is Pauli-blocked and shows no superradiant amplification. Using a reciprocal relation, we also analyze Schwinger emission in anti-de Sitter (AdS) and compare fermionic and bosonic cases.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>不同參數取值下的陰影臨界曲線。 | 在大角動量下，陰影臨界曲線中尖點結構的形成。</t>
+          <t>近極端 Nariai 黑洞中費米子與純量粒子放射的比較。虛線表示純量粒子，實線表示費米子。</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>files/research/具熱力學一致性的旋轉黑洞陰影1.webp</t>
+          <t>files/research/近極端帶電Nariai黑洞中泡利阻礙的飽和效應.webp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>PtSe2/PtTe2凡德瓦莫瑞雙層之電子結構調變</t>
+          <t>具熱力學一致性的旋轉黑洞陰影</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ACS Nano</t>
+          <t>Phys. Rev. D 113 (2026) 044044</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yin-Song Liao, Ruei-Yu Wang, Han-Wei Tsai, Guan-Hao Chen, Hsin-Hsien Chan, Hsun-Ting Hsieh, Cheng-Maw Cheng, Chun-Liang Lin, Meng-Kai Lin,* and Jyh-Pin Chou</t>
+          <t>Che-Yu Chen, Chiang-Mei Chen and Nobuyoshi Ohta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Moiré-Induced Electronic Reconstruction in van der Waals Heterobilayer PtSe2/PtTe2</t>
+          <t>Shadow of Rotating Black Holes with Consistent Thermodynamics</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/ptse2-ptte2%e5%87%a1%e5%be%b7%e7%93%a6%e8%8e%ab%e7%91%9e%e9%9b%99%e5%b1%a4%e4%b9%8b%e9%9b%bb%e5%ad%90%e7%b5%90%e6%a7%8b%e8%aa%bf%e8%ae%8a/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%85%b7%e7%86%b1%e5%8a%9b%e5%ad%b8%e4%b8%80%e8%87%b4%e6%80%a7%e7%9a%84%e6%97%8b%e8%bd%89%e9%bb%91%e6%b4%9e%e9%99%b0%e5%bd%b1/</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>凡德瓦異質結構，由於材料可逼近原子尺度，因此在凝態物理學群極受注目。由於界面間沒有鍵結，凡德瓦異質結構界面間仍會透過如莫瑞週期調製、電荷重新分配、以及電子軌域的混層導致能帶結構的變化以及調製界面耦合的強弱。於本研究中，林孟凱的團隊透過分子束磊晶技術成功成長出單層PtSe2/PtTe2異質接面，並運用角解析光電子能譜技術證實了此凡德瓦異質接面的耦合特性。除實驗發現，林孟凱的實驗團隊亦協同台灣大學周至品教授團隊進行第一原理計算，研究更深入的物理機制。藉由實驗及理論比對，得知此異質結構會透過界面交互作用，使得PtSe2產生曲折而破壞晶體對稱性，進一步導致自旋能帶分裂；此外，莫瑞週期中特定的局域電子態，會產生靠近費米能階的「平帶」結構，意味著部分的價電子產生了局域性。此研究結果解釋了凡德瓦二維系統的界面交互作用機制，並說明了界面交互作用如何影響能帶結構的分布，提供了凡德瓦二維系統在低維度下的應用可能性。</t>
+          <t>我們研究具有尺度依賴牛頓常數的 Kerr 黑洞，並以熱力學一致性加以約束。結合 Sgr A* 的觀測資料，我們對模型參數空間給出限制，並指出黑洞陰影的特徵主要由事件視界性質所決定。值得注意的是，熱力學一致性預示陰影尺寸存在下限，且模型允許超越 Kerr 極限的自旋，並可能產生具有尖角結構的陰影。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>van der Waals heterostructures composed of a few atomic layers have attracted significant attention in the condensed matter physics community. Although interlayer bonding is weak, effects such as moiré modulation, charge redistribution, and electronic hybridization can substantially modify the band structure and interlayer coupling. In this work, we investigate heterostructures composed of few-layer PtSe2 and PtTe2 by using first-principles calculations implemented within density functional theory (DFT) and angle-resolved photoemission spectroscopy (ARPES). While both materials are Dirac semimetals in the bulk form, they undergo a transition to semiconducting states in the few-layer limit. These heterostructures allow systematic examination of how dimensional confinement and interfacial interactions influence band structure and interlayer coupling. Our combined ARPES measurements and DFT calculations indicate the presence of electronic hybridization at the interface. The interlayer coupling in PtSe2/PtTe2 is associated with flat-band features and valence-band splitting induced by both inversion symmetry breaking and spin–orbit coupling. Furthermore, the local density of states indicates metallic behavior at the MM site while it remains semiconducting at MX and XX sites with the band gap of 0.40 and 0.25 eV, respectively. Further analysis shows that the electronic hybridization and charge transfer between PtSe2 and PtTe2 are sensitive to the interlayer distance, which is consistent with moiré characteristics. These results highlight how interfacial interactions govern the electronic properties of vdW heterostructures.</t>
+          <t>We study Kerr black holes with a running Newton coupling, constrained by thermodynamic consistency. Using Sgr A* observations, we place bounds on the model and show that shadow features are largely determined by horizon properties. Notably, consistency implies a lower bound on shadow size and allows for possible super-Kerr rotation with distinctive cuspy shadows.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>不同參數取值下的陰影臨界曲線。 | 在大角動量下，陰影臨界曲線中尖點結構的形成。</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>files/research/PtSe2_PtTe2凡德瓦莫瑞雙層之電子結構調變.webp</t>
+          <t>files/research/具熱力學一致性的旋轉黑洞陰影1.webp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>PtSe2/PtTe2凡德瓦莫瑞雙層之電子結構調變</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ACS Nano</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Yin-Song Liao, Ruei-Yu Wang, Han-Wei Tsai, Guan-Hao Chen, Hsin-Hsien Chan, Hsun-Ting Hsieh, Cheng-Maw Cheng, Chun-Liang Lin, Meng-Kai Lin,* and Jyh-Pin Chou</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Moiré-Induced Electronic Reconstruction in van der Waals Heterobilayer PtSe2/PtTe2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/ptse2-ptte2%e5%87%a1%e5%be%b7%e7%93%a6%e8%8e%ab%e7%91%9e%e9%9b%99%e5%b1%a4%e4%b9%8b%e9%9b%bb%e5%ad%90%e7%b5%90%e6%a7%8b%e8%aa%bf%e8%ae%8a/</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>凡德瓦異質結構，由於材料可逼近原子尺度，因此在凝態物理學群極受注目。由於界面間沒有鍵結，凡德瓦異質結構界面間仍會透過如莫瑞週期調製、電荷重新分配、以及電子軌域的混層導致能帶結構的變化以及調製界面耦合的強弱。於本研究中，林孟凱的團隊透過分子束磊晶技術成功成長出單層PtSe2/PtTe2異質接面，並運用角解析光電子能譜技術證實了此凡德瓦異質接面的耦合特性。除實驗發現，林孟凱的實驗團隊亦協同台灣大學周至品教授團隊進行第一原理計算，研究更深入的物理機制。藉由實驗及理論比對，得知此異質結構會透過界面交互作用，使得PtSe2產生曲折而破壞晶體對稱性，進一步導致自旋能帶分裂；此外，莫瑞週期中特定的局域電子態，會產生靠近費米能階的「平帶」結構，意味著部分的價電子產生了局域性。此研究結果解釋了凡德瓦二維系統的界面交互作用機制，並說明了界面交互作用如何影響能帶結構的分布，提供了凡德瓦二維系統在低維度下的應用可能性。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>van der Waals heterostructures composed of a few atomic layers have attracted significant attention in the condensed matter physics community. Although interlayer bonding is weak, effects such as moiré modulation, charge redistribution, and electronic hybridization can substantially modify the band structure and interlayer coupling. In this work, we investigate heterostructures composed of few-layer PtSe2 and PtTe2 by using first-principles calculations implemented within density functional theory (DFT) and angle-resolved photoemission spectroscopy (ARPES). While both materials are Dirac semimetals in the bulk form, they undergo a transition to semiconducting states in the few-layer limit. These heterostructures allow systematic examination of how dimensional confinement and interfacial interactions influence band structure and interlayer coupling. Our combined ARPES measurements and DFT calculations indicate the presence of electronic hybridization at the interface. The interlayer coupling in PtSe2/PtTe2 is associated with flat-band features and valence-band splitting induced by both inversion symmetry breaking and spin–orbit coupling. Furthermore, the local density of states indicates metallic behavior at the MM site while it remains semiconducting at MX and XX sites with the band gap of 0.40 and 0.25 eV, respectively. Further analysis shows that the electronic hybridization and charge transfer between PtSe2 and PtTe2 are sensitive to the interlayer distance, which is consistent with moiré characteristics. These results highlight how interfacial interactions govern the electronic properties of vdW heterostructures.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>files/research/PtSe2_PtTe2凡德瓦莫瑞雙層之電子結構調變.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>彎曲時空中的量子力學新理論 -- 海森堡繪景及非交換幾何觀點</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>Chin. J. Phys. 96 (2025) 690</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Otto C. W. Kong</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>Quantum Mechanics in Curved Space(time) with a Noncommutative Geometric Perspective</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%bd%8e%e6%9b%b2%e6%99%82%e7%a9%ba%e4%b8%ad%e7%9a%84%e9%87%8f%e5%ad%90%e5%8a%9b%e5%ad%b8%e6%96%b0%e7%90%86%e8%ab%96-%e6%b5%b7%e6%a3%ae%e5%a0%a1%e7%b9%aa%e6%99%af%e5%8f%8a%e9%9d%9e%e4%ba%a4/</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>向量具有四種形式和不變幅值平方。
 由自由粒子哈密頓運動獲得一般度量張量下的量子測地線方程。</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Vector quantity in four forms with invariant magnitude square.
 Quantum geodesic equations under a generic metric obtained from free-particle Hamiltonian motion.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>Hamiltonian Dynamics for Quantum Particle</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>files/research/彎曲時空中的量子力學新理論-海森堡繪景及非交換幾何觀點.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>狹義量子相對論－(量子)閔可夫斯基中作為量子參考系變換的狹義相對論對稱性</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Class. Quantum Grav. 42 (2025) 115007</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Otto C. W. Kong</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>On the Symmetry of Special Quantum Relativity</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%8b%b9%e7%be%a9%e9%87%8f%e5%ad%90%e7%9b%b8%e5%b0%8d%e8%ab%96%ef%bc%8d%e9%87%8f%e5%ad%90%e9%96%94%e5%8f%af%e5%a4%ab%e6%96%af%e5%9f%ba%e4%b8%ad%e4%bd%9c%e7%82%ba%e9%87%8f%e5%ad%90%e5%8f%83%e8%80%83/</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>(量子)閔可夫斯基時空中的量子參考系變換具有四向量非交換參數的李群形式。洛倫茲變換作為極限情況包含其中。</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Quantum reference frame transformations in (quantum) Minkowski spacetime obtained as Lie group with a four-vector noncommutative parameter. Lorentz transformations included as limiting cases.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>files/research/狹義量子相對論-(量子)閔可夫斯基中作為量子參考系變換的狹義相對論對稱性.webp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>細胞也會被拉高！揭開反覆拉扯如何塑造柱狀細胞的祕密</t>
+          <t>狹義量子相對論－(量子)閔可夫斯基中作為量子參考系變換的狹義相對論對稱性</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cell Reports</t>
+          <t>Class. Quantum Grav. 42 (2025) 115007</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Lun-Wei Lee, Gang-Hui Lee, I-Hsiu Su, Chia-Hsuan Lu, Keng-Hui Lin, Fu-Lai Wen, Ming-Jer Tang</t>
+          <t>Otto C. W. Kong</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Mechanobiological mechanism of cyclic stretch-induced cell columnarization</t>
+          <t>On the Symmetry of Special Quantum Relativity</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%b4%b0%e8%83%9e%e4%b9%9f%e6%9c%83%e8%a2%ab%e6%8b%89%e9%ab%98%ef%bc%81%e6%8f%ad%e9%96%8b%e5%8f%8d%e8%a6%86%e6%8b%89%e6%89%af%e5%a6%82%e4%bd%95%e5%a1%91%e9%80%a0%e6%9f%b1%e7%8b%80%e7%b4%b0%e8%83%9e/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%8b%b9%e7%be%a9%e9%87%8f%e5%ad%90%e7%9b%b8%e5%b0%8d%e8%ab%96%ef%bc%8d%e9%87%8f%e5%ad%90%e9%96%94%e5%8f%af%e5%a4%ab%e6%96%af%e5%9f%ba%e4%b8%ad%e4%bd%9c%e7%82%ba%e9%87%8f%e5%ad%90%e5%8f%83%e8%80%83/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>本研究發現，長時間單軸循環拉伸，會誘發上皮細胞內部細胞骨架重塑與細胞間黏著分子重組，促使MDCK細胞(一種狗腎上皮細胞)由立方形轉變為柱狀形態。透過原子力顯微鏡的量測與數學模型的分析，我們證實此過程伴隨著細胞頂端與底端的張力增強，因而驅動細胞形狀改變。此研究揭示上皮細胞適應機械刺激之力學調控機制</t>
+          <t>(量子)閔可夫斯基時空中的量子參考系變換具有四向量非交換參數的李群形式。洛倫茲變換作為極限情況包含其中。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>This study demonstrates that long-term uniaxial cyclic stretching induces cytoskeletal remodeling and reorganization of cell–cell adhesion molecules in epithelial cells, driving the morphological transition of MDCK cells (a canine kidney epithelial cell line) from a cuboidal to a columnar shape. Through atomic force microscopy (AFM) measurements and mathematical modeling analyses, we confirmed that this process is accompanied by increased tensile forces at both the apical and basal regions of the cell, which in turn promote the shape change. Our findings reveal the mechanobiological mechanisms by which epithelial cells adapt to mechanical stimulation.</t>
+          <t>Quantum reference frame transformations in (quantum) Minkowski spacetime obtained as Lie group with a four-vector noncommutative parameter. Lorentz transformations included as limiting cases.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>files/research/細胞也會被拉高!揭開反覆拉扯如何塑造柱狀細胞的祕密.webp</t>
+          <t>files/research/狹義量子相對論-(量子)閔可夫斯基中作為量子參考系變換的狹義相對論對稱性.webp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>多個驅動蛋白在擁擠的環境中通過分擔負載來加速貨物運輸</t>
+          <t>細胞也會被拉高！揭開反覆拉扯如何塑造柱狀細胞的祕密</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Communications Biology</t>
+          <t>Cell Reports</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ya-Ting Huang, Michio Tomishige, Steven Gross, Pik-Yin Lai, and Yonggun Jun</t>
+          <t>Lun-Wei Lee, Gang-Hui Lee, I-Hsiu Su, Chia-Hsuan Lu, Keng-Hui Lin, Fu-Lai Wen, Ming-Jer Tang</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Multiple kinesins speed up cargo transport in crowded environments by sharing load</t>
+          <t>Mechanobiological mechanism of cyclic stretch-induced cell columnarization</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/56769/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%b4%b0%e8%83%9e%e4%b9%9f%e6%9c%83%e8%a2%ab%e6%8b%89%e9%ab%98%ef%bc%81%e6%8f%ad%e9%96%8b%e5%8f%8d%e8%a6%86%e6%8b%89%e6%89%af%e5%a6%82%e4%bd%95%e5%a1%91%e9%80%a0%e6%9f%b1%e7%8b%80%e7%b4%b0%e8%83%9e/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>這項研究表明多個驅動蛋白馬達如何在擁擠的細胞環境中沿著微管運輸貨物。我們使用非侵入性方法來量化活躍的馬達數量，並發現貨物的運動速度取決於參與運輸的馬達數量以及周圍環境內高分子的大小。結果表明，驅動蛋白產生的張力能在集體運輸中發揮作用。我們同時也有隨機模擬來佐證此一結論。該研究強調了此方法在研究馬達蛋白的參與機制方面的廣泛適用性，並還能用來探討擁擠環境中張力與驅動蛋白運輸貨物之間的複雜相互作用關係。</t>
+          <t>本研究發現，長時間單軸循環拉伸，會誘發上皮細胞內部細胞骨架重塑與細胞間黏著分子重組，促使MDCK細胞(一種狗腎上皮細胞)由立方形轉變為柱狀形態。透過原子力顯微鏡的量測與數學模型的分析，我們證實此過程伴隨著細胞頂端與底端的張力增強，因而驅動細胞形狀改變。此研究揭示上皮細胞適應機械刺激之力學調控機制</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>This study investigates how multiple kinesin motors transport cargo along microtubules in crowded environments. Using a non-invasive method to quantify the number of active motors, we find that cargo velocity depends on both motor number and the size of surrounding macromolecular obstacles. Their results suggest that kinesin-generated tension influences collective transport, a finding supported by stochastic simulations. The study highlights the method's broad applicability for studying motor engagement and the complex interplay between crowding tension and kinesin-driven cargo movement.</t>
+          <t>This study demonstrates that long-term uniaxial cyclic stretching induces cytoskeletal remodeling and reorganization of cell–cell adhesion molecules in epithelial cells, driving the morphological transition of MDCK cells (a canine kidney epithelial cell line) from a cuboidal to a columnar shape. Through atomic force microscopy (AFM) measurements and mathematical modeling analyses, we confirmed that this process is accompanied by increased tensile forces at both the apical and basal regions of the cell, which in turn promote the shape change. Our findings reveal the mechanobiological mechanisms by which epithelial cells adapt to mechanical stimulation.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>files/research/多個驅動蛋白在擁擠的環境中通過分擔負載來加速貨物運輸.webp</t>
+          <t>files/research/細胞也會被拉高!揭開反覆拉扯如何塑造柱狀細胞的祕密.webp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>替地球重力拍X光影像</t>
+          <t>多個驅動蛋白在擁擠的環境中通過分擔負載來加速貨物運輸</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Phys. Rev. Research 7, 013158</t>
+          <t>Communications Biology</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Shin-Yu Lee, Sven Ahrens, and Wen-Te Liao</t>
+          <t>Ya-Ting Huang, Michio Tomishige, Steven Gross, Pik-Yin Lai, and Yonggun Jun</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Gravitationally sensitive structured x-ray optics using nuclear resonances</t>
+          <t>Multiple kinesins speed up cargo transport in crowded environments by sharing load</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%9b%bf%e5%9c%b0%e7%90%83%e9%87%8d%e5%8a%9b%e6%8b%8dx%e5%85%89%e5%bd%b1%e5%83%8f/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/56769/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>我們與上海師範大學的Sven Ahrens教授合作設計一種新型結構化X光波導管[structured X-ray waveguide (SXWG)]，能探測地球上1毫米高度變化所引起的重力差異。根據X光通過波導管傳播行為與量子粒子行為之間的類比，我們在光學薛丁格方程式的引導下設計了SXWG，將鈧-45-碳交錯的週期性結構夾在兩個鉑包覆層之間。其中鈧-45同位素的極窄原子核鐘躍遷，其自然線寬約為2 Hz，躍遷能量約為12.4 keV。如此窄的線寬能用來檢測到鈧-45與共振X光之間在1毫米高度變化下的微小交互作用差異。因此改變SXWG的高度將因重力紅位移效應而改變兩個X光波導管模態之間的耦合強度。我們的計算結果顯示，SXWG的X光輸出光班分佈會受到高度變化的影響。故透過檢視光班的變化便能得知SXWG與X光光源之間的高度差。而使用其他同位素，如釷-229、銀-109等，甚至可以達到微米等級的靈敏度。</t>
+          <t>這項研究表明多個驅動蛋白馬達如何在擁擠的細胞環境中沿著微管運輸貨物。我們使用非侵入性方法來量化活躍的馬達數量，並發現貨物的運動速度取決於參與運輸的馬達數量以及周圍環境內高分子的大小。結果表明，驅動蛋白產生的張力能在集體運輸中發揮作用。我們同時也有隨機模擬來佐證此一結論。該研究強調了此方法在研究馬達蛋白的參與機制方面的廣泛適用性，並還能用來探討擁擠環境中張力與驅動蛋白運輸貨物之間的複雜相互作用關係。</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>We collaborate with Prof. Sven Ahrens from Shanghai Normal University to design a novel structured X-ray waveguide (SXWG) capable of detecting gravitational differences caused by height changes as small as 1 millimeter on Earth. Based on  an analogy between the propagation of X-rays through a waveguide and the behavior of quantum particles, we designed the SXWG under the guidance of the optical Schrödinger equation, sandwiching a periodic structure of 45Sc scandium-carbon interleaved layers between two platinum-coated layers. The scandium isotope has an extremely narrow nuclear clock transition, with a natural linewidth of about 2 Hz and a transition energy of approximately 12.4 keV. Such a narrow linewidth can be used to detect tiny interaction differences between 45Sc and resonant X-rays under a 1-millimeter height change. Thus, altering the height of the SXWG will change the coupling strength between two X-ray waveguide modes due to the gravitational redshift effect. Our calculations show that the X-ray output intensity distribution of the SXWG is affected by height changes. Therefore, by examining the changes in the light pattern, the height difference between the SXWG and the X-ray source can be determined. Using other isotopes, such as 229Th or 109Ag, can even achieve sensitivity at the micrometer level.</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Figure. Sensing the difference of gravity in 1mm altitude change on Earth using an SXWG and 45Sc nuclear clock transition.</t>
+          <t>This study investigates how multiple kinesin motors transport cargo along microtubules in crowded environments. Using a non-invasive method to quantify the number of active motors, we find that cargo velocity depends on both motor number and the size of surrounding macromolecular obstacles. Their results suggest that kinesin-generated tension influences collective transport, a finding supported by stochastic simulations. The study highlights the method's broad applicability for studying motor engagement and the complex interplay between crowding tension and kinesin-driven cargo movement.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>files/research/替地球重力拍X光影像.webp</t>
+          <t>files/research/多個驅動蛋白在擁擠的環境中通過分擔負載來加速貨物運輸.webp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>準一維外爾半金屬材料(TaSe4)2I之電荷密度波行為</t>
+          <t>替地球重力拍X光影像</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Nano Letters 24, 8778 (2024)</t>
+          <t>Phys. Rev. Research 7, 013158</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Meng-Kai Lin*, Joseph Andrew Hlevyack, Chengxi Zhao, Pavel Dudin, José Avila, Sung-Kwan Mo, Cheng-Maw Cheng, Peter Abbamonte, Daniel P. Shoemaker, and Tai-Chang Chiang*</t>
+          <t>Shin-Yu Lee, Sven Ahrens, and Wen-Te Liao</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Unconventional Spectral Gaps Induced by Charge Density Waves in the Weyl Semimetal (TaSe4)2I</t>
+          <t>Gravitationally sensitive structured x-ray optics using nuclear resonances</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%ba%96%e4%b8%80%e7%b6%ad%e5%a4%96%e7%88%be%e5%8d%8a%e9%87%91%e5%b1%ac%e6%9d%90%e6%96%99tase42i%e4%b9%8b%e9%9b%bb%e8%8d%b7%e5%af%86%e5%ba%a6%e6%b3%a2%e8%a1%8c%e7%82%ba/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%9b%bf%e5%9c%b0%e7%90%83%e9%87%8d%e5%8a%9b%e6%8b%8dx%e5%85%89%e5%bd%b1%e5%83%8f/</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>近幾年的理論指出，若外爾半金屬(Weyl semimetal)材料同時具備電荷密度波(Charge density wave)特性，電荷密度波相量有機會與外爾費米子間耦合，形成軸子絕緣體(axion insulator)。而準一維材料(TaSe4)2I是少數符合上述特性的材料，被認為是軸子絕緣體的候選材料。然而實驗上並未能提出直接的電荷密度波-外爾點交互作用證據，原因出自於此材料在溫度低於相轉變溫度時，靠近費米能階之光電子能譜訊號會急遽衰減，導致無法解析外爾點上是否有能隙產生。對於無法解析的費米能階附近能帶結構，過往的研究提出如axion insulator phases、correlation pseudogaps、polaron subbands、bipolaron bound states等解釋，然而這些解釋都會牽涉能隙的打開或能帶結構變化。我們運用角解析光電子能譜(Angle-resolved photoemission spectroscopy, ARPES)技術重新檢視此材料系統，並發現隨著樣品溫度的變化，能帶結構並沒有任何的變化，費米能階附近能帶結構的消失，是出自於樣品進入電荷密度波的相後，因為非相稱(incommensurate)電荷密度波特性，電荷密度波的週期並不跟晶格週期匹配，導致了準粒子的局域效應，進一步讓低能量激發之準粒子的動量資訊損失，此結果即是費米能階附近光電子能譜訊號急遽衰減的原因；此外，能帶結構並不隨溫度變化一事，也指出了此系統中並沒有電荷密度波-外爾點耦合效應，此材料並非軸子絕緣體的系統。</t>
+          <t>我們與上海師範大學的Sven Ahrens教授合作設計一種新型結構化X光波導管[structured X-ray waveguide (SXWG)]，能探測地球上1毫米高度變化所引起的重力差異。根據X光通過波導管傳播行為與量子粒子行為之間的類比，我們在光學薛丁格方程式的引導下設計了SXWG，將鈧-45-碳交錯的週期性結構夾在兩個鉑包覆層之間。其中鈧-45同位素的極窄原子核鐘躍遷，其自然線寬約為2 Hz，躍遷能量約為12.4 keV。如此窄的線寬能用來檢測到鈧-45與共振X光之間在1毫米高度變化下的微小交互作用差異。因此改變SXWG的高度將因重力紅位移效應而改變兩個X光波導管模態之間的耦合強度。我們的計算結果顯示，SXWG的X光輸出光班分佈會受到高度變化的影響。故透過檢視光班的變化便能得知SXWG與X光光源之間的高度差。而使用其他同位素，如釷-229、銀-109等，甚至可以達到微米等級的靈敏度。</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Coupling Weyl quasiparticles and charge density waves (CDWs) can lead to fascinating band renormalization and many-body effects beyond band folding and Peierls gaps. For the quasi-one-dimensional chiral compound (TaSe4)2I with an incommensurate CDW transition at TC = 263 K, photoemission mappings thus far are intriguing due to suppressed emission near the Fermi level. Models for this unconventional behavior include axion insulator phases, correlation pseudogaps, polaron subbands, bipolaron bound states, etc. Our photoemission measurements show sharp quasiparticle bands crossing the Fermi level at T &gt; TC, but for T &lt; TC, these bands retain their dispersions with no Peierls or axion gaps at the Weyl points. Instead, occupied band edges recede from the Fermi level, opening a spectral gap. Our results confirm localization of quasiparticles (holes created by photoemission) is the key physics, which suppresses spectral weights over an energy window governed by incommensurate modulation and inherent phase defects of CDW.</t>
+          <t>We collaborate with Prof. Sven Ahrens from Shanghai Normal University to design a novel structured X-ray waveguide (SXWG) capable of detecting gravitational differences caused by height changes as small as 1 millimeter on Earth. Based on  an analogy between the propagation of X-rays through a waveguide and the behavior of quantum particles, we designed the SXWG under the guidance of the optical Schrödinger equation, sandwiching a periodic structure of 45Sc scandium-carbon interleaved layers between two platinum-coated layers. The scandium isotope has an extremely narrow nuclear clock transition, with a natural linewidth of about 2 Hz and a transition energy of approximately 12.4 keV. Such a narrow linewidth can be used to detect tiny interaction differences between 45Sc and resonant X-rays under a 1-millimeter height change. Thus, altering the height of the SXWG will change the coupling strength between two X-ray waveguide modes due to the gravitational redshift effect. Our calculations show that the X-ray output intensity distribution of the SXWG is affected by height changes. Therefore, by examining the changes in the light pattern, the height difference between the SXWG and the X-ray source can be determined. Using other isotopes, such as 229Th or 109Ag, can even achieve sensitivity at the micrometer level.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Figure. Sensing the difference of gravity in 1mm altitude change on Earth using an SXWG and 45Sc nuclear clock transition.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>files/research/準一維外爾半金屬材料(TaSe4)2I之電荷密度波行為.webp</t>
+          <t>files/research/替地球重力拍X光影像.webp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>磁約束核融合電漿中漂移阿爾文波偏振的測量</t>
+          <t>準一維外爾半金屬材料(TaSe4)2I之電荷密度波行為</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>PHYSICAL REVIEW LETTERS</t>
+          <t>Nano Letters 24, 8778 (2024)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Xiaodi Du, Liu Chen(陳騮), William W. Heidbrink, Michael A. Van Zeeland, Max E. Austin, Jie Chen, Yueqiang Liu, George R. McKee, and Zheng Yan</t>
+          <t>Meng-Kai Lin*, Joseph Andrew Hlevyack, Chengxi Zhao, Pavel Dudin, José Avila, Sung-Kwan Mo, Cheng-Maw Cheng, Peter Abbamonte, Daniel P. Shoemaker, and Tai-Chang Chiang*</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>First Measurement of Drift-Alfvén Wave Polarization in Magnetically Confined Fusion Plasmas</t>
+          <t>Unconventional Spectral Gaps Induced by Charge Density Waves in the Weyl Semimetal (TaSe4)2I</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/first-measurement-of-drift-alfven-wave-polarization-in-magnetically-confined-fusion-plasmas/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%ba%96%e4%b8%80%e7%b6%ad%e5%a4%96%e7%88%be%e5%8d%8a%e9%87%91%e5%b1%ac%e6%9d%90%e6%96%99tase42i%e4%b9%8b%e9%9b%bb%e8%8d%b7%e5%af%86%e5%ba%a6%e6%b3%a2%e8%a1%8c%e7%82%ba/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>漂移聲波和剪切阿爾文波是磁化電漿中的兩種基本電磁波動，它們在各種電漿成分的動力學和傳輸中都扮演著至關重要的角色。在托卡馬克核融合裝置中，這兩種波動會耦合再一起，但是到目前為止，都還沒有可靠的方法來確定觀察到的波動的相對偏振性。在這項研究工作中，我們基於迴旋動力學理論與實驗量測的電子密度和溫度，開發了一種新穎且廣泛適用的方法來確定漂移阿爾文波的極化性，並將此方法應用於 DIII-D 裝置，首次在托卡馬克裝置中提供漂移阿爾文波偏振測量。</t>
+          <t>近幾年的理論指出，若外爾半金屬(Weyl semimetal)材料同時具備電荷密度波(Charge density wave)特性，電荷密度波相量有機會與外爾費米子間耦合，形成軸子絕緣體(axion insulator)。而準一維材料(TaSe4)2I是少數符合上述特性的材料，被認為是軸子絕緣體的候選材料。然而實驗上並未能提出直接的電荷密度波-外爾點交互作用證據，原因出自於此材料在溫度低於相轉變溫度時，靠近費米能階之光電子能譜訊號會急遽衰減，導致無法解析外爾點上是否有能隙產生。對於無法解析的費米能階附近能帶結構，過往的研究提出如axion insulator phases、correlation pseudogaps、polaron subbands、bipolaron bound states等解釋，然而這些解釋都會牽涉能隙的打開或能帶結構變化。我們運用角解析光電子能譜(Angle-resolved photoemission spectroscopy, ARPES)技術重新檢視此材料系統，並發現隨著樣品溫度的變化，能帶結構並沒有任何的變化，費米能階附近能帶結構的消失，是出自於樣品進入電荷密度波的相後，因為非相稱(incommensurate)電荷密度波特性，電荷密度波的週期並不跟晶格週期匹配，導致了準粒子的局域效應，進一步讓低能量激發之準粒子的動量資訊損失，此結果即是費米能階附近光電子能譜訊號急遽衰減的原因；此外，能帶結構並不隨溫度變化一事，也指出了此系統中並沒有電荷密度波-外爾點耦合效應，此材料並非軸子絕緣體的系統。</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Drift-acoustic wave and shear Alfven wave are two fundamental electromagnetic fluctuations in magnetized plasmas. They both play crucial roles in the dynamics and transports of various components of plasmas. In fusion devices; such as tokamaks, these two waves are coupled and , up to now, there has not been a reliable technique to determine the relative polarizations of the observed fluctuations. In this work, we have, based on the gyrokinetic theory and using electron density and temperature measurements, developed a novel and widely applicable method to determine the drift-Alfven wave polarization. This technique is then applied to the DIII-D device and provides , for the first time, drift-Alfven wave polarization measurements in a tokamak device.</t>
+          <t>Coupling Weyl quasiparticles and charge density waves (CDWs) can lead to fascinating band renormalization and many-body effects beyond band folding and Peierls gaps. For the quasi-one-dimensional chiral compound (TaSe4)2I with an incommensurate CDW transition at TC = 263 K, photoemission mappings thus far are intriguing due to suppressed emission near the Fermi level. Models for this unconventional behavior include axion insulator phases, correlation pseudogaps, polaron subbands, bipolaron bound states, etc. Our photoemission measurements show sharp quasiparticle bands crossing the Fermi level at T &gt; TC, but for T &lt; TC, these bands retain their dispersions with no Peierls or axion gaps at the Weyl points. Instead, occupied band edges recede from the Fermi level, opening a spectral gap. Our results confirm localization of quasiparticles (holes created by photoemission) is the key physics, which suppresses spectral weights over an energy window governed by incommensurate modulation and inherent phase defects of CDW.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>files/research/磁約束核融合電漿中漂移阿爾文波偏振的測量.webp</t>
+          <t>files/research/準一維外爾半金屬材料(TaSe4)2I之電荷密度波行為.webp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>量子非局域性的質疑</t>
+          <t>磁約束核融合電漿中漂移阿爾文波偏振的測量</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Chin. J. Phys. 89 (2024) 1462</t>
+          <t>PHYSICAL REVIEW LETTERS</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Otto C. W. Kong</t>
+          <t>Xiaodi Du, Liu Chen(陳騮), William W. Heidbrink, Michael A. Van Zeeland, Max E. Austin, Jie Chen, Yueqiang Liu, George R. McKee, and Zheng Yan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>On Locality of Quantum Information in the Heisenberg Picture for Arbitrary States</t>
+          <t>First Measurement of Drift-Alfvén Wave Polarization in Magnetically Confined Fusion Plasmas</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%87%8f%e5%ad%90%e9%9d%9e%e5%b1%80%e5%9f%9f%e6%80%a7%e7%9a%84%e8%b3%aa%e7%96%91/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/first-measurement-of-drift-alfven-wave-polarization-in-magnetically-confined-fusion-plasmas/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>以局域性可觀測量的非交換值給出能描述不管是否在糾纏態中的量子複合系統的完整資訊</t>
+          <t>漂移聲波和剪切阿爾文波是磁化電漿中的兩種基本電磁波動，它們在各種電漿成分的動力學和傳輸中都扮演著至關重要的角色。在托卡馬克核融合裝置中，這兩種波動會耦合再一起，但是到目前為止，都還沒有可靠的方法來確定觀察到的波動的相對偏振性。在這項研究工作中，我們基於迴旋動力學理論與實驗量測的電子密度和溫度，開發了一種新穎且廣泛適用的方法來確定漂移阿爾文波的極化性，並將此方法應用於 DIII-D 裝置，首次在托卡馬克裝置中提供漂移阿爾文波偏振測量。</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Local observables with values depicting complete information in a quantum system, entangled or not.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Quantum Information in (Values of) Observables</t>
+          <t>Drift-acoustic wave and shear Alfven wave are two fundamental electromagnetic fluctuations in magnetized plasmas. They both play crucial roles in the dynamics and transports of various components of plasmas. In fusion devices; such as tokamaks, these two waves are coupled and , up to now, there has not been a reliable technique to determine the relative polarizations of the observed fluctuations. In this work, we have, based on the gyrokinetic theory and using electron density and temperature measurements, developed a novel and widely applicable method to determine the drift-Alfven wave polarization. This technique is then applied to the DIII-D device and provides , for the first time, drift-Alfven wave polarization measurements in a tokamak device.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>files/research/量子非局域性的質疑.webp</t>
+          <t>files/research/磁約束核融合電漿中漂移阿爾文波偏振的測量.webp</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>量子非局域性的質疑</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Chin. J. Phys. 89 (2024) 1462</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Otto C. W. Kong</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>On Locality of Quantum Information in the Heisenberg Picture for Arbitrary States</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%87%8f%e5%ad%90%e9%9d%9e%e5%b1%80%e5%9f%9f%e6%80%a7%e7%9a%84%e8%b3%aa%e7%96%91/</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>以局域性可觀測量的非交換值給出能描述不管是否在糾纏態中的量子複合系統的完整資訊</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Local observables with values depicting complete information in a quantum system, entangled or not.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Quantum Information in (Values of) Observables</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>files/research/量子非局域性的質疑.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>牛頓質量源於卡西米爾不變量/時間僅為哈密頓演化參數</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>Chin. J. Phys. 83 (2023) 337</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Otto C. W. Kong</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>Quantum Origin of (Newtonian) Mass and Galilean Relativity Symmetry</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%89%9b%e9%a0%93%e8%b3%aa%e9%87%8f%e6%ba%90%e6%96%bc%e5%8d%a1%e8%a5%bf%e7%b1%b3%e7%88%be%e4%b8%8d%e8%ae%8a%e9%87%8f-%e6%99%82%e9%96%93%e5%83%85%e7%82%ba%e5%93%88%e5%af%86%e9%a0%93%e6%bc%94%e5%8c%96/</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>對稱性 → 粒子質量 → 相空間 → 量子粒子動力學 → 演化時間;
 相對論應該是相空間參考系變換的對稱性</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>Symmetry → Particle mass →  Phase Space  →  Quantum Particle Dynamics  → Evolutionary Time ;
 Relativity symmetry should be reference frame transformation symmetry of phase space</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Correct Symmetry Theoretical Picture of Q.M.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>files/research/牛頓質量源於卡西米爾不變量_時間僅為哈密頓演化參數.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>量子粒子也走與質量無關的測地線</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Class. Quantum Grav. 41 (2024) 085013</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Otto C. W. Kong</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Equivalence Principle for Quantum Mechanics in the Heisenberg Picture</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%87%8f%e5%ad%90%e7%b2%92%e5%ad%90%e4%b9%9f%e8%b5%b0%e8%88%87%e8%b3%aa%e9%87%8f%e7%84%a1%e9%97%9c%e7%9a%84%e6%b8%ac%e5%9c%b0%e7%b7%9a/</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>從海森堡運動方程獲得“相對論”粒子精確的弱等價原理及瞬時自由落體框架的量子測地方程</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>An exact quantum version of Weak Equivalence Principle for a ‘relativistic’ particle. Quantum geodesic equations obtained from Heisenberg equations of motion.</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Hamiltonian Dynamics for Quantum Particle</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>files/research/量子粒子也走與質量無關的測地線.webp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>二維材料PtTe2表面的甲醇分解反應</t>
+          <t>量子粒子也走與質量無關的測地線</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nature Communications 15 (2024) 653</t>
+          <t>Class. Quantum Grav. 41 (2024) 085013</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jing-Wen Hsueh, Lai-Hsiang Kuo, Po-Han Chen, Wan-Hsin Chen, Chi-Yao Chuang, Chia-Nung Kuo, Chin-Shan Lue, Yu-Ling Lai, Bo-Hong Liu, Chia-Hsin Wang, Yao-Jane Hsu, Chun-Liang Lin,* Jyh-Pin Chou* and Meng-Fan Luo*</t>
+          <t>Otto C. W. Kong</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Investigating the role of undercoordinated Pt sites at the surface of layered PtTe2 for methanol decomposition</t>
+          <t>Equivalence Principle for Quantum Mechanics in the Heisenberg Picture</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%ba%8c%e7%b6%ad%e6%9d%90%e6%96%99ptte2%e8%a1%a8%e9%9d%a2%e7%9a%84%e7%94%b2%e9%86%87%e5%88%86%e8%a7%a3%e5%8f%8d%e6%87%89/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%87%8f%e5%ad%90%e7%b2%92%e5%ad%90%e4%b9%9f%e8%b5%b0%e8%88%87%e8%b3%aa%e9%87%8f%e7%84%a1%e9%97%9c%e7%9a%84%e6%b8%ac%e5%9c%b0%e7%b7%9a/</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>TMD二維材料因為它的二維結構能夠提供最大反應表面積卻使用最少的材料。我們發現吸附在PtTe2表面Te空缺裏低配位Pt位置上的甲醇有超過90%的反應機率。這特別的反應能力起源於低配位Pt的三角形分布與部分氧化。</t>
+          <t>從海森堡運動方程獲得“相對論”粒子精確的弱等價原理及瞬時自由落體框架的量子測地方程</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Transition metal dichalcogenides, by virtue of their two-dimensional structures, could provide the largest active surface for reactions with minimal materials consumed. We show a reaction probability &gt; 90 % for adsorbed methanol (CH3OH) on under-coordinated Pt sites at surface Te vacancies on layered PtTe2. The characteristic reactivity is attributed to both the triangular positioning and varied degrees of oxidation of the under-coordinated Pt at Te vacancies.</t>
+          <t>An exact quantum version of Weak Equivalence Principle for a ‘relativistic’ particle. Quantum geodesic equations obtained from Heisenberg equations of motion.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>具有Te空缺裏低配位Pt的PtTe2表面對甲醇分解是極優越的觸媒。被催化的甲醇分解最後產生氣態氫氣、甲醛、甲烷和水。</t>
+          <t>Hamiltonian Dynamics for Quantum Particle</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>files/research/二維材料PtTe2表面的甲醇分解反應.webp</t>
+          <t>files/research/量子粒子也走與質量無關的測地線.webp</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>在 BGGSe 晶體中產生用於非線性注入兆瓦級 CO2 放大器的高能量皮秒 10.2 微米脈衝</t>
+          <t>二維材料PtTe2表面的甲醇分解反應</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Optics Express 32, 11182–11192 (2024) (Editor’s Pick)</t>
+          <t>Nature Communications 15 (2024) 653</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ya-Po Yang, Jheng-Yu Lee, and Jyhpyng Wang</t>
+          <t>Jing-Wen Hsueh, Lai-Hsiang Kuo, Po-Han Chen, Wan-Hsin Chen, Chi-Yao Chuang, Chia-Nung Kuo, Chin-Shan Lue, Yu-Ling Lai, Bo-Hong Liu, Chia-Hsin Wang, Yao-Jane Hsu, Chun-Liang Lin,* Jyh-Pin Chou* and Meng-Fan Luo*</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Energetic picosecond 10.2-μm pulses generated in a BGGSe crystal for nonlinear seeding of terawatt-class CO2 amplifiers</t>
+          <t>Investigating the role of undercoordinated Pt sites at the surface of layered PtTe2 for methanol decomposition</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%9c%a8-bggse-%e6%99%b6%e9%ab%94%e4%b8%ad%e7%94%a2%e7%94%9f%e7%94%a8%e6%96%bc%e9%9d%9e%e7%b7%9a%e6%80%a7%e6%b3%a8%e5%85%a5%e5%85%86%e7%93%a6%e7%b4%9a-co2-%e6%94%be%e5%a4%a7%e5%99%a8%e7%9a%84/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%ba%8c%e7%b6%ad%e6%9d%90%e6%96%99ptte2%e8%a1%a8%e9%9d%a2%e7%9a%84%e7%94%b2%e9%86%87%e5%88%86%e8%a7%a3%e5%8f%8d%e6%87%89/</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>我們展示了一種產生高能量皮秒 10.2 微米脈衝的新方法，此方法基於次奈秒單頻 1338 奈米脈衝和寬頻 1540 奈米啾頻脈衝在 BGGSe 晶體中進行非線性混頻。經過光柵壓縮器壓縮後的 10.2 微米脈衝可用於注入高功率 CO2 放大器。該脈衝的能量可超過 60 微焦耳且擾動為 3.4% (方均根誤差)。由條紋相機配合克爾偏振旋轉進行單擊發脈衝寬度量測，並結合脈衝頻譜的量測，顯示該脈衝寬度在 2.7-3 皮秒之間。數值計算表明，在高氣壓 CO2 放大器中注入此高能量的種子脈衝可引起功率增寬和動態增益飽和產生的拉比翻動。藉此由 CO2 分子的梳狀光譜所導致的脈衝分裂現象可被這些非線性效應極大地抑制。經過多通 CO2 放大器之後，我們預計峰值功率可超過 1 兆瓦。</t>
+          <t>TMD二維材料因為它的二維結構能夠提供最大反應表面積卻使用最少的材料。我們發現吸附在PtTe2表面Te空缺裏低配位Pt位置上的甲醇有超過90%的反應機率。這特別的反應能力起源於低配位Pt的三角形分布與部分氧化。</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>We demonstrate a new approach to energetic picosecond 10.2-µm pulse generation. The approach is based on nonlinear mixing of subnanosecond single-frequency 1338-nm pulses and broadband 1540-nm chirped pulses in a BGGSe crystal followed by a grating compressor for seeding high-power CO2 amplifiers. Pulse energy exceeding 60 µJ with 3.4%-rms fluctuation can be routinely obtained. Single-shot pulse duration measurement, performed by Kerr polarization rotation time-resolved by a streak camera, along with the pulse spectrum, indicates the pulse duration is between 2.7-3 ps. Numerical calculations show that power broadening and dynamic gain saturation with Rabi-flopping can be induced with such an intense seed in a multi-bar CO2 amplifier. These nonlinear effects greatly suppress pulse splitting due to the comb-like spectrum of the CO2 molecule. A peak power exceeding 1 TW is expected after multipass amplification.</t>
+          <t>Transition metal dichalcogenides, by virtue of their two-dimensional structures, could provide the largest active surface for reactions with minimal materials consumed. We show a reaction probability &gt; 90 % for adsorbed methanol (CH3OH) on under-coordinated Pt sites at surface Te vacancies on layered PtTe2. The characteristic reactivity is attributed to both the triangular positioning and varied degrees of oxidation of the under-coordinated Pt at Te vacancies.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>左: 10.2 微米種子脈衝系統及提案的五通 CO2 放大器的圖示。右: 由條紋相機量測 10.2 微米脈衝的影像。</t>
+          <t>具有Te空缺裏低配位Pt的PtTe2表面對甲醇分解是極優越的觸媒。被催化的甲醇分解最後產生氣態氫氣、甲醛、甲烷和水。</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>files/research/在 BGGSe 晶體中產生用於非線性注入兆瓦級CO2放大器的高能量皮秒10.2微米脈衝.webp</t>
+          <t>files/research/二維材料PtTe2表面的甲醇分解反應.webp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>直接參考原子躍遷頻率的光梳光鐘</t>
+          <t>在 BGGSe 晶體中產生用於非線性注入兆瓦級 CO2 放大器的高能量皮秒 10.2 微米脈衝</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optics Letters 48, 2421 (2023)</t>
+          <t>Optics Express 32, 11182–11192 (2024) (Editor’s Pick)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>T. -W. Liu, B. W. Chen, H. –H. Yu and W. –Y. Cheng*</t>
+          <t>Ya-Po Yang, Jheng-Yu Lee, and Jyhpyng Wang</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>High-resolution Cs-Rb two-photon spectrometer for directly stabilizing Ti:sapphire comb laser</t>
+          <t>Energetic picosecond 10.2-μm pulses generated in a BGGSe crystal for nonlinear seeding of terawatt-class CO2 amplifiers</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%9b%b4%e6%8e%a5%e5%8f%83%e8%80%83%e5%8e%9f%e5%ad%90%e8%ba%8d%e9%81%b7%e9%a0%bb%e7%8e%87%e7%9a%84%e5%85%89%e6%a2%b3%e5%85%89%e9%90%98-2/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%9c%a8-bggse-%e6%99%b6%e9%ab%94%e4%b8%ad%e7%94%a2%e7%94%9f%e7%94%a8%e6%96%bc%e9%9d%9e%e7%b7%9a%e6%80%a7%e6%b3%a8%e5%85%a5%e5%85%86%e7%93%a6%e7%b4%9a-co2-%e6%94%be%e5%a4%a7%e5%99%a8%e7%9a%84/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>超短脈衝光梳雷射直接與銫銣原子交互作用，做成光鐘。等於用一台寬頻雷射建立十萬個光鐘並有目前文獻所知最高解析光梳光譜。為日後6G通訊所需之太空計量學重要進展。</t>
+          <t>我們展示了一種產生高能量皮秒 10.2 微米脈衝的新方法，此方法基於次奈秒單頻 1338 奈米脈衝和寬頻 1540 奈米啾頻脈衝在 BGGSe 晶體中進行非線性混頻。經過光柵壓縮器壓縮後的 10.2 微米脈衝可用於注入高功率 CO2 放大器。該脈衝的能量可超過 60 微焦耳且擾動為 3.4% (方均根誤差)。由條紋相機配合克爾偏振旋轉進行單擊發脈衝寬度量測，並結合脈衝頻譜的量測，顯示該脈衝寬度在 2.7-3 皮秒之間。數值計算表明，在高氣壓 CO2 放大器中注入此高能量的種子脈衝可引起功率增寬和動態增益飽和產生的拉比翻動。藉此由 CO2 分子的梳狀光譜所導致的脈衝分裂現象可被這些非線性效應極大地抑制。經過多通 CO2 放大器之後，我們預計峰值功率可超過 1 兆瓦。</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>100 thousand optical clocks were simultaneously developed with one femtosecond frequency comb laser. The direct comb spectroscopy for laser stabilization has the best resolution in literature . Our compact scheme is the first step toward to build up the space-borne metrology for next 6G scenario.</t>
+          <t>We demonstrate a new approach to energetic picosecond 10.2-µm pulse generation. The approach is based on nonlinear mixing of subnanosecond single-frequency 1338-nm pulses and broadband 1540-nm chirped pulses in a BGGSe crystal followed by a grating compressor for seeding high-power CO2 amplifiers. Pulse energy exceeding 60 µJ with 3.4%-rms fluctuation can be routinely obtained. Single-shot pulse duration measurement, performed by Kerr polarization rotation time-resolved by a streak camera, along with the pulse spectrum, indicates the pulse duration is between 2.7-3 ps. Numerical calculations show that power broadening and dynamic gain saturation with Rabi-flopping can be induced with such an intense seed in a multi-bar CO2 amplifier. These nonlinear effects greatly suppress pulse splitting due to the comb-like spectrum of the CO2 molecule. A peak power exceeding 1 TW is expected after multipass amplification.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>超短脈衝光梳雷射光譜﹐同時解析差40 nm的兩種原子的光譜﹐解析度高到看到量子干涉 (Dips)。</t>
+          <t>左: 10.2 微米種子脈衝系統及提案的五通 CO2 放大器的圖示。右: 由條紋相機量測 10.2 微米脈衝的影像。</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>files/research/直接參考原子躍遷頻率的光梳光鐘.webp</t>
+          <t>files/research/在 BGGSe 晶體中產生用於非線性注入兆瓦級CO2放大器的高能量皮秒10.2微米脈衝.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>高真空下的銣原子雙光子光鐘</t>
+          <t>直接參考原子躍遷頻率的光梳光鐘</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Optics Letters 48, 5984 (2023)</t>
+          <t>Optics Letters 48, 2421 (2023)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>C.-H Chu, P. C. Chang, Y. –J. Shih, D. A. Luh, M. –S Chang, T. W. Liu, Y. –T. Lin, B. W. Chen and W. –Y. Cheng</t>
+          <t>T. -W. Liu, B. W. Chen, H. –H. Yu and W. –Y. Cheng*</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Measurement of the 5S1/2 to 5D5/2 two-photon clock transition frequency of rubidium-85 in high vacuum</t>
+          <t>High-resolution Cs-Rb two-photon spectrometer for directly stabilizing Ti:sapphire comb laser</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%ab%98%e7%9c%9f%e7%a9%ba%e4%b8%8b%e7%9a%84%e9%8a%a3%e5%8e%9f%e5%ad%90%e9%9b%99%e5%85%89%e5%ad%90%e5%85%89%e9%90%98/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%9b%b4%e6%8e%a5%e5%8f%83%e8%80%83%e5%8e%9f%e5%ad%90%e8%ba%8d%e9%81%b7%e9%a0%bb%e7%8e%87%e7%9a%84%e5%85%89%e6%a2%b3%e5%85%89%e9%90%98-2/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>我們使用在本實驗室研發的量子干涉光譜製作光鐘 ﹐獨特的做法不但高解析﹐而且避免了二級光鐘常有的頻率誤差。在高真空下我們決定了銣原子光鐘的頻率﹐為文獻所知最接近原子自然躍遷頻率。</t>
+          <t>超短脈衝光梳雷射直接與銫銣原子交互作用，做成光鐘。等於用一台寬頻雷射建立十萬個光鐘並有目前文獻所知最高解析光梳光譜。為日後6G通訊所需之太空計量學重要進展。</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A quantum-interfered-spectrum based Rb optical clock in high vacuum was uniquely built, by which several systematic errors in this kind of clock were avoided. The determined transition frequency by us yields the best accuracy nearest that of the unperturbed  atomic two-photon transition, to our knowledge</t>
+          <t>100 thousand optical clocks were simultaneously developed with one femtosecond frequency comb laser. The direct comb spectroscopy for laser stabilization has the best resolution in literature . Our compact scheme is the first step toward to build up the space-borne metrology for next 6G scenario.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>實驗架設流程圖</t>
+          <t>超短脈衝光梳雷射光譜﹐同時解析差40 nm的兩種原子的光譜﹐解析度高到看到量子干涉 (Dips)。</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>files/research/高真空下的銣原子雙光子光鐘.webp</t>
+          <t>files/research/直接參考原子躍遷頻率的光梳光鐘.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>高真空下的銣原子雙光子光鐘</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Optics Letters 48, 5984 (2023)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C.-H Chu, P. C. Chang, Y. –J. Shih, D. A. Luh, M. –S Chang, T. W. Liu, Y. –T. Lin, B. W. Chen and W. –Y. Cheng</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Measurement of the 5S1/2 to 5D5/2 two-photon clock transition frequency of rubidium-85 in high vacuum</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%ab%98%e7%9c%9f%e7%a9%ba%e4%b8%8b%e7%9a%84%e9%8a%a3%e5%8e%9f%e5%ad%90%e9%9b%99%e5%85%89%e5%ad%90%e5%85%89%e9%90%98/</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>我們使用在本實驗室研發的量子干涉光譜製作光鐘 ﹐獨特的做法不但高解析﹐而且避免了二級光鐘常有的頻率誤差。在高真空下我們決定了銣原子光鐘的頻率﹐為文獻所知最接近原子自然躍遷頻率。</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>A quantum-interfered-spectrum based Rb optical clock in high vacuum was uniquely built, by which several systematic errors in this kind of clock were avoided. The determined transition frequency by us yields the best accuracy nearest that of the unperturbed  atomic two-photon transition, to our knowledge</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>實驗架設流程圖</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>files/research/高真空下的銣原子雙光子光鐘.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>Cu7PS6黃銀礦晶體之類非晶超低熱傳導行為</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>Advanced Science</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Xingchen Shen*, Niuchang Ouyang, Yuling Huang, Yung-Hsiang Tung, Chun-Chuen Yang*, Muhammad Faizan, Nicolas Perez, Ran He, Andrei Sotnikov, Kristin Willa, Chen Wang, Yue Chen*, Emmanuel Guilmeau</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>Amorphous-Like Ultralow Thermal Transport in Crystalline Argyrodite Cu7PS6</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/amorphous-like-ultralow-thermal-transport-in-crystalline-argyrodite-cu7ps6/</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>銅基與銀基的黃銀礦超離子導體晶體在超離子相變溫度附近展現出類似非晶體的超低晶格熱導率特性，引起了學術界的廣泛關注。這些材料因其獨特的熱電性能，被視為具有潛力的熱電材料候選。然而，對於其晶格熱導率的量化分析以及驅動其顯著熱電性能的微觀機制仍不充分了解。
 在本研究中，我們通過結合實驗和理論分析的方法，揭示了在銅基黃銀礦-Cu7PS6中，低能量光學聲子的存在與其超低晶格熱導率之間的關聯。研究指出，這些低能量的聲頻支透過減少聲學-光學聲子間的能量交叉，引發了強烈的聲子散射現象，從而實現了類似非晶體的超低熱導率。透過統一的熱傳導理論對熱導率進行分析，本研究成功地再現了實驗觀察到的超低晶格熱導率範圍，從0.43到0.58 W mˉ¹ Kˉ¹，在100至400 K的溫度範圍內。
@@ -1783,640 +1825,603 @@
 透過本研究的成果，我們不僅對Cu和Ag基黃銀礦超離子導體材料的低熱導率現象有了更深入的理解，同時也為開發新型高效熱電材料提供了重要的理論基礎和實驗證據。</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>Due to their amorphous-like ultralow lattice thermal conductivity both below and above the superionic phase transition, crystalline Cu- and Ag-based superionic argyrodites have garnered widespread attention as promising thermoelectric materials. However, despite their intriguing properties, quantifying their lattice thermal conductivities and a comprehensive understanding of the microscopic dynamics that drive these extraordinary properties are still lacking. Here, an integrated experimental and theoretical approach is adopted to reveal the presence of Cu-dominated low-energy optical phonons in the Cu-based argyrodite Cu7PS6. These phonons yield strong acoustic-optical phonon scattering through avoided crossing, enabling ultralow lattice thermal conductivity. The Unified Theory of thermal transport is employed to analyze heat conduction and successfully reproduce the experimental amorphous-like ultralow lattice thermal conductivities, ranging from 0.43 to 0.58 W mˉ¹ Kˉ¹, in the temperature range of 100–400 K. The study reveals that the amorphous-like ultralow thermal conductivity of Cu7PS6 stems from a significantly dominant wave-like conduction mechanism. Moreover, the simulations elucidate the wave-like thermal transport mainly results from the contribution of Cu-associated low-energy overlapping optical phonons. This study highlights the crucial role of low-energy and overlapping optical modes in facilitating amorphous-like ultralow thermal transport, providing a thorough understanding of the underlying complex dynamics of argyrodites.</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>(a) Raman spectrum and b) the calculated PDOS for Cu7PS6 at 100 K. The phonon energy of the calculated PDOS is multiplied by a factor of 1.06 for comparison. (c) The fitting profile of the Raman spectrum at 100 K. The black cross symbols represent experimental values; the blue solid line illustrates the fitted peaks, while the red solid line indicates the sum of the fitted peaks. (d) The contour temperature-dependent Raman spectrum is from 100 to 300 K, where hollow circles mark the energy positions of the fitted Raman peaks.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>files/research/Cu7PS6黃銀礦晶體之類非晶超低熱傳導行為.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>介觀尺度接觸線的雪崩與極值統計</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Phys. Rev Lett. 132, 084003</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>C. Yan, D. Guan, Y. Wang, P.Y. Lai,  H.Y. Chen, P. Tong</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Avalanches and Extreme Value Statistics of a Mesoscale Moving Contact Line</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%8b%e8%a7%80%e5%b0%ba%e5%ba%a6%e6%8e%a5%e8%a7%b8%e7%b7%9a%e7%9a%84%e9%9b%aa%e5%b4%a9%e8%88%87%e6%a5%b5%e5%80%bc%e7%b5%b1%e8%a8%88/</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>我們分析了懸掛 AFM 玻璃纖維粗糙表面上接觸線 (CL) 的黏滑動力學。，CL滑動所需的最大力 遵循極值統計，測量的 δf 遵循雪崩動力學，其冪律分佈與 Alessandro-Beatrice-Bertotti-Montorsi 模型非常一致。結果提供了介觀尺度的 CL 動力學的準確統計描述，這對於涉及隨機缺陷或粗糙度景觀中的黏滑運動的常見問題具有重要意義。</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>The pinning-depinning dynamics of a circular moving contact line (CL) over the rough surface of a micron-sized vertical hanging AFM glass fiber are analyzed.  The capillary force acting on the CL exhibits sawtooth-like fluctuations, with a linear accumulation of force of slope k (stick) followed by a sharp release of force δf, which is proportional to the CL slip length. We find that the local maximal force Fc needed for CL depinning follows the extreme value statistics and the measured δf follows the avalanche dynamics with a power law distribution in good agreement with the Alessandro-Beatrice-Bertotti-Montorsi model. The results provide an accurate statistical description of the CL dynamics at mesoscale, which has important implications to a common class of problems involving stick-slip motion in a random defect or roughness landscape.</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>左:原子力顯微鏡施力於玻璃棒與液面接觸線示意圖；右: 接觸線滑動距離分布為冪次。</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>files/research/介觀尺度接觸線的雪崩與極值統計.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>介觀尺度的黏滑摩擦統計定律</t>
+          <t>介觀尺度接觸線的雪崩與極值統計</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nature Communications 14, 6221</t>
+          <t>Phys. Rev Lett. 132, 084003</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Caishan Yan, Hsuan-Yi Chen, Pik-Yin Lai &amp; Penger Tong</t>
+          <t>C. Yan, D. Guan, Y. Wang, P.Y. Lai,  H.Y. Chen, P. Tong</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Statistical laws of stick-slip friction at mesoscale</t>
+          <t>Avalanches and Extreme Value Statistics of a Mesoscale Moving Contact Line</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%8b%e8%a7%80%e5%b0%ba%e5%ba%a6%e7%9a%84%e9%bb%8f%e6%bb%91%e6%91%a9%e6%93%a6%e7%b5%b1%e8%a8%88%e5%ae%9a%e5%be%8b/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%8b%e8%a7%80%e5%b0%ba%e5%ba%a6%e6%8e%a5%e8%a7%b8%e7%b7%9a%e7%9a%84%e9%9b%aa%e5%b4%a9%e8%88%87%e6%a5%b5%e5%80%bc%e7%b5%b1%e8%a8%88/</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>我們透過一組通用的雪崩動力學統計定律來描述黏滑摩擦。例如，觸發局部滑移所需的最大力服從廣義極值分佈，而滑移長度則透過冪律分佈很好地表徵，並解釋了冪律指數。此外，掃描探頭的黏滑運動可以想像為其質心在隨機釘扎場中移動的結果，該隨機釘扎力場由受到布朗相關釘扎力場的欠阻尼彈簧塊模型描述。本模型捕捉了黏滑摩擦的基本物理原理，為黏滑摩擦中的雪崩動力學提供了長期尋求的物理機制。</t>
+          <t>我們分析了懸掛 AFM 玻璃纖維粗糙表面上接觸線 (CL) 的黏滑動力學。，CL滑動所需的最大力 遵循極值統計，測量的 δf 遵循雪崩動力學，其冪律分佈與 Alessandro-Beatrice-Bertotti-Montorsi 模型非常一致。結果提供了介觀尺度的 CL 動力學的準確統計描述，這對於涉及隨機缺陷或粗糙度景觀中的黏滑運動的常見問題具有重要意義。</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>We demonstrated that stick-slip friction can be described by a common set of statistical laws of avalanche dynamics. The force needed to trigger the local slips obeys the generalized extreme value distribution, whereas the slip lengths are well-characterized by a power-law distribution with the power-law exponent explained as a result of the center-of-mass of a block moving in a random pinning force field described by an under-damped spring-block model subjected to a Brownian-correlated pinning force field. This model captures the essential physics of the stick-slip friction at mesoscale, providing a long-sought physical mechanism for the avalanche dynamics in stick-slip friction.</t>
+          <t>The pinning-depinning dynamics of a circular moving contact line (CL) over the rough surface of a micron-sized vertical hanging AFM glass fiber are analyzed.  The capillary force acting on the CL exhibits sawtooth-like fluctuations, with a linear accumulation of force of slope k (stick) followed by a sharp release of force δf, which is proportional to the CL slip length. We find that the local maximal force Fc needed for CL depinning follows the extreme value statistics and the measured δf follows the avalanche dynamics with a power law distribution in good agreement with the Alessandro-Beatrice-Bertotti-Montorsi model. The results provide an accurate statistical description of the CL dynamics at mesoscale, which has important implications to a common class of problems involving stick-slip motion in a random defect or roughness landscape.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(a)觸發局部滑移所需的最大力 與 (b) 不同掃描速率下的滑移長度的分布。</t>
+          <t>左:原子力顯微鏡施力於玻璃棒與液面接觸線示意圖；右: 接觸線滑動距離分布為冪次。</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>files/research/介觀尺度的黏滑摩擦統計定律.webp</t>
+          <t>files/research/介觀尺度接觸線的雪崩與極值統計.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>使慢光做迴旋運動</t>
+          <t>介觀尺度的黏滑摩擦統計定律</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Phys. Rev. Research 5, L042029</t>
+          <t>Nature Communications 14, 6221</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Yu-Hung Kuan, Shin-Yu Lee, Siang-Wei Shao, Wu-Cheng Chiang, I-Kang Liu, Julius Ruseckas, Gediminas Juzeliūnas, Yu-Ju Lin, and Wen-Te Liao</t>
+          <t>Caishan Yan, Hsuan-Yi Chen, Pik-Yin Lai &amp; Penger Tong</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Synthetic Landau levels and robust chiral edge states for dark-state polaritons in a static and scalable continuum media</t>
+          <t>Statistical laws of stick-slip friction at mesoscale</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bd%bf%e6%85%a2%e5%85%89%e5%81%9a%e8%bf%b4%e6%97%8b%e9%81%8b%e5%8b%95/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%8b%e8%a7%80%e5%b0%ba%e5%ba%a6%e7%9a%84%e9%bb%8f%e6%bb%91%e6%91%a9%e6%93%a6%e7%b5%b1%e8%a8%88%e5%ae%9a%e5%be%8b/</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>一般來說電中性粒子無法感受到電磁場所產生的Lorentz力。我們與立陶宛Vilnius大學、英國Newcastle大學及IAMS 合作提出利用電磁誘發透明替電中性暗態激極子產生等效磁場。我們更進一步展示如何產生並操控處於Landau能階及堅固手徵性邊界態的二維暗態激極子。我們利用光學方法在實驗室坐標系中產生的合成磁場具有可擴展性，且Aharonov-Bohm相位是在連續介質中產生，而非一般具晶格結構的拓樸材料。 我們的系統能作為多功能量子模擬器、動態可控光子線路和拓樸光量子態產生器。</t>
+          <t>我們透過一組通用的雪崩動力學統計定律來描述黏滑摩擦。例如，觸發局部滑移所需的最大力服從廣義極值分佈，而滑移長度則透過冪律分佈很好地表徵，並解釋了冪律指數。此外，掃描探頭的黏滑運動可以想像為其質心在隨機釘扎場中移動的結果，該隨機釘扎力場由受到布朗相關釘扎力場的欠阻尼彈簧塊模型描述。本模型捕捉了黏滑摩擦的基本物理原理，為黏滑摩擦中的雪崩動力學提供了長期尋求的物理機制。</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>We collaborate with Vilnius university, Newcastle university, and IAMS to demonstrate the generation and dynamical control of synthetic Landau levels and robust chiral edge states for neutral dark-state polaritons using electromagnetically induced transparency in our theoretical studies. We adopt an optical approach to produce synthetic magnetic fields for dark-state polaritons in the static laboratory frame. In our scalable system, an Aharonov-Bohm phase is obtained along a closed loop in a continuous material rather than a sophisticated lattice structure. Our scheme paves the way toward versatile quantum simulators, dynamically controllable photonic circuits, and generators for exotic states of light carrying topological winding numbers.</t>
+          <t>We demonstrated that stick-slip friction can be described by a common set of statistical laws of avalanche dynamics. The force needed to trigger the local slips obeys the generalized extreme value distribution, whereas the slip lengths are well-characterized by a power-law distribution with the power-law exponent explained as a result of the center-of-mass of a block moving in a random pinning force field described by an under-damped spring-block model subjected to a Brownian-correlated pinning force field. This model captures the essential physics of the stick-slip friction at mesoscale, providing a long-sought physical mechanism for the avalanche dynamics in stick-slip friction.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Figure. The evolution of (a) initially rightward dark state polariton (DSP) entering the medium at (x, y) = ( -2mm, 0). The subsequent snapshot at 0.2ms of the DSP edge state by (b) out-of-plane and (c)(d) into-plane synthetic magnetic field turned on at 0.038ms. In (d) the DSP bypasses the vacuum area illustrated by the white dashed square.</t>
+          <t>(a)觸發局部滑移所需的最大力 與 (b) 不同掃描速率下的滑移長度的分布。</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>files/research/使慢光做迴旋運動.webp</t>
+          <t>files/research/介觀尺度的黏滑摩擦統計定律.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>原行星盤中的手搖杯</t>
+          <t>使慢光做迴旋運動</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Astrophysical Journal, 926, 176 (2022)</t>
+          <t>Phys. Rev. Research 5, L042029</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>A. Jiménez-Escobar*, A. Ciaravella, C. Cecchi-Pestellini, G. M. Muñoz Caro, C.-H. Huang, N.-E. Sie, Y.-J. Chen*</t>
+          <t>Yu-Hung Kuan, Shin-Yu Lee, Siang-Wei Shao, Wu-Cheng Chiang, I-Kang Liu, Julius Ruseckas, Gediminas Juzeliūnas, Yu-Ju Lin, and Wen-Te Liao</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>X-ray induced diffusion and mixing in layered astrophysical ices</t>
+          <t>Synthetic Landau levels and robust chiral edge states for dark-state polaritons in a static and scalable continuum media</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%8e%9f%e8%a1%8c%e6%98%9f%e7%9b%a4%e4%b8%ad%e7%9a%84%e6%89%8b%e6%90%96%e6%9d%af/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bd%bf%e6%85%a2%e5%85%89%e5%81%9a%e8%bf%b4%e6%97%8b%e9%81%8b%e5%8b%95/</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>在極低溫的天文環境中，由於不同分子的固化溫度不同，因此冰晶結構被預期應該呈現極性與非極性的雙層結構。先固化的極性冰晶主要由水、甲烷、氨所組成，而覆蓋在上層的非極性冰晶以一氧化碳分子為主要元素，在氫化作用後形成由一氧化碳與甲醇所組成的混合冰晶。我們的研究結果顯示，在X光的作用下誘發雙層結構冰晶中的分子發生了長距離的擴散現象，進而造成上下層冰晶分子的混合破壞了層狀結構，而這樣的混合現象將大大提昇有機複雜分子的生成機會。</t>
+          <t>一般來說電中性粒子無法感受到電磁場所產生的Lorentz力。我們與立陶宛Vilnius大學、英國Newcastle大學及IAMS 合作提出利用電磁誘發透明替電中性暗態激極子產生等效磁場。我們更進一步展示如何產生並操控處於Landau能階及堅固手徵性邊界態的二維暗態激極子。我們利用光學方法在實驗室坐標系中產生的合成磁場具有可擴展性，且Aharonov-Bohm相位是在連續介質中產生，而非一般具晶格結構的拓樸材料。 我們的系統能作為多功能量子模擬器、動態可控光子線路和拓樸光量子態產生器。</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ice in cold cosmic environments is expected to be organized in a bilayered structure of polar and apolar components. The initial water-rich layer is embedded in an icy CO envelope, which provides the feedstock for methanol formation through hydrogenation. These two components are thought to be physically segregated, unless an increase in temperature favors mobility and reactivity within the ice. We present new and robust evidence of X-ray-induced diffusion within interstellar ice analogues at very low temperatures, leading to an efficient mixing of the molecular content of the ice. The results of our study have two main implications. First, molecular mixing enhances chemical reactions from which complex organic species, including many of prebiotic interest, are formed. Second, diffusion drives the desorption of species that would otherwise remain buried near the surface of dust, thus enhancing their abundances in the gas, where they can be detected in the radio-wave domain. Such a scenario may have implications for the chemical history of ices in protoplanetary disks, in particular in the early stages of their life.</t>
+          <t>We collaborate with Vilnius university, Newcastle university, and IAMS to demonstrate the generation and dynamical control of synthetic Landau levels and robust chiral edge states for neutral dark-state polaritons using electromagnetically induced transparency in our theoretical studies. We adopt an optical approach to produce synthetic magnetic fields for dark-state polaritons in the static laboratory frame. In our scalable system, an Aharonov-Bohm phase is obtained along a closed loop in a continuous material rather than a sophisticated lattice structure. Our scheme paves the way toward versatile quantum simulators, dynamically controllable photonic circuits, and generators for exotic states of light carrying topological winding numbers.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Figure. A bilayered ice accreted onto a CaF2 window (sample) is irradiated by soft X-rays (yellow vertical cylinder). During the irradiation, species produced in the bottom layer diffuse within the top layer (mobility), allowing blending and chemical reactions among species of the two layers (mixing), and possibly release into the gas phase (desorption).</t>
+          <t>Figure. The evolution of (a) initially rightward dark state polariton (DSP) entering the medium at (x, y) = ( -2mm, 0). The subsequent snapshot at 0.2ms of the DSP edge state by (b) out-of-plane and (c)(d) into-plane synthetic magnetic field turned on at 0.038ms. In (d) the DSP bypasses the vacuum area illustrated by the white dashed square.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>files/research/原行星盤中的手搖杯.webp</t>
+          <t>files/research/使慢光做迴旋運動.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>原行星盤中的手搖杯</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Astrophysical Journal, 926, 176 (2022)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>A. Jiménez-Escobar*, A. Ciaravella, C. Cecchi-Pestellini, G. M. Muñoz Caro, C.-H. Huang, N.-E. Sie, Y.-J. Chen*</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>X-ray induced diffusion and mixing in layered astrophysical ices</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%8e%9f%e8%a1%8c%e6%98%9f%e7%9b%a4%e4%b8%ad%e7%9a%84%e6%89%8b%e6%90%96%e6%9d%af/</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>在極低溫的天文環境中，由於不同分子的固化溫度不同，因此冰晶結構被預期應該呈現極性與非極性的雙層結構。先固化的極性冰晶主要由水、甲烷、氨所組成，而覆蓋在上層的非極性冰晶以一氧化碳分子為主要元素，在氫化作用後形成由一氧化碳與甲醇所組成的混合冰晶。我們的研究結果顯示，在X光的作用下誘發雙層結構冰晶中的分子發生了長距離的擴散現象，進而造成上下層冰晶分子的混合破壞了層狀結構，而這樣的混合現象將大大提昇有機複雜分子的生成機會。</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ice in cold cosmic environments is expected to be organized in a bilayered structure of polar and apolar components. The initial water-rich layer is embedded in an icy CO envelope, which provides the feedstock for methanol formation through hydrogenation. These two components are thought to be physically segregated, unless an increase in temperature favors mobility and reactivity within the ice. We present new and robust evidence of X-ray-induced diffusion within interstellar ice analogues at very low temperatures, leading to an efficient mixing of the molecular content of the ice. The results of our study have two main implications. First, molecular mixing enhances chemical reactions from which complex organic species, including many of prebiotic interest, are formed. Second, diffusion drives the desorption of species that would otherwise remain buried near the surface of dust, thus enhancing their abundances in the gas, where they can be detected in the radio-wave domain. Such a scenario may have implications for the chemical history of ices in protoplanetary disks, in particular in the early stages of their life.</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Figure. A bilayered ice accreted onto a CaF2 window (sample) is irradiated by soft X-rays (yellow vertical cylinder). During the irradiation, species produced in the bottom layer diffuse within the top layer (mobility), allowing blending and chemical reactions among species of the two layers (mixing), and possibly release into the gas phase (desorption).</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>files/research/原行星盤中的手搖杯.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>在X光錐形波導管中產生原子核瞬時居量反轉</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>Phys. Rev. Research 4, L032007 (2022)</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Yu-Hsueh Chen, Po-Han Lin, Guan-Ying Wang, Adriana Pálffy, &amp; Wen-Te Liao</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Transient nuclear inversion by X-Ray Free Electron Laser in a tapered x-ray waveguide</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%9c%a8x%e5%85%89%e9%8c%90%e5%bd%a2%e6%b3%a2%e5%b0%8e%e7%ae%a1%e4%b8%ad%e7%94%a2%e7%94%9f%e5%8e%9f%e5%ad%90%e6%a0%b8%e7%9e%ac%e6%99%82%e5%b1%85%e9%87%8f%e5%8f%8d%e8%bd%89/</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>本工作表明將原子核樣本放置在X光錐形波導的焦點處，聚焦的 X 光自由電子雷射(XFEL)可以產生同調地產生瞬時原子核居量反轉。用高原子序的包覆材料(如鉑)所製成的橢圓X光波導管可以聚焦X光使其強度比入口端大800倍左右。此功能可用於驅動原子核Mössbauer躍遷並達到原子核瞬時居量反轉。本工作還證明儘管在XFEL相干時間≤10fs 的參數區域中，仍可產生高達約 2×10^5 顆原子核處於激發態。此結果展示了錐形波導在 X 光量子光學領域中的重要作用。本工作和製造gamma射線雷射或原子核電池的應用息息相關。</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>This work show that transient nuclear population inversion can be coherently generated by a focused x-ray free electron laser pulse in a tapered waveguide where a nuclear sample is placed at the focal point.
 We theoretically show that elliptical waveguides using a cladding material with a high atomic number, such as platinum, can maintain an x-ray intensity of up to three orders of magnitude larger than in free space. This feature can be used to place a nuclear sample in the waveguide focal area and drive nuclear Mössbauer transitions up to transient nuclear population inversion. The latter is a long-standing goal related to gamma-ray lasers or nuclear state population control for energy storage. We show that inverted nuclei numbers of up to approximately 2×10^5 are achievable in the realistic region of longitudinal x-ray-free-electron-laser coherence time ≤ 10fs. Our results anticipate the important role of tapered x-ray waveguides and strategically embedded samples in the field of x-ray quantum optics.</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Figure. (a) Axial x-ray intensity for 14.4 keV x-ray propagation in a Pt-cladding elliptical waveguide (EWG). (b) Spatial distribution of 57Fe nuclear inversion (NI) driven by a focused XFEL. The maximum NI for 133Ba, 57Fe, 187Os, and 169Tm is depicted as a function of the photon number per pulse in a (c) platinum- (d) silicon-cladding EWG.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>files/research/在X光錐形波導管中產生原子核瞬時居量反轉.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>利用原子核磁旋轉及Fano共振增強X光</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Physical Review Applied 18, L051001</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Po-Han Lin, Yu-Hung Kuan, Yen-Yu Fu, &amp; Wen-Te Liao</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Time-Delayed Magnetic Control of X-ray Spectral Enhancement in Two-Target Nuclear Forward Scattering</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%88%a9%e7%94%a8%e5%8e%9f%e5%ad%90%e6%a0%b8%e7%a3%81%e6%97%8b%e8%bd%89%e5%8f%8afano%e5%85%b1%e6%8c%af%e5%a2%9e%e5%bc%b7x%e5%85%89/</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>X光的核共振散射是探測凝聚態物理動力學和結構的重要方法。 由於同步輻射脈衝的帶寬比靶材中Mössbauer同位素的線寬大上好幾個數量級，因此入射的共振X 光光子數非常小。 這項工作建議使用磁開關來控制非共振背景 X光和共振散射信號之間的干涉，並通過Fano共振增強輸出X光強度達10倍。 本方案適用於現有的同步輻射光束線來製造一個更亮的X光源，並進一步增加原子核散射X光精密光譜學的訊雜比。</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Nuclear resonant scattering of x rays is an important method to probe the dynamics and structure of condensed matter. As the bandwidth of a synchrotron-radiation pulse is much broader than the linewidth of Mössbauer isotopes in a target, the resonant fraction of the incident x-ray photons is extremely tiny. This work proposes using magnetic switching to control the interference between the off-resonant background x rays and the resonant scattered signal, for enhancement of the output intensity via Fano resonance. This scheme points toward a bright, flexible x-ray source for precision spectroscopy utilizing modern synchrotrons.</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Figure. Output x-ray spectrum for single (blue dashed line), 50 (red dashed-dotted-filled line), and without (black solid line) magnetic switching. Green long-dashed line depicts the theoretic maximum spectrum.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>files/research/利用原子核磁旋轉及Fano共振增強X光.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>硒分子吸附於雙層石墨稀之迪拉克錐複製效應</t>
+          <t>利用原子核磁旋轉及Fano共振增強X光</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>npj 2D Materials and Applications</t>
+          <t>Physical Review Applied 18, L051001</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Meng-Kai Lin, Jun Zhao , Joseph A. Hlevyack, and T.-C. Chiang</t>
+          <t>Po-Han Lin, Yu-Hung Kuan, Yen-Yu Fu, &amp; Wen-Te Liao</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>硒分子吸附於雙層石墨稀之迪拉克錐複製效應</t>
+          <t>Time-Delayed Magnetic Control of X-ray Spectral Enhancement in Two-Target Nuclear Forward Scattering</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a1%92%e5%88%86%e5%ad%90%e5%90%b8%e9%99%84%e6%96%bc%e9%9b%99%e5%b1%a4%e7%9f%b3%e5%a2%a8%e7%a8%80%e4%b9%8b%e8%bf%aa%e6%8b%89%e5%85%8b%e9%8c%90%e8%a4%87%e8%a3%bd%e6%95%88%e6%87%89/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%88%a9%e7%94%a8%e5%8e%9f%e5%ad%90%e6%a0%b8%e7%a3%81%e6%97%8b%e8%bd%89%e5%8f%8afano%e5%85%b1%e6%8c%af%e5%a2%9e%e5%bc%b7x%e5%85%89/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>石墨烯是最廣為人知的迪拉克材料。其中迪拉克錐的線性能帶結構讓材料展現出特殊的電子特性，並在電子元件的應用上非常有價值。於本研究中，我們藉由蒸鍍硒於雙層石墨烯上，發現硒分子於低溫時會藉由物理吸附於雙層石墨稀上，並進一步形成有序結構，此有序結構因為良好的對稱性，將石墨烯的迪拉克錐反折到能帶結構的對稱中心。此研究提出了運用材料界面間微弱的凡德瓦作用調控表面電子結構的新穎機制。</t>
+          <t>X光的核共振散射是探測凝聚態物理動力學和結構的重要方法。 由於同步輻射脈衝的帶寬比靶材中Mössbauer同位素的線寬大上好幾個數量級，因此入射的共振X 光光子數非常小。 這項工作建議使用磁開關來控制非共振背景 X光和共振散射信號之間的干涉，並通過Fano共振增強輸出X光強度達10倍。 本方案適用於現有的同步輻射光束線來製造一個更亮的X光源，並進一步增加原子核散射X光精密光譜學的訊雜比。</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Graphene is a well-known Dirac material. The linear dispersive electronic bands of Dirac cone can foster extraordinary electronic effects, and it is thus of importance in electronic applications. In this work, we show that adsorption of selenium (Se) vapor on bilayer graphene creates a symmetric hybrid clone of the Dirac cones at the zone center at low temperature. The finding illustrates a method to generate electronic features of scientific and technological interests by gentle surface modification via van der Waals adsorption.</t>
+          <t>Nuclear resonant scattering of x rays is an important method to probe the dynamics and structure of condensed matter. As the bandwidth of a synchrotron-radiation pulse is much broader than the linewidth of Mössbauer isotopes in a target, the resonant fraction of the incident x-ray photons is extremely tiny. This work proposes using magnetic switching to control the interference between the off-resonant background x rays and the resonant scattered signal, for enhancement of the output intensity via Fano resonance. This scheme points toward a bright, flexible x-ray source for precision spectroscopy utilizing modern synchrotrons.</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Figure. Output x-ray spectrum for single (blue dashed line), 50 (red dashed-dotted-filled line), and without (black solid line) magnetic switching. Green long-dashed line depicts the theoretic maximum spectrum.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>files/research/硒分子吸附於雙層石墨稀之迪拉克錐複製效應.webp</t>
+          <t>files/research/利用原子核磁旋轉及Fano共振增強X光.webp</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>透過分形維度和熵分析評估斑馬魚在暴露於二十種抗生素後的運動複雜性</t>
+          <t>硒分子吸附於雙層石墨稀之迪拉克錐複製效應</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Antibiotics</t>
+          <t>npj 2D Materials and Applications</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Michael Edbert Suryanto, Chun-Chuen Yang, Gilbert Audira, Ross D. Vasquez, Marri Jmelou M. Roldan, Tzong-Rong Ger, Chung-Der Hsiao</t>
+          <t>Meng-Kai Lin, Jun Zhao , Joseph A. Hlevyack, and T.-C. Chiang</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Evaluation of Locomotion Complexity in Zebrafish after Exposure to Twenty Antibiotics by Fractal Dimension and Entropy Analysis</t>
+          <t>硒分子吸附於雙層石墨稀之迪拉克錐複製效應</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/evaluation-of-locomotion-complexity-in-zebrafish-after-exposure-to-twenty-antibiotics-by-fractal-dimension-and-entropy-analysis/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a1%92%e5%88%86%e5%ad%90%e5%90%b8%e9%99%84%e6%96%bc%e9%9b%99%e5%b1%a4%e7%9f%b3%e5%a2%a8%e7%a8%80%e4%b9%8b%e8%bf%aa%e6%8b%89%e5%85%8b%e9%8c%90%e8%a4%87%e8%a3%bd%e6%95%88%e6%87%89/</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>抗生素廣泛用於水產養殖，以防止細菌感染和疾病傳播。一些抗生素在水中的半衰期相對較長，可能會對目標魚類產生一些不利影響。本研究通過表型方法在行為水平上分析了抗生素對斑馬魚的潛在不利影響。在急性暴露於濃度為 100 ppb 的 20 種不同抗生素 10 天后，我們對成年斑馬魚進行了三維 (3D) 運動跟踪。通過分形維數和排列熵分析對它們的運動複雜性進行了分析和比較。通過結合從行為端點改變收集的數據來執行降維方法。主成分和層次分析得出的結論是，三種抗生素：阿莫西林、甲氧芐啶和泰樂菌素，表現出獨特的特徵。在後續研究中觀察到這三種抗生素在較低濃度（1 和 10 ppb）下的作用。根據結果，這些抗生素可以引發成年斑馬魚的一些行為改變，即使是低劑量也是如此。運動行為活動的顯著變化，如總距離活動、平均速度、快速運動時間、角速度、頂部/底部持續時間和蜿蜒運動與神經運動障礙、焦慮水平和壓力反應高度相關。這項研究提供了基於體內實驗的證據，以支持應仔細處理某些抗生素的使用這一觀點，因為它們會引起魚類行為改變的顯著影響。</t>
+          <t>石墨烯是最廣為人知的迪拉克材料。其中迪拉克錐的線性能帶結構讓材料展現出特殊的電子特性，並在電子元件的應用上非常有價值。於本研究中，我們藉由蒸鍍硒於雙層石墨烯上，發現硒分子於低溫時會藉由物理吸附於雙層石墨稀上，並進一步形成有序結構，此有序結構因為良好的對稱性，將石墨烯的迪拉克錐反折到能帶結構的對稱中心。此研究提出了運用材料界面間微弱的凡德瓦作用調控表面電子結構的新穎機制。</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Antibiotics are extensively used in aquaculture to prevent bacterial infection and the spread of diseases. Some antibiotics have a relatively longer half-life in water and may induce some adverse effects on the targeted fish species. This study analyzed the potential adverse effects of antibiotics in zebrafish at the behavioral level by a phenomic approach. We conducted three-dimensional (3D) locomotion tracking for adult zebrafish after acute exposure to twenty different antibiotics at a concentration of 100 ppb for 10 days. Their locomotor complexity was analyzed and compared by fractal dimension and permutation entropy analysis. The dimensionality reduction method was performed by combining the data gathered from behavioral endpoints alteration. Principal component and hierarchical analysis conclude that three antibiotics: amoxicillin, trimethoprim, and tylosin, displayed unique characteristics. The effects of these three antibiotics at lower concentrations (1 and 10 ppb) were observed in a follow-up study. Based on the results, these antibiotics can trigger several behavioral alterations in adult zebrafish, even in low doses. Significant changes in locomotor behavioral activity, such as total distance activity, average speed, rapid movement time, angular velocity, time in top/bottom duration, and meandering movement are highly related to neurological motor impairments, anxiety levels, and stress responses were observed. This study provides evidence based on an in vivo experiment to support the idea that the usage of some antibiotics should be carefully addressed since they can induce a significant effect of behavioral alterations in fish.</t>
+          <t>Graphene is a well-known Dirac material. The linear dispersive electronic bands of Dirac cone can foster extraordinary electronic effects, and it is thus of importance in electronic applications. In this work, we show that adsorption of selenium (Se) vapor on bilayer graphene creates a symmetric hybrid clone of the Dirac cones at the zone center at low temperature. The finding illustrates a method to generate electronic features of scientific and technological interests by gentle surface modification via van der Waals adsorption.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>files/research/透過分形維度和熵分析評估斑馬魚在暴露於二十種抗生素後的運動複雜性.webp</t>
+          <t>files/research/硒分子吸附於雙層石墨稀之迪拉克錐複製效應.webp</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>台灣軸子偵測實驗室TASEH首波物理結果- 尋找質量為 19.6 微電子伏特的軸子暗物質</t>
+          <t>透過分形維度和熵分析評估斑馬魚在暴露於二十種抗生素後的運動複雜性</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PHYSICAL REVIEW LETTERS</t>
+          <t>Antibiotics</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hsin Chang, Jing-Yang Chang, Yi-Chieh Chang, Yu-Han Chang, Yuan-Hann Chang, Chien-Han Chen, Ching-Fang Chen, Kuan-Yu Chen, Yung-Fu Chen, Wei-Yuan Chiang, Wei-Chen Chien, Hien Thi Doan, Wei-Cheng Hung, Watson Kuo, Shou-Bai Lai, Han-Wen Liu, Min-Wei OuYang, Ping-I Wu, and Shin-Shan Yu (TASEH Collaboration)</t>
+          <t>Michael Edbert Suryanto, Chun-Chuen Yang, Gilbert Audira, Ross D. Vasquez, Marri Jmelou M. Roldan, Tzong-Rong Ger, Chung-Der Hsiao</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>First Results from the Taiwan Axion Search Experiment with a Haloscope at 19.6 μ eV</t>
+          <t>Evaluation of Locomotion Complexity in Zebrafish after Exposure to Twenty Antibiotics by Fractal Dimension and Entropy Analysis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%8f%b0%e7%81%a3%e8%bb%b8%e5%ad%90%e5%81%b5%e6%b8%ac%e5%af%a6%e9%a9%97%e5%ae%a4taseh%e9%a6%96%e6%b3%a2%e7%89%a9%e7%90%86%e7%b5%90%e6%9e%9c-%e5%b0%8b%e6%89%be%e8%b3%aa%e9%87%8f%e7%82%ba-19-6/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/evaluation-of-locomotion-complexity-in-zebrafish-after-exposure-to-twenty-antibiotics-by-fractal-dimension-and-entropy-analysis/</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>軸子為熱門的暗物質候選人之一。在外加強磁場的影響之下，軸子有機會轉換成光子。如果偵測器裡的微波共振腔共振頻率對應到了光子頻率，經過低噪放大器的放大信號，我們有機會探測到軸子的存在。台灣軸子偵測實驗室(TASEH)用在2021年10月13日至11月15日所取的數據，尋找了軸子暗物質。我們的結果排除了軸子-雙光子耦合常數大於8.1 x 10-14 GeV-1的理論模型。在19.4687 至19.7639微電子伏特這個質量範圍，我們對理論模型的敏感度比之前實驗還要好三個數量級。</t>
+          <t>抗生素廣泛用於水產養殖，以防止細菌感染和疾病傳播。一些抗生素在水中的半衰期相對較長，可能會對目標魚類產生一些不利影響。本研究通過表型方法在行為水平上分析了抗生素對斑馬魚的潛在不利影響。在急性暴露於濃度為 100 ppb 的 20 種不同抗生素 10 天后，我們對成年斑馬魚進行了三維 (3D) 運動跟踪。通過分形維數和排列熵分析對它們的運動複雜性進行了分析和比較。通過結合從行為端點改變收集的數據來執行降維方法。主成分和層次分析得出的結論是，三種抗生素：阿莫西林、甲氧芐啶和泰樂菌素，表現出獨特的特徵。在後續研究中觀察到這三種抗生素在較低濃度（1 和 10 ppb）下的作用。根據結果，這些抗生素可以引發成年斑馬魚的一些行為改變，即使是低劑量也是如此。運動行為活動的顯著變化，如總距離活動、平均速度、快速運動時間、角速度、頂部/底部持續時間和蜿蜒運動與神經運動障礙、焦慮水平和壓力反應高度相關。這項研究提供了基於體內實驗的證據，以支持應仔細處理某些抗生素的使用這一觀點，因為它們會引起魚類行為改變的顯著影響。</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>One of the viable dark matter candidates is the axion. An axion in an external magnetic field can convert to an equal-energy photon. The converted photons can be accumulated in a cavity with a matched resonant frequency and subsequently be detected by a low-noise linear amplifier. The Taiwan Axion Search Experiment with a Haloscope (TASEH) has performed a search for axions, using the data collected from October 13, 2021 to November 15, 2021. The results of TASEH excludes models with the axion-two-photon coupling |gaγγ|8.1 x 10-14 GeV-1. It is the first time that a haloscope experiment places constraints in the mass region of 19.4687 &lt; ma &lt; 19.7639 μeV, reaching a sensitivity 3 orders of magnitude better than the limits obtained by nonhaloscope experiments.</t>
+          <t>Antibiotics are extensively used in aquaculture to prevent bacterial infection and the spread of diseases. Some antibiotics have a relatively longer half-life in water and may induce some adverse effects on the targeted fish species. This study analyzed the potential adverse effects of antibiotics in zebrafish at the behavioral level by a phenomic approach. We conducted three-dimensional (3D) locomotion tracking for adult zebrafish after acute exposure to twenty different antibiotics at a concentration of 100 ppb for 10 days. Their locomotor complexity was analyzed and compared by fractal dimension and permutation entropy analysis. The dimensionality reduction method was performed by combining the data gathered from behavioral endpoints alteration. Principal component and hierarchical analysis conclude that three antibiotics: amoxicillin, trimethoprim, and tylosin, displayed unique characteristics. The effects of these three antibiotics at lower concentrations (1 and 10 ppb) were observed in a follow-up study. Based on the results, these antibiotics can trigger several behavioral alterations in adult zebrafish, even in low doses. Significant changes in locomotor behavioral activity, such as total distance activity, average speed, rapid movement time, angular velocity, time in top/bottom duration, and meandering movement are highly related to neurological motor impairments, anxiety levels, and stress responses were observed. This study provides evidence based on an in vivo experiment to support the idea that the usage of some antibiotics should be carefully addressed since they can induce a significant effect of behavioral alterations in fish.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>files/research/台灣軸子偵測實驗室TASEH首波物理結果3.webp</t>
+          <t>files/research/透過分形維度和熵分析評估斑馬魚在暴露於二十種抗生素後的運動複雜性.webp</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>掃描探針於單層過渡金屬硫化物之能隙調控</t>
+          <t>台灣軸子偵測實驗室TASEH首波物理結果- 尋找質量為 19.6 微電子伏特的軸子暗物質</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ACS Nano</t>
+          <t>PHYSICAL REVIEW LETTERS</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Meng-Kai Lin, Guan-Hao Chen, Ciao-Lin Ho, Wei-Chen Chueh, Joseph Andrew Hlevyack, Chia-Nung Kuo, Tsu-Yi Fu, Juhn-Jong Lin, Chin Shan Lue, Wen-Hao Chang, Noriaki Takagi, Ryuichi Arafune, Tai-Chang Chiang, and Chun-Liang Lin</t>
+          <t>Hsin Chang, Jing-Yang Chang, Yi-Chieh Chang, Yu-Han Chang, Yuan-Hann Chang, Chien-Han Chen, Ching-Fang Chen, Kuan-Yu Chen, Yung-Fu Chen, Wei-Yuan Chiang, Wei-Chen Chien, Hien Thi Doan, Wei-Cheng Hung, Watson Kuo, Shou-Bai Lai, Han-Wen Liu, Min-Wei OuYang, Ping-I Wu, and Shin-Shan Yu (TASEH Collaboration)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>掃描探針於單層過渡金屬硫化物之能隙調控</t>
+          <t>First Results from the Taiwan Axion Search Experiment with a Haloscope at 19.6 μ eV</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%8e%83%e6%8f%8f%e6%8e%a2%e9%87%9d%e6%96%bc%e5%96%ae%e5%b1%a4%e9%81%8e%e6%b8%a1%e9%87%91%e5%b1%ac%e7%a1%ab%e5%8c%96%e7%89%a9%e4%b9%8b%e8%83%bd%e9%9a%99%e8%aa%bf%e6%8e%a7/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%8f%b0%e7%81%a3%e8%bb%b8%e5%ad%90%e5%81%b5%e6%b8%ac%e5%af%a6%e9%a9%97%e5%ae%a4taseh%e9%a6%96%e6%b3%a2%e7%89%a9%e7%90%86%e7%b5%90%e6%9e%9c-%e5%b0%8b%e6%89%be%e8%b3%aa%e9%87%8f%e7%82%ba-19-6/</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>單層材料的物理特性與調控機制解明是做為新穎電子元件設計的基石，本研究由中央大學物理系林孟凱教授、陽明交通大學林俊良教授與美國伊利諾大學江台章院士主導。我們透過掃描穿遂顯微術/電子譜比較單層的MoS2和PtTe2材料電子結構隨穿遂電流的響應，發現單層MoS2的能隙隨著穿遂電流增加呈現指數遞減；反之PtTe2單層則隨著穿遂電流增加，展現出半導體-金屬電性轉變行為，且是一個可逆過程。藉由理論輔助，我們提出單層過渡金屬硫化物電性調控的兩個機制，分別為電場驅動響應(MoS2)以及電子態混成(PtTe2)的作用。此研究將在電子元件的電性調控上有著重要意義。</t>
+          <t>軸子為熱門的暗物質候選人之一。在外加強磁場的影響之下，軸子有機會轉換成光子。如果偵測器裡的微波共振腔共振頻率對應到了光子頻率，經過低噪放大器的放大信號，我們有機會探測到軸子的存在。台灣軸子偵測實驗室(TASEH)用在2021年10月13日至11月15日所取的數據，尋找了軸子暗物質。我們的結果排除了軸子-雙光子耦合常數大於8.1 x 10-14 GeV-1的理論模型。在19.4687 至19.7639微電子伏特這個質量範圍，我們對理論模型的敏感度比之前實驗還要好三個數量級。</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Physical properties of monolayer materials are keys of developing novel electronic devices. The research project leading by Prof. Meng-Kai Lin (NCU), Prof. Chun-Liang Lin (NYCU), and Prof. Tai-Chang Chiang (UIUC) discovers two mechanisms of fulfilling bandgap engineering in transition metal dichalcogenides down to monolayers by scanning tunneling microscopy/spectroscopy. Bandgap reduction with increasing tunneling current in the tip-MoS2 system suggests an electric-field-induced gap renormalization effect. By contrast, a reversible semiconductor-to-metal transition occurs at a moderate tunneling current in the tip-PtTe2 system suggests an electronic coupling in between the electronic states of tip and PtTe2 film. The finding is of significant implications regarding methods and the principles for bandgap engineering of monolayer transition metal dichalcogenides.</t>
+          <t>One of the viable dark matter candidates is the axion. An axion in an external magnetic field can convert to an equal-energy photon. The converted photons can be accumulated in a cavity with a matched resonant frequency and subsequently be detected by a low-noise linear amplifier. The Taiwan Axion Search Experiment with a Haloscope (TASEH) has performed a search for axions, using the data collected from October 13, 2021 to November 15, 2021. The results of TASEH excludes models with the axion-two-photon coupling |gaγγ|8.1 x 10-14 GeV-1. It is the first time that a haloscope experiment places constraints in the mass region of 19.4687 &lt; ma &lt; 19.7639 μeV, reaching a sensitivity 3 orders of magnitude better than the limits obtained by nonhaloscope experiments.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>files/research/掃描探針於單層過渡金屬硫化物之能隙調控.webp</t>
+          <t>files/research/台灣軸子偵測實驗室TASEH首波物理結果3.webp</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>地球內部物質在系外行星內部超高壓之複雜相變</t>
+          <t>掃描探針於單層過渡金屬硫化物之能隙調控</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nat. Commun. 13, 2780 (2022)</t>
+          <t>ACS Nano</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Han Hsu &amp; Koichiro Umemoto</t>
+          <t>Meng-Kai Lin, Guan-Hao Chen, Ciao-Lin Ho, Wei-Chen Chueh, Joseph Andrew Hlevyack, Chia-Nung Kuo, Tsu-Yi Fu, Juhn-Jong Lin, Chin Shan Lue, Wen-Hao Chang, Noriaki Takagi, Ryuichi Arafune, Tai-Chang Chiang, and Chun-Liang Lin</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Structural transition and re-emergence of iron's total electron spin in (Mg,Fe)O at ultrahigh pressure</t>
+          <t>掃描探針於單層過渡金屬硫化物之能隙調控</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%9c%b0%e7%90%83%e5%85%a7%e9%83%a8%e7%89%a9%e8%b3%aa%e5%9c%a8%e7%b3%bb%e5%a4%96%e8%a1%8c%e6%98%9f%e5%85%a7%e9%83%a8%e8%b6%85%e9%ab%98%e5%a3%93%e4%b9%8b%e8%a4%87%e9%9b%9c%e7%9b%b8%e8%ae%8a/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e6%8e%83%e6%8f%8f%e6%8e%a2%e9%87%9d%e6%96%bc%e5%96%ae%e5%b1%a4%e9%81%8e%e6%b8%a1%e9%87%91%e5%b1%ac%e7%a1%ab%e5%8c%96%e7%89%a9%e4%b9%8b%e8%83%bd%e9%9a%99%e8%aa%bf%e6%8e%a7/</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>中央大學物理系徐翰教授主導國際合作，以第一原理計算探討 (Mg,Fe)O 在超高壓力下的物理性質，闡明 (Mg,Fe)O 在系外行星內部極端條件下所發生的結構、電子自旋態、以及金屬–絕緣體相變。其計算結果顯示：鐵及自旋態轉變，可顯著影響系外行星之內部性質，且影響壓力範圍巨大。</t>
+          <t>單層材料的物理特性與調控機制解明是做為新穎電子元件設計的基石，本研究由中央大學物理系林孟凱教授、陽明交通大學林俊良教授與美國伊利諾大學江台章院士主導。我們透過掃描穿遂顯微術/電子譜比較單層的MoS2和PtTe2材料電子結構隨穿遂電流的響應，發現單層MoS2的能隙隨著穿遂電流增加呈現指數遞減；反之PtTe2單層則隨著穿遂電流增加，展現出半導體-金屬電性轉變行為，且是一個可逆過程。藉由理論輔助，我們提出單層過渡金屬硫化物電性調控的兩個機制，分別為電場驅動響應(MoS2)以及電子態混成(PtTe2)的作用。此研究將在電子元件的電性調控上有著重要意義。</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Via DFT calculations, Prof. Han Hsu and colleagues showed that (Mg,Fe)O, a major constituent of terrestrial exoplanets, undergoes complicated structural, spin, and metal–insulator transitions at ultrahigh pressure, significantly affecting the properties of exoplanet interiors.</t>
+          <t>Physical properties of monolayer materials are keys of developing novel electronic devices. The research project leading by Prof. Meng-Kai Lin (NCU), Prof. Chun-Liang Lin (NYCU), and Prof. Tai-Chang Chiang (UIUC) discovers two mechanisms of fulfilling bandgap engineering in transition metal dichalcogenides down to monolayers by scanning tunneling microscopy/spectroscopy. Bandgap reduction with increasing tunneling current in the tip-MoS2 system suggests an electric-field-induced gap renormalization effect. By contrast, a reversible semiconductor-to-metal transition occurs at a moderate tunneling current in the tip-PtTe2 system suggests an electronic coupling in between the electronic states of tip and PtTe2 film. The finding is of significant implications regarding methods and the principles for bandgap engineering of monolayer transition metal dichalcogenides.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>files/research/地球內部物質在系外行星內部超高壓之複雜相變.webp</t>
+          <t>files/research/掃描探針於單層過渡金屬硫化物之能隙調控.webp</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A POSSIBLE NEW DECAY MODE OF THE HIGGS BOSON</t>
+          <t>地球內部物質在系外行星內部超高壓之複雜相變</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CERN Accelerating science</t>
+          <t>Nat. Commun. 13, 2780 (2022)</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CMS Collaboration</t>
+          <t>Han Hsu &amp; Koichiro Umemoto</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>A POSSIBLE NEW DECAY MODE OF THE HIGGS BOSON</t>
+          <t>Structural transition and re-emergence of iron's total electron spin in (Mg,Fe)O at ultrahigh pressure</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/a-possible-new-decay-mode-of-the-higgs-boson/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e5%9c%b0%e7%90%83%e5%85%a7%e9%83%a8%e7%89%a9%e8%b3%aa%e5%9c%a8%e7%b3%bb%e5%a4%96%e8%a1%8c%e6%98%9f%e5%85%a7%e9%83%a8%e8%b6%85%e9%ab%98%e5%a3%93%e4%b9%8b%e8%a4%87%e9%9b%9c%e7%9b%b8%e8%ae%8a/</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>中央大學物理系徐翰教授主導國際合作，以第一原理計算探討 (Mg,Fe)O 在超高壓力下的物理性質，闡明 (Mg,Fe)O 在系外行星內部極端條件下所發生的結構、電子自旋態、以及金屬–絕緣體相變。其計算結果顯示：鐵及自旋態轉變，可顯著影響系外行星之內部性質，且影響壓力範圍巨大。</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>CMS Collaboration study on a possible new decay mode of the Higgs boson.</t>
+          <t>Via DFT calculations, Prof. Han Hsu and colleagues showed that (Mg,Fe)O, a major constituent of terrestrial exoplanets, undergoes complicated structural, spin, and metal–insulator transitions at ultrahigh pressure, significantly affecting the properties of exoplanet interiors.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>files/research/HIGGS_BOSON.webp</t>
+          <t>files/research/地球內部物質在系外行星內部超高壓之複雜相變.webp</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>碳三-氬凡德瓦爾分子的電子激發態角彎曲振動態的振動初分解研究</t>
+          <t>A POSSIBLE NEW DECAY MODE OF THE HIGGS BOSON</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Journal of Chemical Physics</t>
+          <t>CERN Accelerating science</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Yi-Jen Wang and  Yen-Chu Hsu</t>
+          <t>CMS Collaboration</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Vibrational predissociation in the bending levels of the Ã state of C3Ar</t>
+          <t>A POSSIBLE NEW DECAY MODE OF THE HIGGS BOSON</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a2%b3%e4%b8%89-%e6%b0%ac%e5%87%a1%e5%be%b7%e7%93%a6%e7%88%be%e5%88%86%e5%ad%90%e7%9a%84%e9%9b%bb%e5%ad%90%e6%bf%80%e7%99%bc%e6%85%8b%e8%a7%92%e5%bd%8e%e6%9b%b2%e6%8c%af%e5%8b%95%e6%85%8b%e7%9a%84/</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>從16個碳三-氬凡德瓦爾分子的譜帶中觀察得振動初分解現象並可歸納出兩種形式。其中一種振動初分解現象-碳三碎片的振動能高且振動態符合|Δv| = 1, |ΔP| = 1的規則，P是碳三的電振角動量。另一種，碳三碎片的振動能低。振動初分解並不遵守軌域角動量守恆。所觀察的|ΔP|的規則可以偶極誘發偶極模型解釋。大部分的碎片振動態分布不符合間隙定理，我們認為這些振動初分解發生於臨界且涉及振動模的變動，這些現象未曾在間隙定理裡考慮過。</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/a-possible-new-decay-mode-of-the-higgs-boson/</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Vibrational predissociation (VP) has been observed in 16 。bands of the C3Ar van der Waals complex. Two types of VP processes have been recognized. The first type gives rise to vibrationally hot C3 fragments, mostly following |Δv| = 1, |ΔP| = 1 propensity rules, where P is the vibronic angular momentum of C3. The second type gives vibrationally cooled fragments. Although the initial states are associated with both orbital components of the C3 (Ã), most of the VP fragments belong to the lower orbital component. A dipole-induced dipole model has been used to interpret the observed ΔP- propensities. It is interesting that majority of the VP product distribution do not follow the gap law, we attributed it to the threshold predissociation and mode changing predissociation, which has not been considered in the model of gap law.</t>
+          <t>CMS Collaboration study on a possible new decay mode of the Higgs boson.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>files/research/碳三-氬凡德瓦爾分子的電子激發態角彎曲振動態的振動初分解研究.webp</t>
+          <t>files/research/HIGGS_BOSON.webp</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GWTC-3目錄和O3b觀測結果發表</t>
+          <t>碳三-氬凡德瓦爾分子的電子激發態角彎曲振動態的振動初分解研究</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LIGO Caltech</t>
+          <t>The Journal of Chemical Physics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Yuki Inoue</t>
+          <t>Yi-Jen Wang and  Yen-Chu Hsu</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>GWTC-3 Catalog and O3b Bulk Strain Data Release</t>
+          <t>Vibrational predissociation in the bending levels of the Ã state of C3Ar</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/gwtc-3%e7%9b%ae%e9%8c%84%e5%92%8co3b%e8%a7%80%e6%b8%ac%e7%b5%90%e6%9e%9c%e7%99%bc%e8%a1%a8-gwtc-3-catalog-and-o3b-bulk-strain-data-release/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a2%b3%e4%b8%89-%e6%b0%ac%e5%87%a1%e5%be%b7%e7%93%a6%e7%88%be%e5%88%86%e5%ad%90%e7%9a%84%e9%9b%bb%e5%ad%90%e6%bf%80%e7%99%bc%e6%85%8b%e8%a7%92%e5%bd%8e%e6%9b%b2%e6%8c%af%e5%8b%95%e6%85%8b%e7%9a%84/</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>從16個碳三-氬凡德瓦爾分子的譜帶中觀察得振動初分解現象並可歸納出兩種形式。其中一種振動初分解現象-碳三碎片的振動能高且振動態符合|Δv| = 1, |ΔP| = 1的規則，P是碳三的電振角動量。另一種，碳三碎片的振動能低。振動初分解並不遵守軌域角動量守恆。所觀察的|ΔP|的規則可以偶極誘發偶極模型解釋。大部分的碎片振動態分布不符合間隙定理，我們認為這些振動初分解發生於臨界且涉及振動模的變動，這些現象未曾在間隙定理裡考慮過。</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>GWTC-3 catalog and O3b bulk strain data release from LIGO-Virgo-KAGRA gravitational wave detectors.</t>
+          <t>Vibrational predissociation (VP) has been observed in 16 。bands of the C3Ar van der Waals complex. Two types of VP processes have been recognized. The first type gives rise to vibrationally hot C3 fragments, mostly following |Δv| = 1, |ΔP| = 1 propensity rules, where P is the vibronic angular momentum of C3. The second type gives vibrationally cooled fragments. Although the initial states are associated with both orbital components of the C3 (Ã), most of the VP fragments belong to the lower orbital component. A dipole-induced dipole model has been used to interpret the observed ΔP- propensities. It is interesting that majority of the VP product distribution do not follow the gap law, we attributed it to the threshold predissociation and mode changing predissociation, which has not been considered in the model of gap law.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>files/research/GWTC-3目錄和O3b觀測結果發表.webp</t>
+          <t>files/research/碳三-氬凡德瓦爾分子的電子激發態角彎曲振動態的振動初分解研究.webp</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GWTC-3, 第三個重力波訊號源目錄</t>
+          <t>GWTC-3目錄和O3b觀測結果發表</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LSC</t>
+          <t>LIGO Caltech</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2426,798 +2431,835 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>GWTC-3, 第三個重力波訊號源目錄</t>
+          <t>GWTC-3 Catalog and O3b Bulk Strain Data Release</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/gwtc-3-%e7%ac%ac%e4%b8%89%e5%80%8b%e9%87%8d%e5%8a%9b%e6%b3%a2%e8%a8%8a%e8%99%9f%e6%ba%90%e7%9b%ae%e9%8c%84/</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>GWTC-3 (the 3rd Gravitational-Wave Transient Catalog)是重力波偵測器LIGO, Virgo與KAGRA所收集的第三個重力波訊號源目錄。 GWTC-3額外增加了從2019年11月到2020年3月中重力波偵測器在第三次聯合觀測後半段（簡稱O3b）所偵測到的重力波事件。GWTC-3象徵著重力波觀測至今所累積的最完整目錄。</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/gwtc-3%e7%9b%ae%e9%8c%84%e5%92%8co3b%e8%a7%80%e6%b8%ac%e7%b5%90%e6%9e%9c%e7%99%bc%e8%a1%a8-gwtc-3-catalog-and-o3b-bulk-strain-data-release/</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>GWTC-3 is the third gravitational-wave source catalog collected by LIGO, Virgo, and KAGRA detectors, adding events from O3b (Nov 2019 - Mar 2020), representing the most complete gravitational wave catalog to date.</t>
+          <t>GWTC-3 catalog and O3b bulk strain data release from LIGO-Virgo-KAGRA gravitational wave detectors.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>files/research/GWTC-3_第三個重力波訊號源目錄.webp</t>
+          <t>files/research/GWTC-3目錄和O3b觀測結果發表.webp</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Underlying mechanism for exchange bias in single-molecule magnetic junctions</t>
+          <t>GWTC-3, 第三個重力波訊號源目錄</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Phys. Rev. Research 3, 033264</t>
+          <t>LSC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yu-Hui Tang*, Bao-Huei Huang</t>
+          <t>Yuki Inoue</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Underlying mechanism for exchange bias in single-molecule magnetic junctions</t>
+          <t>GWTC-3, 第三個重力波訊號源目錄</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/underlying-mechanism-for-exchange-bias-in-single-molecule-magnetic-junctions/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/gwtc-3-%e7%ac%ac%e4%b8%89%e5%80%8b%e9%87%8d%e5%8a%9b%e6%b3%a2%e8%a8%8a%e8%99%9f%e6%ba%90%e7%9b%ae%e9%8c%84/</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>我們結合第一原理計算以及由中央大學物理系自主開發的磁電傳輸計算程序（DFT+JunPy+LLG），成功預測在單分子磁性接面中的交換偏移效應，同時，其磁翻轉特性不但可以透過外加電流，亦可通過拉伸應變來操控。透過緊束模型的分析，發現其決定性因素是由分子/磁性電極所提供的介面自旋選擇特性。我們相信這個新開發的DFT+JunPy+LLG計算方法可以有效幫助次世代多重調控且節能的自旋傳輸元件之設計與開發。</t>
+          <t>GWTC-3 (the 3rd Gravitational-Wave Transient Catalog)是重力波偵測器LIGO, Virgo與KAGRA所收集的第三個重力波訊號源目錄。 GWTC-3額外增加了從2019年11月到2020年3月中重力波偵測器在第三次聯合觀測後半段（簡稱O3b）所偵測到的重力波事件。GWTC-3象徵著重力波觀測至今所累積的最完整目錄。</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Magnetic proximity has been observed in a variety of solid-state magnetic devices, but has been less discussed at the molecular scale. In this study, the magnetotransport calculation is carried out using the generalized Landau-Lifshitz-Gilbert (LLG) equation combined with density functional theory (DFT) and our self-developed junpy calculated spin-torque effect. Except for the current driven spin torque, which is a promising approach for magnetization switch in magnetic random access memory, the equilibrium field-like spin torque also plays a crucial role in the strain-controlled exchange bias with current-controlled magnetic coercivity in single-molecule magnetic junctions. The tight-binding model is further employed to clarify the critical role of the interfacial spin filter effect arising from the hybridization between the linker and Co apex. These multidisciplinary DFT+JunPy+LLG results may provide important and practical implications in the dual control of magnetic proximity and magnetization switching in molecular spintronics at low temperature, either by tensile strain or via smaller applied current density of the order of MA/cm2.</t>
+          <t>GWTC-3 is the third gravitational-wave source catalog collected by LIGO, Virgo, and KAGRA detectors, adding events from O3b (Nov 2019 - Mar 2020), representing the most complete gravitational wave catalog to date.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>files/research/Underlying_mechanism.webp</t>
+          <t>files/research/GWTC-3_第三個重力波訊號源目錄.webp</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>能量電子對於一氧化碳冰晶的衍化作用</t>
+          <t>Underlying mechanism for exchange bias in single-molecule magnetic junctions</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Astrophy. J., 889, 57 (2020)</t>
+          <t>Phys. Rev. Research 3, 033264</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>C.-H. Huang, A. Ciaravella, C. Cecchi-Pestellini, A. Jiménez-Escobar, L.-C. Hsiao, C.-C. Huang, P.-C. Chen, N.-E. Sie, and Y.-J. Chen</t>
+          <t>Yu-Hui Tang*, Bao-Huei Huang</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Effects of 150–1000 eV Electron Impacts on Pure Carbon Monoxide Ices Using the Interstellar Energetic-Process System (IEPS)</t>
+          <t>Underlying mechanism for exchange bias in single-molecule magnetic junctions</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%83%bd%e9%87%8f%e9%9b%bb%e5%ad%90%e5%b0%8d%e6%96%bc%e4%b8%80%e6%b0%a7%e5%8c%96%e7%a2%b3%e5%86%b0%e6%99%b6%e7%9a%84%e8%a1%8d%e5%8c%96%e4%bd%9c%e7%94%a8/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/underlying-mechanism-for-exchange-bias-in-single-molecule-magnetic-junctions/</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>在實驗室中透過電子束照射一氧化碳冰晶發現大量的碳長鏈和長鏈碳氧化物在冰晶中生成。此結果可以類比海衛一與冥王星上季節性的揮發性物質如氮氣、甲烷與一氧化碳在冬季時凝華成冰帽受到如太陽風或大氣宇宙射線作用產生一次電子的粒子在極地撞擊冰晶，並驅使著揮發性物質所形成的冰塊中進行化學反應。這些長鏈化合物會在夏季進入大氣，透過光化反應形成碳氮化合物增加大氣中的化學複雜度。</t>
+          <t>我們結合第一原理計算以及由中央大學物理系自主開發的磁電傳輸計算程序（DFT+JunPy+LLG），成功預測在單分子磁性接面中的交換偏移效應，同時，其磁翻轉特性不但可以透過外加電流，亦可通過拉伸應變來操控。透過緊束模型的分析，發現其決定性因素是由分子/磁性電極所提供的介面自旋選擇特性。我們相信這個新開發的DFT+JunPy+LLG計算方法可以有效幫助次世代多重調控且節能的自旋傳輸元件之設計與開發。</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Laboratory simulation shows that amount of long-chain carbons and suboxides are formed in CO ice irradiated by electrons. This result can simulate Triton and Pluto’ s atmosphere including volatile species such as nitrogen, methane, and carbon monoxide condensation during the winter. These ice cap irradiated by solar wind or/and primary electron produced by cosmic ray at polar can drive chemical evolution in the ice. Long-chain carbons and suboxides are introduced into nitrogen-rich atmosphere during summer, and form carbon and nitrogen compound increasing the complicity in the atmosphere through photochemical reactions.</t>
+          <t>Magnetic proximity has been observed in a variety of solid-state magnetic devices, but has been less discussed at the molecular scale. In this study, the magnetotransport calculation is carried out using the generalized Landau-Lifshitz-Gilbert (LLG) equation combined with density functional theory (DFT) and our self-developed junpy calculated spin-torque effect. Except for the current driven spin torque, which is a promising approach for magnetization switch in magnetic random access memory, the equilibrium field-like spin torque also plays a crucial role in the strain-controlled exchange bias with current-controlled magnetic coercivity in single-molecule magnetic junctions. The tight-binding model is further employed to clarify the critical role of the interfacial spin filter effect arising from the hybridization between the linker and Co apex. These multidisciplinary DFT+JunPy+LLG results may provide important and practical implications in the dual control of magnetic proximity and magnetization switching in molecular spintronics at low temperature, either by tensile strain or via smaller applied current density of the order of MA/cm2.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>files/research/能量電子對於一氧化碳冰晶的衍化作用.webp</t>
+          <t>files/research/Underlying_mechanism.webp</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>X射線對於太空中複雜有機分子生成的影響</t>
+          <t>能量電子對於一氧化碳冰晶的衍化作用</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Astrophy. J., 879, 21 (2019)</t>
+          <t>Astrophy. J., 889, 57 (2020)</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>A. Ciaravella, A. Jiménez-Escobar, C. Cecchi-Pestellini, C. H. Huang, N. E. Sie, G. M. Muñoz Caro, and Y. J. Chen</t>
+          <t>C.-H. Huang, A. Ciaravella, C. Cecchi-Pestellini, A. Jiménez-Escobar, L.-C. Hsiao, C.-C. Huang, P.-C. Chen, N.-E. Sie, and Y.-J. Chen</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>The American Astronomical Society, find out more     The Institute of Physics, find out more    Synthesis of Complex Organic Molecules in Soft X-Ray Irradiated Ices</t>
+          <t>Effects of 150–1000 eV Electron Impacts on Pure Carbon Monoxide Ices Using the Interstellar Energetic-Process System (IEPS)</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/x%e5%b0%84%e7%b7%9a%e5%b0%8d%e6%96%bc%e5%a4%aa%e7%a9%ba%e4%b8%ad%e8%a4%87%e9%9b%9c%e6%9c%89%e6%a9%9f%e5%88%86%e5%ad%90%e7%94%9f%e6%88%90%e7%9a%84%e5%bd%b1%e9%9f%bf/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%83%bd%e9%87%8f%e9%9b%bb%e5%ad%90%e5%b0%8d%e6%96%bc%e4%b8%80%e6%b0%a7%e5%8c%96%e7%a2%b3%e5%86%b0%e6%99%b6%e7%9a%84%e8%a1%8d%e5%8c%96%e4%bd%9c%e7%94%a8/</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>透過紅外光譜和質譜的量測發現，許多複雜有機分子可經由X射線照射之水、一氧化碳，以及氨的混和冰晶中產生，如異氰酸甲酯(CH3NCO)、甲酰胺(HCONH2)和甘氨酸(C2H5NO2)。這些含氮分子皆曾在宇宙當中的原恆星、原行星盤等被觀測到，且這些物質為形成天文生物學中相當感興趣的糖和氨基酸的基礎分子。因此，X射線對於研究生命的起源是相當好的方法之一。</t>
+          <t>在實驗室中透過電子束照射一氧化碳冰晶發現大量的碳長鏈和長鏈碳氧化物在冰晶中生成。此結果可以類比海衛一與冥王星上季節性的揮發性物質如氮氣、甲烷與一氧化碳在冬季時凝華成冰帽受到如太陽風或大氣宇宙射線作用產生一次電子的粒子在極地撞擊冰晶，並驅使著揮發性物質所形成的冰塊中進行化學反應。這些長鏈化合物會在夏季進入大氣，透過光化反應形成碳氮化合物增加大氣中的化學複雜度。</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>From the experiments of X-ray irradiated H2O:CO:NH3 ice mixtures, numerous complex organic molecules are observed on IR spectra during X-ray irradiation of H2O:CO:NH3 ice mixtures such as methyl isocyanate (CH3NCO), formamide (HCONH2), and glycine (C2H5NO2). These N-bearing molecules also detected in the region of low-mass solar type protostellar binary, protoplanetary disk, as well as hot cores, which can be the basis for astrobiological interest as sugars and amino acids. Hence, X-ray irradiation has a potential role in prebiotic chemistry.</t>
+          <t>Laboratory simulation shows that amount of long-chain carbons and suboxides are formed in CO ice irradiated by electrons. This result can simulate Triton and Pluto’ s atmosphere including volatile species such as nitrogen, methane, and carbon monoxide condensation during the winter. These ice cap irradiated by solar wind or/and primary electron produced by cosmic ray at polar can drive chemical evolution in the ice. Long-chain carbons and suboxides are introduced into nitrogen-rich atmosphere during summer, and form carbon and nitrogen compound increasing the complicity in the atmosphere through photochemical reactions.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>files/research/X射線對於太空中複雜有機分子生成的影響.webp</t>
+          <t>files/research/能量電子對於一氧化碳冰晶的衍化作用.webp</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Group Theoretical Approach to Pseudo-Hermitian Quantum Mechanics with Lorentz Covariance and c → (infinity) Limit</t>
+          <t>X射線對於太空中複雜有機分子生成的影響</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Symmetry 13, 22 (2021)</t>
+          <t>Astrophy. J., 879, 21 (2019)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Suzana Bedic, Otto C. W. Kong, and Hock King Ting</t>
+          <t>A. Ciaravella, A. Jiménez-Escobar, C. Cecchi-Pestellini, C. H. Huang, N. E. Sie, G. M. Muñoz Caro, and Y. J. Chen</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Group Theoretical Approach to Pseudo-Hermitian Quantum Mechanics with Lorentz Covariance and c → (infinity) Limit</t>
+          <t>The American Astronomical Society, find out more     The Institute of Physics, find out more    Synthesis of Complex Organic Molecules in Soft X-Ray Irradiated Ices</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/group-theoretical-approach-to-pseudo-hermitian-quantum-mechanics-with-lorentz-covariance-and-c-%e2%86%92-infinity-limit-2/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/x%e5%b0%84%e7%b7%9a%e5%b0%8d%e6%96%bc%e5%a4%aa%e7%a9%ba%e4%b8%ad%e8%a4%87%e9%9b%9c%e6%9c%89%e6%a9%9f%e5%88%86%e5%ad%90%e7%94%9f%e6%88%90%e7%9a%84%e5%bd%b1%e9%9f%bf/</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>我們用對稱理論方法寫下了具有 Minkowski度量算符子的新“相對論”量子力學，並且完美地嵌入了“非相對論”理論。它帶有一個量子Minkowski時空的非交換幾何圖像。</t>
+          <t>透過紅外光譜和質譜的量測發現，許多複雜有機分子可經由X射線照射之水、一氧化碳，以及氨的混和冰晶中產生，如異氰酸甲酯(CH3NCO)、甲酰胺(HCONH2)和甘氨酸(C2H5NO2)。這些含氮分子皆曾在宇宙當中的原恆星、原行星盤等被觀測到，且這些物質為形成天文生物學中相當感興趣的糖和氨基酸的基礎分子。因此，X射線對於研究生命的起源是相當好的方法之一。</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>We give a symmetry theoretical formulation of a new 'relativistic' quantum mechanics with a Minkowski metric operator and a perfect embedding of the 'nonrelativistic' theory. It carries a noncommutative geometric picture of quantum Minkowski spacetime.</t>
+          <t>From the experiments of X-ray irradiated H2O:CO:NH3 ice mixtures, numerous complex organic molecules are observed on IR spectra during X-ray irradiation of H2O:CO:NH3 ice mixtures such as methyl isocyanate (CH3NCO), formamide (HCONH2), and glycine (C2H5NO2). These N-bearing molecules also detected in the region of low-mass solar type protostellar binary, protoplanetary disk, as well as hot cores, which can be the basis for astrobiological interest as sugars and amino acids. Hence, X-ray irradiation has a potential role in prebiotic chemistry.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>files/research/Group_Theoretical_Approach.webp</t>
+          <t>files/research/X射線對於太空中複雜有機分子生成的影響.webp</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Shift a laser beam back and forth to exchange heat and work in thermodynamics</t>
+          <t>Group Theoretical Approach to Pseudo-Hermitian Quantum Mechanics with Lorentz Covariance and c → (infinity) Limit</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Scientific Reports 11, 4394 (2021)</t>
+          <t>Symmetry 13, 22 (2021)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>John A. C. Albay, Zhi-Yi Zhou, Cheng-Hung Chang, and Yonggun Jun</t>
+          <t>Suzana Bedic, Otto C. W. Kong, and Hock King Ting</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Shift a laser beam back and forth to exchange heat and work in thermodynamics</t>
+          <t>Group Theoretical Approach to Pseudo-Hermitian Quantum Mechanics with Lorentz Covariance and c → (infinity) Limit</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/shift-a-laser-beam-back-and-forth-to-exchange-heat-and-work-in-thermodynamics-2/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/group-theoretical-approach-to-pseudo-hermitian-quantum-mechanics-with-lorentz-covariance-and-c-%e2%86%92-infinity-limit-2/</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>許多長期、基本的熱及功相關的微觀"Gedankenexperiment (思想實驗)" 仍未被探索，部分原因是缺乏快速和高度精確的實驗技術來調節微觀世界中的溫度和位能。我們提供了一種有力的方法，透過移動單個鐳射束同時控制位能和溫度，並演示了各種熱力學過程和微觀熱機。這項技術將為檢驗這一領域的不同理論思想鋪平道路。</t>
+          <t>我們用對稱理論方法寫下了具有 Minkowski度量算符子的新“相對論”量子力學，並且完美地嵌入了“非相對論”理論。它帶有一個量子Minkowski時空的非交換幾何圖像。</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Many long-standing, fundamental heat- and work-related microscopic ‘Gedankenexperiment’ remain unexplored, partly due to the lack of swift and highly precise experimental techniques to adjust temperature and potentials in the microscopic world. We provided a powerful method to simultaneously control potentials and temperature by shifting a single laser beam and demonstrated various thermodynamic processes and microscopic heat engines. This technique will pave the new way for the test of diverse theoretical ideas in this field.</t>
+          <t>We give a symmetry theoretical formulation of a new 'relativistic' quantum mechanics with a Minkowski metric operator and a perfect embedding of the 'nonrelativistic' theory. It carries a noncommutative geometric picture of quantum Minkowski spacetime.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>files/research/Shift_a_laser_beam.webp</t>
+          <t>files/research/Group_Theoretical_Approach.webp</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>鐵的電子自旋態會不會影響地球深部碳循環？</t>
+          <t>Shift a laser beam back and forth to exchange heat and work in thermodynamics</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Phys. Rev. B 103, 054401 (2021)</t>
+          <t>Scientific Reports 11, 4394 (2021)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Han Hsu, Christian P. Crisostomo, Wenzhong Wang, and Zhongqing Wu</t>
+          <t>John A. C. Albay, Zhi-Yi Zhou, Cheng-Hung Chang, and Yonggun Jun</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Anomalous thermal properties and spin crossover of ferromagnesite (Mg,Fe)  CO 3</t>
+          <t>Shift a laser beam back and forth to exchange heat and work in thermodynamics</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%90%b5%e7%9a%84%e9%9b%bb%e5%ad%90%e8%87%aa%e6%97%8b%e6%85%8b%e6%9c%83%e4%b8%8d%e6%9c%83%e5%bd%b1%e9%9f%bf%e5%9c%b0%e7%90%83%e6%b7%b1%e9%83%a8%e7%a2%b3%e5%be%aa%e7%92%b0%ef%bc%9f/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/shift-a-laser-beam-back-and-forth-to-exchange-heat-and-work-in-thermodynamics-2/</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>一般相信，含鐵碳酸鎂 (Mg,Fe)CO3 是下地函的主要攜碳礦物，且此礦物中的鐵在下地函的溫度壓力下會發生自旋態轉變。物理系徐翰教授研究團隊近期的計算結果顯示：伴隨著鐵自旋態轉變，含鐵碳酸鎂的種種熱力學性質 (密度、熱膨脹、彈性、比熱、熱傳導等) 會發生劇烈的異常變化，可能進一步影響地球深部碳循環。</t>
+          <t>許多長期、基本的熱及功相關的微觀"Gedankenexperiment (思想實驗)" 仍未被探索，部分原因是缺乏快速和高度精確的實驗技術來調節微觀世界中的溫度和位能。我們提供了一種有力的方法，透過移動單個鐳射束同時控制位能和溫度，並演示了各種熱力學過程和微觀熱機。這項技術將為檢驗這一領域的不同理論思想鋪平道路。</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Ferromagnesite (Mg,Fe)CO3 is believed to enter the Earth’s lower mantle via subduction and is considered a major carbon carrier in the Earth’s lower mantle, playing a key role in the Earth’s deep carbon cycle. Experiments have shown that ferromagnesite undergoes a pressure-induced spin crossover in the lower-mantle pressure range. A recent computational work done by Prof. Han Hsu’s group has indicated that nearly all thermal properties of ferromagnesite are drastically altered by iron spin crossover, including anomalous reduction of volume, anomalous softening of bulk modulus, and anomalous increases of thermal expansion, heat capacity, and the Grüneisen parameter. Remarkably, the anomaly of heat capacity remains prominent at high temperature without smearing out, which suggests that iron spin crossover may significantly affect the thermal properties of subducting slabs and the Earth’s deep carbon cycle. See further details in Hsu et al., Phys. Rev. B 103, 054401 (2021).</t>
+          <t>Many long-standing, fundamental heat- and work-related microscopic ‘Gedankenexperiment’ remain unexplored, partly due to the lack of swift and highly precise experimental techniques to adjust temperature and potentials in the microscopic world. We provided a powerful method to simultaneously control potentials and temperature by shifting a single laser beam and demonstrated various thermodynamic processes and microscopic heat engines. This technique will pave the new way for the test of diverse theoretical ideas in this field.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>files/research/鐵的電子自旋態會不會影響地球深部碳循環.webp</t>
+          <t>files/research/Shift_a_laser_beam.webp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>鐵的電子自旋態會不會影響地球深部碳循環？</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Phys. Rev. B 103, 054401 (2021)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Han Hsu, Christian P. Crisostomo, Wenzhong Wang, and Zhongqing Wu</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Anomalous thermal properties and spin crossover of ferromagnesite (Mg,Fe)  CO 3</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%90%b5%e7%9a%84%e9%9b%bb%e5%ad%90%e8%87%aa%e6%97%8b%e6%85%8b%e6%9c%83%e4%b8%8d%e6%9c%83%e5%bd%b1%e9%9f%bf%e5%9c%b0%e7%90%83%e6%b7%b1%e9%83%a8%e7%a2%b3%e5%be%aa%e7%92%b0%ef%bc%9f/</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>一般相信，含鐵碳酸鎂 (Mg,Fe)CO3 是下地函的主要攜碳礦物，且此礦物中的鐵在下地函的溫度壓力下會發生自旋態轉變。物理系徐翰教授研究團隊近期的計算結果顯示：伴隨著鐵自旋態轉變，含鐵碳酸鎂的種種熱力學性質 (密度、熱膨脹、彈性、比熱、熱傳導等) 會發生劇烈的異常變化，可能進一步影響地球深部碳循環。</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Ferromagnesite (Mg,Fe)CO3 is believed to enter the Earth’s lower mantle via subduction and is considered a major carbon carrier in the Earth’s lower mantle, playing a key role in the Earth’s deep carbon cycle. Experiments have shown that ferromagnesite undergoes a pressure-induced spin crossover in the lower-mantle pressure range. A recent computational work done by Prof. Han Hsu’s group has indicated that nearly all thermal properties of ferromagnesite are drastically altered by iron spin crossover, including anomalous reduction of volume, anomalous softening of bulk modulus, and anomalous increases of thermal expansion, heat capacity, and the Grüneisen parameter. Remarkably, the anomaly of heat capacity remains prominent at high temperature without smearing out, which suggests that iron spin crossover may significantly affect the thermal properties of subducting slabs and the Earth’s deep carbon cycle. See further details in Hsu et al., Phys. Rev. B 103, 054401 (2021).</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>files/research/鐵的電子自旋態會不會影響地球深部碳循環.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>不只是能量分子</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>Molecular Cell, 73, 143-156 (2019)</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Yingying Pu, Yingxing Li, Xin Jin, Tian Tian, Qi Ma, Ziyi Zhao, Ssu-yuan Lin, Zhanghua Chen, Binghui Li, Guang Yao, Mark C. Leake, Chien-Jung Lo, and Fan Bai</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D44" t="inlineStr">
         <is>
           <t>不只是能量分子</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%b8%8d%e5%8f%aa%e6%98%af%e8%83%bd%e9%87%8f%e5%88%86%e5%ad%90/</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>我們提出一個新概念，細菌的休眠深度，是由於不同ATP濃度降低引起的不同程度蛋白聚集所引起，此舉有助於細菌抗藥性</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>We introduced a concept of ‘‘dormancy depth’’ that provides a unifying framework for understanding both persisters and viable
 but non-culturable cells. Subsequent mechanistic investigations revealed how ATP-dependent dynamic protein aggregation regulates cellular dormancy and resuscitation, the fine control of
 which facilitates bacterial drug tolerance.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>files/research/不只是能量分子.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Nature Communications 11, 2787 (2020)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Zan Nie, Chih-Hao Pai, Jie Zhang, Xiaonan Ning, Jianfei Hua, Yunxiao He, Yipeng Wu, Qianqian Su, Shuang Liu, Yue Ma, Zhi Cheng, Wei Lu, Hsu-Hsin Chu, Jyhpyng Wang, Chaojie Zhang, Warren B. Mori, and Chan Joshi</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%a5%e9%9b%b7%e5%b0%84%e9%9b%bb%e6%bc%bf%e7%94%a2%e7%94%9f%e5%85%b7%e6%9c%89%e7%9b%b8%e5%b0%8d%e8%ab%96%e6%80%a7%e5%bc%b7%e5%ba%a6%e3%80%81%e6%b3%a2%e9%95%b7%e5%8f%af%e8%aa%bf%e3%80%81%e5%96%ae/</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>實現單週期、相對論光強並且可調的中紅外脈衝將會為超快化學、強場物理與阿秒科學等研究領域帶來全新的機遇。但是由於傳統雷射晶體技術的限制，長期以來如何產生超短超強中紅外光源（特別是波長大於5微米）始終是超快雷射技術的一大挑戰。基於中大100兆瓦雷射設施，本論文在國際上首次實驗驗證了一種基於雷射電漿“光子減速”的機制可以用來產生具有相對論光強、波長可調、單週期、長波紅外脈衝的新方案。在特殊設計的電漿密度結構中，兆瓦級雷射脈衝將驅動近乎真空的電漿空泡，並且脈衝中的光子會大量減速而轉換成中紅外光。利用此方法我們可以能量效率大於百分之一產生中心波長在3–20微米可調、近單周期、峰值功率0.1兆瓦的超強中紅外脈衝源。</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Based on NCU's 100 TW laser facility, this paper is the first experimental demonstration of a laser-plasma photon deceleration mechanism generating relativistic-intensity, tunable wavelength, single-cycle long-wavelength infrared pulses. In a tailored plasma density structure, TW laser pulses drive plasma bubbles, photons decelerate and convert to mid-IR light with &gt;1% efficiency, tunable 3-20 um wavelength, and 0.1 TW peak power.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>files/research/以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源.webp</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>看見細胞壁的生長</t>
+          <t>以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Nature Communications, 12, 2160 (2021)</t>
+          <t>Nature Communications 11, 2787 (2020)</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Yi-Jen Sun, Fan Bai, An-Chi Luo, Xiang-Yu Zhuang, Tsai-Shun Lin, Yu-Cheng Sung, Yu-Ling Shih &amp; Chien-Jung Lo</t>
+          <t>Zan Nie, Chih-Hao Pai, Jie Zhang, Xiaonan Ning, Jianfei Hua, Yunxiao He, Yipeng Wu, Qianqian Su, Shuang Liu, Yue Ma, Zhi Cheng, Wei Lu, Hsu-Hsin Chu, Jyhpyng Wang, Chaojie Zhang, Warren B. Mori, and Chan Joshi</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Probing bacterial cell wall growth by tracing wall-anchored protein complexes</t>
+          <t>以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%9c%8b%e8%a6%8b%e7%b4%b0%e8%83%9e%e5%a3%81%e7%9a%84%e7%94%9f%e9%95%b7/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e4%bb%a5%e9%9b%b7%e5%b0%84%e9%9b%bb%e6%bc%bf%e7%94%a2%e7%94%9f%e5%85%b7%e6%9c%89%e7%9b%b8%e5%b0%8d%e8%ab%96%e6%80%a7%e5%bc%b7%e5%ba%a6%e3%80%81%e6%b3%a2%e9%95%b7%e5%8f%af%e8%aa%bf%e3%80%81%e5%96%ae/</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>細菌怎麼一邊生長一邊維持外型呢? 細菌細胞壁的動態組裝是細菌生長時維持外型的重要關鍵。我們發明一個新實驗方法來量測細菌生長時生長區、非生長區和分裂區的高解析動態。我們也建立一個數學模型來預測表面固定蛋白在細胞分裂後的位置分配。這個結果告訴我們細菌可以簡單並且有效地平均分配表面固定蛋白給下一代。</t>
+          <t>實現單週期、相對論光強並且可調的中紅外脈衝將會為超快化學、強場物理與阿秒科學等研究領域帶來全新的機遇。但是由於傳統雷射晶體技術的限制，長期以來如何產生超短超強中紅外光源（特別是波長大於5微米）始終是超快雷射技術的一大挑戰。基於中大100兆瓦雷射設施，本論文在國際上首次實驗驗證了一種基於雷射電漿“光子減速”的機制可以用來產生具有相對論光強、波長可調、單週期、長波紅外脈衝的新方案。在特殊設計的電漿密度結構中，兆瓦級雷射脈衝將驅動近乎真空的電漿空泡，並且脈衝中的光子會大量減速而轉換成中紅外光。利用此方法我們可以能量效率大於百分之一產生中心波長在3–20微米可調、近單周期、峰值功率0.1兆瓦的超強中紅外脈衝源。</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dynamic cell wall assembly is key to cell shape maintenance during bacterial growth. Here, we present a method that allows high-resolution analysis of active and inert zones of cell wall growth during bacterial elongation. We also formulate a mathematical model to predict the even partitioning of cell wall-anchored proteins following cell division.</t>
+          <t>Based on NCU's 100 TW laser facility, this paper is the first experimental demonstration of a laser-plasma photon deceleration mechanism generating relativistic-intensity, tunable wavelength, single-cycle long-wavelength infrared pulses. In a tailored plasma density structure, TW laser pulses drive plasma bubbles, photons decelerate and convert to mid-IR light with &gt;1% efficiency, tunable 3-20 um wavelength, and 0.1 TW peak power.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>files/research/看見細胞壁的生長.webp</t>
+          <t>files/research/以雷射電漿產生具有相對論性強度、波長可調、單週期的長波紅外脈衝源.webp</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>物理量有非交換值的量子力學直觀幾何圖像</t>
+          <t>看見細胞壁的生長</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Results in Physics 19, 103636 (2020)</t>
+          <t>Nature Communications, 12, 2160 (2021)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Otto C.W. Kong</t>
+          <t>Yi-Jen Sun, Fan Bai, An-Chi Luo, Xiang-Yu Zhuang, Tsai-Shun Lin, Yu-Cheng Sung, Yu-Ling Shih &amp; Chien-Jung Lo</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>An Intuitive Geometric Picture of Quantum Mechanics with Noncommutative Values for Observables</t>
+          <t>Probing bacterial cell wall growth by tracing wall-anchored protein complexes</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/an-intuitive-geometric-picture-of-quantum-mechanics-with-noncommutative-values-for-observables/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%9c%8b%e8%a6%8b%e7%b4%b0%e8%83%9e%e5%a3%81%e7%9a%84%e7%94%9f%e9%95%b7/</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>位置和動量算符是物理空間的量子非交換幾何圖像的坐標。 如所有可觀測值一樣，它們有確定但非可交換的值，包含理論所預測的多於整個概率分佈的完整信息。 我們可學會更直接地處理此類非交換值。</t>
+          <t>細菌怎麼一邊生長一邊維持外型呢? 細菌細胞壁的動態組裝是細菌生長時維持外型的重要關鍵。我們發明一個新實驗方法來量測細菌生長時生長區、非生長區和分裂區的高解析動態。我們也建立一個數學模型來預測表面固定蛋白在細胞分裂後的位置分配。這個結果告訴我們細菌可以簡單並且有效地平均分配表面固定蛋白給下一代。</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Position and momentum operators are coordinates of the quantum, noncommutative geometric, picture of our physical space. Like all observables, they take definite but noncommutative values which give full information about them, beyond the whole probability distributions, as predicted by the theory. We may learn to deal with such noncommutative values more directly.</t>
+          <t>Dynamic cell wall assembly is key to cell shape maintenance during bacterial growth. Here, we present a method that allows high-resolution analysis of active and inert zones of cell wall growth during bacterial elongation. We also formulate a mathematical model to predict the even partitioning of cell wall-anchored proteins following cell division.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>files/research/物理量有非交換值的量子力學直觀幾何圖像.webp</t>
+          <t>files/research/看見細胞壁的生長.webp</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Thickness dependence of spin torque effect in Fe/MgO/Fe magnetic tunnel junction: Implementation of divide-and-conquer with first-principles calculation</t>
+          <t>物理量有非交換值的量子力學直觀幾何圖像</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AIP Advances 11, 015036 (2021)</t>
+          <t>Results in Physics 19, 103636 (2020)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bao-Huei Huang*, Chia-Chia Chao, Yu-Hui Tang*</t>
+          <t>Otto C.W. Kong</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Thickness dependence of spin torque effect in Fe/MgO/Fe magnetic tunnel junction: Implementation of divide-and-conquer with first-principles calculation</t>
+          <t>An Intuitive Geometric Picture of Quantum Mechanics with Noncommutative Values for Observables</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/thickness-dependence-of-spin-torque-effect-in-fe-mgo-fe-magnetic-tunnel-junction-implementation-of-divide-and-conquer-with-first-principles-calculation/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/an-intuitive-geometric-picture-of-quantum-mechanics-with-noncommutative-values-for-observables/</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>在第一原理計算材料的領域中，計算複雜度通常會跟原子數成正比，所需要的計算時間與自洽困難度也會隨之增長。在本篇研究中，我們應用分治演算法 (divide-and-conquer, DC) 的概念，來避免直接求解大型系統的哈密頓量。利用原子軌道的局域特性，與符合邊界條件的情況下，我們可以先將大型系統分成若干個小型系統個別求解，最後再組合出大系統的哈密頓量。搭配我們開發的JunPy軟體來計算系統的非平衡格林函數，可以求解系統在加電壓下的自旋電子流與自旋力矩。我們結合這些方法，來研究磁性穿隧接面Fe/MgO/Fe的自旋傳輸特性，結果顯示大部分的自旋力矩會在接面附近被完全吸收，因此如果想要利用電流來有效率地翻轉磁矩，Fe磁性層薄膜的厚度須盡量小於2奈米。</t>
+          <t>位置和動量算符是物理空間的量子非交換幾何圖像的坐標。 如所有可觀測值一樣，它們有確定但非可交換的值，包含理論所預測的多於整個概率分佈的完整信息。 我們可學會更直接地處理此類非交換值。</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>In this study, our newly developed JunPy package is generalized by divide-and-conquer (DC) methodology to calculate the layer-resolved spin torques in Fe/MgO/Fe magnetic tunnel junction (MTJ), efficiently but without losing accuracy. Instead of directly carrying out the first-principles calculation for whole device with large amount of Fe layers, we divide it into smaller components that can be solved individually. The device Hamiltonian is thus recombined by the self-consistent block tridiagonal Hamiltonian matrix of each sub-system. Finally, the JunPy-DC calculation is applied to investigate the oscillatory decay of layer-resolved and cumulative spin torques for the Fe electrode with finite thickness. These results suggest that the Fe layer thickness should be no larger than 2 nm to preserve the current-driven magnetization switching process.</t>
+          <t>Position and momentum operators are coordinates of the quantum, noncommutative geometric, picture of our physical space. Like all observables, they take definite but noncommutative values which give full information about them, beyond the whole probability distributions, as predicted by the theory. We may learn to deal with such noncommutative values more directly.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>files/research/Thickness_dependence_of_spin1.webp</t>
+          <t>files/research/物理量有非交換值的量子力學直觀幾何圖像.webp</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>X光對原恆星盤冰晶的化學衍化影響</t>
+          <t>Thickness dependence of spin torque effect in Fe/MgO/Fe magnetic tunnel junction: Implementation of divide-and-conquer with first-principles calculation</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Proceedings of the National Academy of Sciences, 117, 16149 (2020)</t>
+          <t>AIP Advances 11, 015036 (2021)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>A. Ciaravella*, G. M. Muñoz Caro, A. Jiménez-Escobar, C. Cecchi-Pestellini, L.-C. Hsiao, C.-H. Huang, and Y.-J. Chen*</t>
+          <t>Bao-Huei Huang*, Chia-Chia Chao, Yu-Hui Tang*</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>X-ray processing of a realistic ice mantle can explain the gas abundances in protoplanetary disks</t>
+          <t>Thickness dependence of spin torque effect in Fe/MgO/Fe magnetic tunnel junction: Implementation of divide-and-conquer with first-principles calculation</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/x-ray-processing-of-a-realistic-ice-mantle-can-explain-the-gas-abundances-in-protoplanetary-disks/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/thickness-dependence-of-spin-torque-effect-in-fe-mgo-fe-magnetic-tunnel-junction-implementation-of-divide-and-conquer-with-first-principles-calculation/</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>在恆星系統剛形成的環境中，存在高通量的 X光能對冰晶分子的化學衍化造成極大的影響。由別於長久以來對於冰晶分子脫附現象只能發生在冰晶表面的觀念，我們首次觀測到在冰晶分子中數百奈米深的分子竟然也能在X光的照射下發生脫附的現象。此現象將對原有的冰晶脫附模型造成相當大的衝擊，此發現也對有機大分子脫附機制找到一線曙光。</t>
+          <t>在第一原理計算材料的領域中，計算複雜度通常會跟原子數成正比，所需要的計算時間與自洽困難度也會隨之增長。在本篇研究中，我們應用分治演算法 (divide-and-conquer, DC) 的概念，來避免直接求解大型系統的哈密頓量。利用原子軌道的局域特性，與符合邊界條件的情況下，我們可以先將大型系統分成若干個小型系統個別求解，最後再組合出大系統的哈密頓量。搭配我們開發的JunPy軟體來計算系統的非平衡格林函數，可以求解系統在加電壓下的自旋電子流與自旋力矩。我們結合這些方法，來研究磁性穿隧接面Fe/MgO/Fe的自旋傳輸特性，結果顯示大部分的自旋力矩會在接面附近被完全吸收，因此如果想要利用電流來有效率地翻轉磁矩，Fe磁性層薄膜的厚度須盡量小於2奈米。</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>In newly formed stellar systems, high X-ray flux significantly affects chemical processing of ice molecules. We first observed desorption of molecules hundreds of nanometers deep in ice upon X-ray irradiation, contrary to the view that desorption only occurs at the ice surface, shedding light on the desorption mechanism of complex organic molecules.</t>
+          <t>In this study, our newly developed JunPy package is generalized by divide-and-conquer (DC) methodology to calculate the layer-resolved spin torques in Fe/MgO/Fe magnetic tunnel junction (MTJ), efficiently but without losing accuracy. Instead of directly carrying out the first-principles calculation for whole device with large amount of Fe layers, we divide it into smaller components that can be solved individually. The device Hamiltonian is thus recombined by the self-consistent block tridiagonal Hamiltonian matrix of each sub-system. Finally, the JunPy-DC calculation is applied to investigate the oscillatory decay of layer-resolved and cumulative spin torques for the Fe electrode with finite thickness. These results suggest that the Fe layer thickness should be no larger than 2 nm to preserve the current-driven magnetization switching process.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>files/research/X光對原恆星盤冰晶的化學衍化影響.webp</t>
+          <t>files/research/Thickness_dependence_of_spin1.webp</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Distinct electronic and transport properties between 1T-HfSe2 and 1T-PtSe2</t>
+          <t>X光對原恆星盤冰晶的化學衍化影響</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Chin. J. Phys 62, 151-160 (2019)</t>
+          <t>Proceedings of the National Academy of Sciences, 117, 16149 (2020)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Icuk Setiyawati, Kuan-Rong Chiang, Hsin-Mei Ho, Yu-Hui Tang*</t>
+          <t>A. Ciaravella*, G. M. Muñoz Caro, A. Jiménez-Escobar, C. Cecchi-Pestellini, L.-C. Hsiao, C.-H. Huang, and Y.-J. Chen*</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Distinct electronic and transport properties between 1T-HfSe2 and 1T-PtSe2</t>
+          <t>X-ray processing of a realistic ice mantle can explain the gas abundances in protoplanetary disks</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/distinct-electronic-and-transport-properties-between-1t-hfse2-and-1t-ptse2/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/x-ray-processing-of-a-realistic-ice-mantle-can-explain-the-gas-abundances-in-protoplanetary-disks/</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>透過第一原理計算來研究1T-HfSe2以及1T-PtSe2過渡金屬二硫族化物（transition metal dichalcogenides）的結構、電子、以及傳輸特性；我們更進一步解釋為何這兩種化合物具有相同的1T (八面體)層狀結構，但卻存在非常不同的電子和傳輸特性。我們發現有兩個決定性的因素(i)過度金屬的5d價電子數以及(ii)層內鍵結離子性。因此，我們認為1T-HfSe2所具有的二維傳輸特性，以及在1T-PtSe2中可透過層數所調控的金屬-半導體轉換，可以應用在新型態的奈米電子以及光電元件開發。</t>
+          <t>在恆星系統剛形成的環境中，存在高通量的 X光能對冰晶分子的化學衍化造成極大的影響。由別於長久以來對於冰晶分子脫附現象只能發生在冰晶表面的觀念，我們首次觀測到在冰晶分子中數百奈米深的分子竟然也能在X光的照射下發生脫附的現象。此現象將對原有的冰晶脫附模型造成相當大的衝擊，此發現也對有機大分子脫附機制找到一線曙光。</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>In this study, we employed the first-principles calculation to investigate the structural, electronic and transport properties of 1T-HfSe2 and 1T-PtSe2 transition metal dichalcogenides, and further explain why they share the same 1T (octahedral) layered structure but exhibit very different electronic and transport properties. There are two underlying concepts: the degree of intralayer bond ionicity and the number of 5d valence electrons of transition metal. The high degree of Hf-Se bond ionicity not only gives rise to the indirect energy gap of HfSe2 bulk and thin films, but also results in the weak Se-Se vdW interlayer coupling to further restrict the electron transport only within a HfSe2 layer. On the other hand, the modulation of metallic/semiconducting property of PtSe2 bulk and thin films can be understood by the significant vdW interlayer coupling, which induces charge redistribution of Se atom and allows electrons to transport within a PtSe2 layer as well as cross neighboring layers. Finally, our transport calculation for 1T-HfSe2/1T-PtSe2 bulks and monolayers suggests the great electron transport within Hf-Se/Pt-Se layer but suppresses/allows electron from neighboring layers. The robust two-dimensional characteristic of 1T-HfSe2 and the metal-to-semiconductor transition of 1T-PtSe2 may provide more knowledge for future application in nanoelectronic and optoelectronic devices.</t>
+          <t>In newly formed stellar systems, high X-ray flux significantly affects chemical processing of ice molecules. We first observed desorption of molecules hundreds of nanometers deep in ice upon X-ray irradiation, contrary to the view that desorption only occurs at the ice surface, shedding light on the desorption mechanism of complex organic molecules.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>files/research/Distinct_electronic.webp</t>
+          <t>files/research/X光對原恆星盤冰晶的化學衍化影響.webp</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>離子通道 Betatron X 光光源研究</t>
+          <t>Distinct electronic and transport properties between 1T-HfSe2 and 1T-PtSe2</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Plasma Physics and Controlled Fusion, 61, 035003 (2019)</t>
+          <t>Chin. J. Phys 62, 151-160 (2019)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>B. Guo, Z. Cheng, S. Liu, X.-N. Ning, J. Zhang, C.-H. Pai, J.-F. Hua, H.-H. Chu, J. Wang, and W. Lu</t>
+          <t>Icuk Setiyawati, Kuan-Rong Chiang, Hsin-Mei Ho, Yu-Hui Tang*</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Enhancement of laser-driven betatron X-rays by a density-depressed plasma structure</t>
+          <t>Distinct electronic and transport properties between 1T-HfSe2 and 1T-PtSe2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%9b%a2%e5%ad%90%e9%80%9a%e9%81%93-betatron-x-%e5%85%89%e5%85%89%e6%ba%90%e7%a0%94%e7%a9%b6/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/distinct-electronic-and-transport-properties-between-1t-hfse2-and-1t-ptse2/</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>利用電漿結構密度變化增強雷射電子加速器中之 Betatron X 光輸出</t>
+          <t>透過第一原理計算來研究1T-HfSe2以及1T-PtSe2過渡金屬二硫族化物（transition metal dichalcogenides）的結構、電子、以及傳輸特性；我們更進一步解釋為何這兩種化合物具有相同的1T (八面體)層狀結構，但卻存在非常不同的電子和傳輸特性。我們發現有兩個決定性的因素(i)過度金屬的5d價電子數以及(ii)層內鍵結離子性。因此，我們認為1T-HfSe2所具有的二維傳輸特性，以及在1T-PtSe2中可透過層數所調控的金屬-半導體轉換，可以應用在新型態的奈米電子以及光電元件開發。</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Significant enhancement of betatron x-ray radiation from a laser-wakefield electron accelerator is done by inserting a density-depressed plasma structure.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>雷射尾波電子加速器產生Betatron X 光架設圖</t>
+          <t>In this study, we employed the first-principles calculation to investigate the structural, electronic and transport properties of 1T-HfSe2 and 1T-PtSe2 transition metal dichalcogenides, and further explain why they share the same 1T (octahedral) layered structure but exhibit very different electronic and transport properties. There are two underlying concepts: the degree of intralayer bond ionicity and the number of 5d valence electrons of transition metal. The high degree of Hf-Se bond ionicity not only gives rise to the indirect energy gap of HfSe2 bulk and thin films, but also results in the weak Se-Se vdW interlayer coupling to further restrict the electron transport only within a HfSe2 layer. On the other hand, the modulation of metallic/semiconducting property of PtSe2 bulk and thin films can be understood by the significant vdW interlayer coupling, which induces charge redistribution of Se atom and allows electrons to transport within a PtSe2 layer as well as cross neighboring layers. Finally, our transport calculation for 1T-HfSe2/1T-PtSe2 bulks and monolayers suggests the great electron transport within Hf-Se/Pt-Se layer but suppresses/allows electron from neighboring layers. The robust two-dimensional characteristic of 1T-HfSe2 and the metal-to-semiconductor transition of 1T-PtSe2 may provide more knowledge for future application in nanoelectronic and optoelectronic devices.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>files/research/離子通道BetatronX光光源研究.webp</t>
+          <t>files/research/Distinct_electronic.webp</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>高解析度 X 光相位對比攝影</t>
+          <t>離子通道 Betatron X 光光源研究</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Scientific Reports 9, 7796 (2019)</t>
+          <t>Plasma Physics and Controlled Fusion, 61, 035003 (2019)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Bo Guo, Xiaohui Zhang, Jie Zhang, Jianfei Hua, Chih-Hao Pai, Chaojie Zhang, Hsu-Hsin Chu, Warren Mori, Chan Joshi, Jyhpyng Wang, and Wei Lu</t>
+          <t>B. Guo, Z. Cheng, S. Liu, X.-N. Ning, J. Zhang, C.-H. Pai, J.-F. Hua, H.-H. Chu, J. Wang, and W. Lu</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>High-resolution phase-contrast imaging of biological specimens using a stable betatron X-ray source in the multiple-exposure mode</t>
+          <t>Enhancement of laser-driven betatron X-rays by a density-depressed plasma structure</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%ab%98%e8%a7%a3%e6%9e%90%e5%ba%a6-x-%e5%85%89%e7%9b%b8%e4%bd%8d%e5%b0%8d%e6%af%94%e6%94%9d%e5%bd%b1/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%9b%a2%e5%ad%90%e9%80%9a%e9%81%93-betatron-x-%e5%85%89%e5%85%89%e6%ba%90%e7%a0%94%e7%a9%b6/</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>利用電漿結構密度變化增強雷射電子加速器中之 Betatron X 光輸出</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>High-resolution phase-contrast imaging of biological specimens using a stable betatron X-ray source in multiple-exposure mode.</t>
+          <t>Significant enhancement of betatron x-ray radiation from a laser-wakefield electron accelerator is done by inserting a density-depressed plasma structure.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>實驗架設圖與X光相位對比影像</t>
+          <t>雷射尾波電子加速器產生Betatron X 光架設圖</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>files/research/高解析度X光相位對比攝影.webp</t>
+          <t>files/research/離子通道BetatronX光光源研究.webp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>碳化鈧自由基近紅外雷射光譜</t>
+          <t>高解析度 X 光相位對比攝影</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Journal of Molecular Spectroscopy 361, 40-46 (2019)</t>
+          <t>Scientific Reports 9, 7796 (2019)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chiao-Wei Chen, Anthony J. Merer, and Yen-Chu Hsu</t>
+          <t>Bo Guo, Xiaohui Zhang, Jie Zhang, Jianfei Hua, Chih-Hao Pai, Chaojie Zhang, Hsu-Hsin Chu, Warren Mori, Chan Joshi, Jyhpyng Wang, and Wei Lu</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A new 4Σ − a4Π electronic transition of ScC in the near infra-red</t>
+          <t>High-resolution phase-contrast imaging of biological specimens using a stable betatron X-ray source in the multiple-exposure mode</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a2%b3%e5%8c%96%e9%88%a7%e8%87%aa%e7%94%b1%e5%9f%ba%e8%bf%91%e7%b4%85%e5%a4%96%e9%9b%b7%e5%b0%84%e5%85%89%e8%ad%9c/</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>繼先前我們在可見光區的碳化鈧自由基光譜工作(Chen et. al., J. Chem.Phys. 149, 074302-1‒074302-15(2018) )，在近紅外光譜區找到一新系統。除了得到更精準的a4Π光譜常數外，提供在星雲中或太陽裡搜索ScC自由基的資訊。</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e9%ab%98%e8%a7%a3%e6%9e%90%e5%ba%a6-x-%e5%85%89%e7%9b%b8%e4%bd%8d%e5%b0%8d%e6%af%94%e6%94%9d%e5%bd%b1/</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Following our previous work of ScC radical (Chen et. al., J. Chem. Phys. 149, 074302-1‒074302-15 (2018) ), a new system in the near Infra-red region was found. Improved spectroscopic constants of a4Π were obtained, the line positions of this sytem are provided for searching the ScC radical in the interstellar cloud.</t>
+          <t>High-resolution phase-contrast imaging of biological specimens using a stable betatron X-ray source in multiple-exposure mode.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>碳化鈧自由基的能階 及鍵長。箭號指出相關的躍遷。 | 碳化鈧自由基的 4-a 4Π5/2 (1,0)近紅外光譜躍遷(部分), 黑色光譜為實驗結果，紅色譜線為譜帶模擬。</t>
+          <t>實驗架設圖與X光相位對比影像</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>files/research/碳化鈧自由基近紅外雷射光譜.webp</t>
+          <t>files/research/高解析度X光相位對比攝影.webp</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>超高強度單週期中紅外光脈衝產生</t>
+          <t>碳化鈧自由基近紅外雷射光譜</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Nature Photonics, 12, 489–494 (2018)</t>
+          <t>Journal of Molecular Spectroscopy 361, 40-46 (2019)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Zan Nie, Chih-Hao Pai, Jianfei Hua, Chaojie Zhang, Yipeng Wu, Yang Wan, Fei Li, Jie Zhang, Zhi Cheng, Qianqian Su, Shuang Liu, Yue Ma, Xiaonan Ning, Yunxiao He, Wei Lu, Hsu-Hsin Chu, Jyhpyng Wang, Warren B. Mori, and Chan Joshi</t>
+          <t>Chiao-Wei Chen, Anthony J. Merer, and Yen-Chu Hsu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Relativistic single-cycle tunable infrared pulses generated from a tailored plasma density structure</t>
+          <t>A new 4Σ − a4Π electronic transition of ScC in the near infra-red</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%b6%85%e9%ab%98%e5%bc%b7%e5%ba%a6%e5%96%ae%e9%80%b1%e6%9c%9f%e4%b8%ad%e7%b4%85%e5%a4%96%e5%85%89%e8%84%88%e8%a1%9d%e7%94%a2%e7%94%9f/</t>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e7%a2%b3%e5%8c%96%e9%88%a7%e8%87%aa%e7%94%b1%e5%9f%ba%e8%bf%91%e7%b4%85%e5%a4%96%e9%9b%b7%e5%b0%84%e5%85%89%e8%ad%9c/</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>模擬研究利用電漿非線性相位調變產生單週期強場中紅外光脈衝，並進行實驗驗證。</t>
+          <t>繼先前我們在可見光區的碳化鈧自由基光譜工作(Chen et. al., J. Chem.Phys. 149, 074302-1‒074302-15(2018) )，在近紅外光譜區找到一新系統。除了得到更精準的a4Π光譜常數外，提供在星雲中或太陽裡搜索ScC自由基的資訊。</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>By focusing ultrashort intense near-IR pulses into a tailored plasma density structure, relativistic single-cycle tunable infrared pulses can be generated from extreme frequency broadening.</t>
+          <t>Following our previous work of ScC radical (Chen et. al., J. Chem. Phys. 149, 074302-1‒074302-15 (2018) ), a new system in the near Infra-red region was found. Improved spectroscopic constants of a4Π were obtained, the line positions of this sytem are provided for searching the ScC radical in the interstellar cloud.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>電腦模擬電漿結構演化與單週期中紅外光脈衝生成</t>
+          <t>碳化鈧自由基的能階 及鍵長。箭號指出相關的躍遷。 | 碳化鈧自由基的 4-a 4Π5/2 (1,0)近紅外光譜躍遷(部分), 黑色光譜為實驗結果，紅色譜線為譜帶模擬。</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>files/research/超高強度單週期中紅外光脈衝產生.webp</t>
+          <t>files/research/碳化鈧自由基近紅外雷射光譜.webp</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>超高強度單週期中紅外光脈衝產生</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Nature Photonics, 12, 489–494 (2018)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Zan Nie, Chih-Hao Pai, Jianfei Hua, Chaojie Zhang, Yipeng Wu, Yang Wan, Fei Li, Jie Zhang, Zhi Cheng, Qianqian Su, Shuang Liu, Yue Ma, Xiaonan Ning, Yunxiao He, Wei Lu, Hsu-Hsin Chu, Jyhpyng Wang, Warren B. Mori, and Chan Joshi</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Relativistic single-cycle tunable infrared pulses generated from a tailored plasma density structure</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.phy.ncu.edu.tw/faculty-blog/%e8%b6%85%e9%ab%98%e5%bc%b7%e5%ba%a6%e5%96%ae%e9%80%b1%e6%9c%9f%e4%b8%ad%e7%b4%85%e5%a4%96%e5%85%89%e8%84%88%e8%a1%9d%e7%94%a2%e7%94%9f/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>模擬研究利用電漿非線性相位調變產生單週期強場中紅外光脈衝，並進行實驗驗證。</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>By focusing ultrashort intense near-IR pulses into a tailored plasma density structure, relativistic single-cycle tunable infrared pulses can be generated from extreme frequency broadening.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>電腦模擬電漿結構演化與單週期中紅外光脈衝生成</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>files/research/超高強度單週期中紅外光脈衝產生.webp</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
           <t>X光造成星際冰晶的脫附效應</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B55" t="inlineStr">
         <is>
           <t>Astrophysical Journal, 868, 73 (2018)</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>A. Jiménez-Escobar, A. Ciaravella, C. Cecchi-Pestellini, C.-H. Huang, N.-E. Sie, Y.-J. Chen* and G. M. Muñoz Caro</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>X-Ray Photo-Desorption of H2O:CO:NH3 Circumstellar Ice Analogs: Gas-Phase Enrichment</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>https://www.phy.ncu.edu.tw/faculty-blog/x-ray-photo-desorption-of-h2oconh3-circumstellar-ice-analogs-gas-phase-enrichment/</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>在太空環境中，複雜分子的生成機制被認為無法只經由氣體-氣體交互作用模型解釋其豐富的氣態含量。一般認為複雜分子是在星際冰中經由宇宙射線或是真空紫外光子照射下產生化學反應而生成，然而在極低溫環境下，這些複雜分子是如何不經由熱脫附過程而變成氣態分子一直是目前尚待了解的謎題。在此論文中，我們使用國家同步輻射研究中心所提供的soft X-ray觀測到C3H3NO, C4H5O, C4H7N等分子能夠在soft X-ray照射H2O+CO+NH3冰晶狀態下生成並脫附成為氣態分子。</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>In space, complex molecule formation cannot be explained solely by gas-gas interaction models. Using soft X-rays at the NSRRC, we observed that molecules such as C3H3NO, C4H5O, and C4H7N are formed and desorbed from H2O+CO+NH3 ice under soft X-ray irradiation.</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>files/research/X光造成星際冰晶的脫附效應.webp</t>
         </is>
